--- a/database/seeders/data/data.xlsx
+++ b/database/seeders/data/data.xlsx
@@ -231,7 +231,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8020" uniqueCount="1362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8390" uniqueCount="1362">
   <si>
     <t>PT. TASM</t>
   </si>
@@ -44574,9 +44574,8 @@
       <c r="P5" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q5" t="str">
-        <f>VLOOKUP(D5,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q5" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="18">
@@ -44627,9 +44626,8 @@
       <c r="P6" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q6" t="str">
-        <f>VLOOKUP(D6,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q6" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="18">
@@ -44680,9 +44678,8 @@
       <c r="P7" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q7" t="str">
-        <f>VLOOKUP(D7,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q7" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="18">
@@ -44733,9 +44730,8 @@
       <c r="P8" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q8" t="str">
-        <f>VLOOKUP(D8,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q8" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="18">
@@ -44786,9 +44782,8 @@
       <c r="P9" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q9" t="str">
-        <f>VLOOKUP(D9,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q9" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="18">
@@ -44839,9 +44834,8 @@
       <c r="P10" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q10" t="str">
-        <f>VLOOKUP(D10,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q10" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="18">
@@ -44892,9 +44886,8 @@
       <c r="P11" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q11" t="str">
-        <f>VLOOKUP(D11,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q11" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="18">
@@ -44943,9 +44936,8 @@
       <c r="P12" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q12" t="str">
-        <f>VLOOKUP(D12,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q12" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="18">
@@ -44996,9 +44988,8 @@
       <c r="P13" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q13" t="str">
-        <f>VLOOKUP(D13,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q13" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="18">
@@ -45051,9 +45042,8 @@
       <c r="P14" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q14" t="str">
-        <f>VLOOKUP(D14,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q14" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="18">
@@ -45104,9 +45094,8 @@
       <c r="P15" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q15" t="str">
-        <f>VLOOKUP(D15,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q15" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="18">
@@ -45157,9 +45146,8 @@
       <c r="P16" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q16" t="str">
-        <f>VLOOKUP(D16,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q16" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="18">
@@ -45210,9 +45198,8 @@
       <c r="P17" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q17" t="str">
-        <f>VLOOKUP(D17,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q17" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="18">
@@ -45263,9 +45250,8 @@
       <c r="P18" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q18" t="str">
-        <f>VLOOKUP(D18,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q18" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="18">
@@ -45316,9 +45302,8 @@
       <c r="P19" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q19" t="str">
-        <f>VLOOKUP(D19,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q19" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="18">
@@ -45369,9 +45354,8 @@
       <c r="P20" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q20" t="str">
-        <f>VLOOKUP(D20,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q20" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="18">
@@ -45422,9 +45406,8 @@
       <c r="P21" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q21" t="str">
-        <f>VLOOKUP(D21,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q21" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="18">
@@ -45475,9 +45458,8 @@
       <c r="P22" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q22" t="str">
-        <f>VLOOKUP(D22,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q22" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="18">
@@ -45528,9 +45510,8 @@
       <c r="P23" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q23" t="str">
-        <f>VLOOKUP(D23,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q23" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="18">
@@ -45581,9 +45562,8 @@
       <c r="P24" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q24" t="str">
-        <f>VLOOKUP(D24,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q24" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="18">
@@ -45634,9 +45614,8 @@
       <c r="P25" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q25" t="str">
-        <f>VLOOKUP(D25,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q25" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="18">
@@ -45687,9 +45666,8 @@
       <c r="P26" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q26" t="str">
-        <f>VLOOKUP(D26,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q26" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="18">
@@ -45740,9 +45718,8 @@
       <c r="P27" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q27" t="str">
-        <f>VLOOKUP(D27,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q27" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="18">
@@ -45793,9 +45770,8 @@
       <c r="P28" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q28" t="str">
-        <f>VLOOKUP(D28,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q28" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="18">
@@ -45846,9 +45822,8 @@
       <c r="P29" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q29" t="str">
-        <f>VLOOKUP(D29,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q29" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="18">
@@ -45899,9 +45874,8 @@
       <c r="P30" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q30" t="str">
-        <f>VLOOKUP(D30,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q30" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="18">
@@ -45952,9 +45926,8 @@
       <c r="P31" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q31" t="str">
-        <f>VLOOKUP(D31,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q31" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="18">
@@ -46005,9 +45978,8 @@
       <c r="P32" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q32" t="str">
-        <f>VLOOKUP(D32,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q32" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="18">
@@ -46058,9 +46030,8 @@
       <c r="P33" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q33" t="str">
-        <f>VLOOKUP(D33,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q33" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="18">
@@ -46111,9 +46082,8 @@
       <c r="P34" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q34" t="str">
-        <f>VLOOKUP(D34,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q34" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="18">
@@ -46164,9 +46134,8 @@
       <c r="P35" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q35" t="str">
-        <f>VLOOKUP(D35,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q35" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="18">
@@ -46217,9 +46186,8 @@
       <c r="P36" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q36" t="str">
-        <f>VLOOKUP(D36,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q36" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="18">
@@ -46270,9 +46238,8 @@
       <c r="P37" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q37" t="str">
-        <f>VLOOKUP(D37,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q37" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="18">
@@ -46323,9 +46290,8 @@
       <c r="P38" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q38" t="str">
-        <f>VLOOKUP(D38,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q38" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="18">
@@ -46376,9 +46342,8 @@
       <c r="P39" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q39" t="str">
-        <f>VLOOKUP(D39,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q39" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="18">
@@ -46429,9 +46394,8 @@
       <c r="P40" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q40" t="str">
-        <f>VLOOKUP(D40,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q40" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="41" spans="1:17" ht="18">
@@ -46482,9 +46446,8 @@
       <c r="P41" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q41" t="str">
-        <f>VLOOKUP(D41,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q41" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="42" spans="1:17" ht="18">
@@ -46535,9 +46498,8 @@
       <c r="P42" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q42" t="str">
-        <f>VLOOKUP(D42,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q42" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="43" spans="1:17" ht="18">
@@ -46588,9 +46550,8 @@
       <c r="P43" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q43" t="str">
-        <f>VLOOKUP(D43,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q43" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="44" spans="1:17" ht="18">
@@ -46641,9 +46602,8 @@
       <c r="P44" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q44" t="str">
-        <f>VLOOKUP(D44,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q44" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="45" spans="1:17" ht="18">
@@ -46694,9 +46654,8 @@
       <c r="P45" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q45" t="str">
-        <f>VLOOKUP(D45,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q45" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="46" spans="1:17" ht="18">
@@ -46747,9 +46706,8 @@
       <c r="P46" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q46" t="str">
-        <f>VLOOKUP(D46,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q46" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="47" spans="1:17" ht="18">
@@ -46800,9 +46758,8 @@
       <c r="P47" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q47" t="str">
-        <f>VLOOKUP(D47,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q47" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="48" spans="1:17" ht="18">
@@ -46853,9 +46810,8 @@
       <c r="P48" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q48" t="str">
-        <f>VLOOKUP(D48,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q48" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="49" spans="1:17" ht="18">
@@ -46906,9 +46862,8 @@
       <c r="P49" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q49" t="str">
-        <f>VLOOKUP(D49,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q49" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="50" spans="1:17" ht="18">
@@ -46959,9 +46914,8 @@
       <c r="P50" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q50" t="str">
-        <f>VLOOKUP(D50,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q50" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="18">
@@ -47012,9 +46966,8 @@
       <c r="P51" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q51" t="str">
-        <f>VLOOKUP(D51,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q51" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="52" spans="1:17" ht="18">
@@ -47065,9 +47018,8 @@
       <c r="P52" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q52" t="str">
-        <f>VLOOKUP(D52,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q52" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="18">
@@ -47118,9 +47070,8 @@
       <c r="P53" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q53" t="str">
-        <f>VLOOKUP(D53,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q53" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="54" spans="1:17" ht="18">
@@ -47171,9 +47122,8 @@
       <c r="P54" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q54" t="str">
-        <f>VLOOKUP(D54,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q54" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="55" spans="1:17" ht="18">
@@ -47224,9 +47174,8 @@
       <c r="P55" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q55" t="str">
-        <f>VLOOKUP(D55,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q55" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="56" spans="1:17" ht="18">
@@ -47277,9 +47226,8 @@
       <c r="P56" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q56" t="str">
-        <f>VLOOKUP(D56,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q56" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="57" spans="1:17" ht="18">
@@ -47330,9 +47278,8 @@
       <c r="P57" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q57" t="str">
-        <f>VLOOKUP(D57,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q57" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="18">
@@ -47381,9 +47328,8 @@
       <c r="P58" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q58" t="str">
-        <f>VLOOKUP(D58,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q58" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="59" spans="1:17" ht="18">
@@ -47434,9 +47380,8 @@
       <c r="P59" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q59" t="str">
-        <f>VLOOKUP(D59,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q59" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="18">
@@ -47487,9 +47432,8 @@
       <c r="P60" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q60" t="str">
-        <f>VLOOKUP(D60,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q60" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="61" spans="1:17" ht="18">
@@ -47540,9 +47484,8 @@
       <c r="P61" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q61" t="str">
-        <f>VLOOKUP(D61,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q61" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="62" spans="1:17" ht="18">
@@ -47595,9 +47538,8 @@
       <c r="P62" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q62" t="str">
-        <f>VLOOKUP(D62,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q62" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="63" spans="1:17" ht="18">
@@ -47648,9 +47590,8 @@
       <c r="P63" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q63" t="str">
-        <f>VLOOKUP(D63,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q63" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="64" spans="1:17" ht="18">
@@ -47701,9 +47642,8 @@
       <c r="P64" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q64" t="str">
-        <f>VLOOKUP(D64,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q64" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="65" spans="1:17" ht="18">
@@ -47754,9 +47694,8 @@
       <c r="P65" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q65" t="str">
-        <f>VLOOKUP(D65,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q65" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="18">
@@ -47807,9 +47746,8 @@
       <c r="P66" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q66" t="str">
-        <f>VLOOKUP(D66,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q66" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="67" spans="1:17" ht="18">
@@ -47860,9 +47798,8 @@
       <c r="P67" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q67" t="str">
-        <f>VLOOKUP(D67,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q67" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="68" spans="1:17" ht="18">
@@ -47913,9 +47850,8 @@
       <c r="P68" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q68" t="str">
-        <f>VLOOKUP(D68,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q68" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="69" spans="1:17" ht="18">
@@ -47966,9 +47902,8 @@
       <c r="P69" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q69" t="str">
-        <f>VLOOKUP(D69,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q69" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="70" spans="1:17" ht="18">
@@ -48019,9 +47954,8 @@
       <c r="P70" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q70" t="str">
-        <f>VLOOKUP(D70,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q70" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="71" spans="1:17" ht="18">
@@ -48072,9 +48006,8 @@
       <c r="P71" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q71" t="str">
-        <f>VLOOKUP(D71,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q71" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="72" spans="1:17" ht="18">
@@ -48125,9 +48058,8 @@
       <c r="P72" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q72" t="str">
-        <f>VLOOKUP(D72,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q72" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="73" spans="1:17" ht="18">
@@ -48178,9 +48110,8 @@
       <c r="P73" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q73" t="str">
-        <f>VLOOKUP(D73,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q73" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="74" spans="1:17" ht="18">
@@ -48231,9 +48162,8 @@
       <c r="P74" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q74" t="str">
-        <f>VLOOKUP(D74,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q74" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="75" spans="1:17" ht="18">
@@ -48284,9 +48214,8 @@
       <c r="P75" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q75" t="str">
-        <f>VLOOKUP(D75,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q75" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="76" spans="1:17" ht="18">
@@ -48337,9 +48266,8 @@
       <c r="P76" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q76" t="str">
-        <f>VLOOKUP(D76,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q76" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="77" spans="1:17" ht="18">
@@ -48390,9 +48318,8 @@
       <c r="P77" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q77" t="str">
-        <f>VLOOKUP(D77,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q77" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="78" spans="1:17" ht="18">
@@ -48443,9 +48370,8 @@
       <c r="P78" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q78" t="str">
-        <f>VLOOKUP(D78,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q78" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="79" spans="1:17" ht="18">
@@ -48498,9 +48424,8 @@
       <c r="P79" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q79" t="str">
-        <f>VLOOKUP(D79,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q79" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="80" spans="1:17" ht="18">
@@ -48551,9 +48476,8 @@
       <c r="P80" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q80" t="str">
-        <f>VLOOKUP(D80,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q80" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="81" spans="1:17" ht="18">
@@ -48604,9 +48528,8 @@
       <c r="P81" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q81" t="str">
-        <f>VLOOKUP(D81,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q81" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="82" spans="1:17" ht="18">
@@ -48657,9 +48580,8 @@
       <c r="P82" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q82" t="str">
-        <f>VLOOKUP(D82,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q82" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="83" spans="1:17" ht="18">
@@ -48710,9 +48632,8 @@
       <c r="P83" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q83" t="str">
-        <f>VLOOKUP(D83,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q83" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="84" spans="1:17" ht="18">
@@ -48763,9 +48684,8 @@
       <c r="P84" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q84" t="str">
-        <f>VLOOKUP(D84,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q84" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="85" spans="1:17" ht="18">
@@ -48816,9 +48736,8 @@
       <c r="P85" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q85" t="str">
-        <f>VLOOKUP(D85,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q85" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="86" spans="1:17" ht="18">
@@ -48869,9 +48788,8 @@
       <c r="P86" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q86" t="str">
-        <f>VLOOKUP(D86,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q86" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="87" spans="1:17" ht="18">
@@ -48922,9 +48840,8 @@
       <c r="P87" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q87" t="str">
-        <f>VLOOKUP(D87,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q87" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="88" spans="1:17" ht="18">
@@ -48975,9 +48892,8 @@
       <c r="P88" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q88" t="str">
-        <f>VLOOKUP(D88,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q88" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="89" spans="1:17" ht="18">
@@ -49030,9 +48946,8 @@
       <c r="P89" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q89" t="str">
-        <f>VLOOKUP(D89,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q89" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="90" spans="1:17" ht="18">
@@ -49083,9 +48998,8 @@
       <c r="P90" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q90" t="str">
-        <f>VLOOKUP(D90,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q90" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="91" spans="1:17" ht="18">
@@ -49136,9 +49050,8 @@
       <c r="P91" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q91" t="str">
-        <f>VLOOKUP(D91,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q91" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="92" spans="1:17" ht="18">
@@ -49189,9 +49102,8 @@
       <c r="P92" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q92" t="str">
-        <f>VLOOKUP(D92,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q92" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="93" spans="1:17" ht="18">
@@ -49242,9 +49154,8 @@
       <c r="P93" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q93" t="str">
-        <f>VLOOKUP(D93,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q93" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="94" spans="1:17" ht="18">
@@ -49295,9 +49206,8 @@
       <c r="P94" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q94" t="str">
-        <f>VLOOKUP(D94,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q94" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="95" spans="1:17" ht="18">
@@ -49350,9 +49260,8 @@
       <c r="P95" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q95" t="str">
-        <f>VLOOKUP(D95,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q95" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="96" spans="1:17" ht="18">
@@ -49403,9 +49312,8 @@
       <c r="P96" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q96" t="str">
-        <f>VLOOKUP(D96,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q96" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="97" spans="1:17" ht="18">
@@ -49456,9 +49364,8 @@
       <c r="P97" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q97" t="str">
-        <f>VLOOKUP(D97,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q97" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="98" spans="1:17" ht="18">
@@ -49509,9 +49416,8 @@
       <c r="P98" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q98" t="str">
-        <f>VLOOKUP(D98,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q98" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="99" spans="1:17" ht="18">
@@ -49562,9 +49468,8 @@
       <c r="P99" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q99" t="str">
-        <f>VLOOKUP(D99,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q99" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="100" spans="1:17" ht="18">
@@ -49615,9 +49520,8 @@
       <c r="P100" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q100" t="str">
-        <f>VLOOKUP(D100,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q100" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="101" spans="1:17" ht="18">
@@ -49668,9 +49572,8 @@
       <c r="P101" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q101" t="str">
-        <f>VLOOKUP(D101,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q101" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="102" spans="1:17" ht="18">
@@ -49721,9 +49624,8 @@
       <c r="P102" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q102" t="str">
-        <f>VLOOKUP(D102,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q102" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="103" spans="1:17" ht="18">
@@ -49774,9 +49676,8 @@
       <c r="P103" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q103" t="str">
-        <f>VLOOKUP(D103,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q103" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="104" spans="1:17" ht="18">
@@ -49827,9 +49728,8 @@
       <c r="P104" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q104" t="str">
-        <f>VLOOKUP(D104,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q104" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="105" spans="1:17" ht="18">
@@ -49880,9 +49780,8 @@
       <c r="P105" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q105" t="str">
-        <f>VLOOKUP(D105,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q105" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="106" spans="1:17" ht="18">
@@ -49933,9 +49832,8 @@
       <c r="P106" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q106" t="str">
-        <f>VLOOKUP(D106,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q106" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="107" spans="1:17" ht="18">
@@ -49986,9 +49884,8 @@
       <c r="P107" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q107" t="str">
-        <f>VLOOKUP(D107,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q107" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="108" spans="1:17" ht="18">
@@ -50039,9 +49936,8 @@
       <c r="P108" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q108" t="str">
-        <f>VLOOKUP(D108,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q108" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="109" spans="1:17" ht="18">
@@ -50092,9 +49988,8 @@
       <c r="P109" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q109" t="str">
-        <f>VLOOKUP(D109,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q109" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="110" spans="1:17" ht="18">
@@ -50145,9 +50040,8 @@
       <c r="P110" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q110" t="str">
-        <f>VLOOKUP(D110,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q110" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="111" spans="1:17" ht="18">
@@ -50200,9 +50094,8 @@
       <c r="P111" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q111" t="str">
-        <f>VLOOKUP(D111,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q111" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="112" spans="1:17" ht="18">
@@ -50253,9 +50146,8 @@
       <c r="P112" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q112" t="str">
-        <f>VLOOKUP(D112,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q112" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="113" spans="1:17" ht="18">
@@ -50308,9 +50200,8 @@
       <c r="P113" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q113" t="str">
-        <f>VLOOKUP(D113,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q113" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="114" spans="1:17" ht="18">
@@ -50361,9 +50252,8 @@
       <c r="P114" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q114" t="str">
-        <f>VLOOKUP(D114,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q114" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="115" spans="1:17" ht="18">
@@ -50414,9 +50304,8 @@
       <c r="P115" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q115" t="str">
-        <f>VLOOKUP(D115,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q115" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="116" spans="1:17" ht="18">
@@ -50467,9 +50356,8 @@
       <c r="P116" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q116" t="str">
-        <f>VLOOKUP(D116,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q116" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="117" spans="1:17" ht="18">
@@ -50520,9 +50408,8 @@
       <c r="P117" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q117" t="str">
-        <f>VLOOKUP(D117,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q117" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="118" spans="1:17" ht="18">
@@ -50573,9 +50460,8 @@
       <c r="P118" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q118" t="str">
-        <f>VLOOKUP(D118,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q118" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="119" spans="1:17" ht="18">
@@ -50626,9 +50512,8 @@
       <c r="P119" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q119" t="str">
-        <f>VLOOKUP(D119,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q119" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="120" spans="1:17" ht="18">
@@ -50679,9 +50564,8 @@
       <c r="P120" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q120" t="str">
-        <f>VLOOKUP(D120,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q120" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="121" spans="1:17" ht="18">
@@ -50732,9 +50616,8 @@
       <c r="P121" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q121" t="str">
-        <f>VLOOKUP(D121,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q121" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="122" spans="1:17" ht="18">
@@ -50785,9 +50668,8 @@
       <c r="P122" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q122" t="str">
-        <f>VLOOKUP(D122,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q122" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="123" spans="1:17" ht="18">
@@ -50838,9 +50720,8 @@
       <c r="P123" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q123" t="str">
-        <f>VLOOKUP(D123,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q123" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="124" spans="1:17" ht="18">
@@ -50891,9 +50772,8 @@
       <c r="P124" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q124" t="str">
-        <f>VLOOKUP(D124,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q124" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="125" spans="1:17" ht="18">
@@ -50944,9 +50824,8 @@
       <c r="P125" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q125" t="str">
-        <f>VLOOKUP(D125,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q125" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="126" spans="1:17" ht="18">
@@ -50997,9 +50876,8 @@
       <c r="P126" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q126" t="str">
-        <f>VLOOKUP(D126,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q126" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="127" spans="1:17" ht="18">
@@ -51050,9 +50928,8 @@
       <c r="P127" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q127" t="str">
-        <f>VLOOKUP(D127,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q127" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="128" spans="1:17" ht="18">
@@ -51103,9 +50980,8 @@
       <c r="P128" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q128" t="str">
-        <f>VLOOKUP(D128,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q128" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="129" spans="1:17" ht="18">
@@ -51156,9 +51032,8 @@
       <c r="P129" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q129" t="str">
-        <f>VLOOKUP(D129,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q129" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="130" spans="1:17" ht="18">
@@ -51209,9 +51084,8 @@
       <c r="P130" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q130" t="str">
-        <f>VLOOKUP(D130,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q130" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="131" spans="1:17" ht="18">
@@ -51262,9 +51136,8 @@
       <c r="P131" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q131" t="str">
-        <f>VLOOKUP(D131,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q131" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="132" spans="1:17" ht="18">
@@ -51315,9 +51188,8 @@
       <c r="P132" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q132" t="str">
-        <f>VLOOKUP(D132,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q132" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="133" spans="1:17" ht="18">
@@ -51368,9 +51240,8 @@
       <c r="P133" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q133" t="str">
-        <f>VLOOKUP(D133,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q133" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="134" spans="1:17" ht="18">
@@ -51423,9 +51294,8 @@
       <c r="P134" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q134" t="str">
-        <f>VLOOKUP(D134,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q134" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="135" spans="1:17" ht="18">
@@ -51476,9 +51346,8 @@
       <c r="P135" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q135" t="str">
-        <f>VLOOKUP(D135,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q135" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="136" spans="1:17" ht="18">
@@ -51529,9 +51398,8 @@
       <c r="P136" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q136" t="str">
-        <f>VLOOKUP(D136,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q136" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="137" spans="1:17" ht="18">
@@ -51582,9 +51450,8 @@
       <c r="P137" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q137" t="str">
-        <f>VLOOKUP(D137,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q137" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="138" spans="1:17" ht="18">
@@ -51635,9 +51502,8 @@
       <c r="P138" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q138" t="str">
-        <f>VLOOKUP(D138,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q138" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="139" spans="1:17" ht="18">
@@ -51688,9 +51554,8 @@
       <c r="P139" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q139" t="str">
-        <f>VLOOKUP(D139,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q139" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="140" spans="1:17" ht="18">
@@ -51741,9 +51606,8 @@
       <c r="P140" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q140" t="str">
-        <f>VLOOKUP(D140,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q140" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="141" spans="1:17" ht="18">
@@ -51794,9 +51658,8 @@
       <c r="P141" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q141" t="str">
-        <f>VLOOKUP(D141,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q141" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="142" spans="1:17" ht="18">
@@ -51847,9 +51710,8 @@
       <c r="P142" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q142" t="str">
-        <f>VLOOKUP(D142,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q142" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="143" spans="1:17" ht="18">
@@ -51900,9 +51762,8 @@
       <c r="P143" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q143" t="str">
-        <f>VLOOKUP(D143,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q143" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="144" spans="1:17" ht="18">
@@ -51953,9 +51814,8 @@
       <c r="P144" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q144" t="str">
-        <f>VLOOKUP(D144,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q144" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="145" spans="1:17" ht="18">
@@ -52006,9 +51866,8 @@
       <c r="P145" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q145" t="str">
-        <f>VLOOKUP(D145,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q145" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="146" spans="1:17" ht="18">
@@ -52059,9 +51918,8 @@
       <c r="P146" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q146" t="str">
-        <f>VLOOKUP(D146,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q146" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="147" spans="1:17" ht="18">
@@ -52112,9 +51970,8 @@
       <c r="P147" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q147" t="str">
-        <f>VLOOKUP(D147,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q147" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="148" spans="1:17" ht="18">
@@ -52165,9 +52022,8 @@
       <c r="P148" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q148" t="str">
-        <f>VLOOKUP(D148,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q148" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="149" spans="1:17" ht="18">
@@ -52218,9 +52074,8 @@
       <c r="P149" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q149" t="str">
-        <f>VLOOKUP(D149,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q149" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="150" spans="1:17" ht="18">
@@ -52271,9 +52126,8 @@
       <c r="P150" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q150" t="str">
-        <f>VLOOKUP(D150,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q150" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="151" spans="1:17" ht="18">
@@ -52324,9 +52178,8 @@
       <c r="P151" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q151" t="str">
-        <f>VLOOKUP(D151,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q151" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="152" spans="1:17" ht="18">
@@ -52377,9 +52230,8 @@
       <c r="P152" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q152" t="str">
-        <f>VLOOKUP(D152,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q152" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="153" spans="1:17" ht="18">
@@ -52430,9 +52282,8 @@
       <c r="P153" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q153" t="str">
-        <f>VLOOKUP(D153,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q153" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="154" spans="1:17" ht="18">
@@ -52483,9 +52334,8 @@
       <c r="P154" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q154" t="str">
-        <f>VLOOKUP(D154,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q154" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="155" spans="1:17" ht="18">
@@ -52536,9 +52386,8 @@
       <c r="P155" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q155" t="str">
-        <f>VLOOKUP(D155,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q155" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="156" spans="1:17" ht="18">
@@ -52589,9 +52438,8 @@
       <c r="P156" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q156" t="str">
-        <f>VLOOKUP(D156,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q156" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="157" spans="1:17" ht="18">
@@ -52642,9 +52490,8 @@
       <c r="P157" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q157" t="str">
-        <f>VLOOKUP(D157,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q157" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="158" spans="1:17" ht="18">
@@ -52695,9 +52542,8 @@
       <c r="P158" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q158" t="str">
-        <f>VLOOKUP(D158,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q158" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="159" spans="1:17" ht="18">
@@ -52748,9 +52594,8 @@
       <c r="P159" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q159" t="str">
-        <f>VLOOKUP(D159,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q159" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="160" spans="1:17" ht="18">
@@ -52801,9 +52646,8 @@
       <c r="P160" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q160" t="str">
-        <f>VLOOKUP(D160,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q160" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="161" spans="1:17" ht="18">
@@ -52854,9 +52698,8 @@
       <c r="P161" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q161" t="str">
-        <f>VLOOKUP(D161,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q161" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="162" spans="1:17" ht="18">
@@ -52907,9 +52750,8 @@
       <c r="P162" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q162" t="str">
-        <f>VLOOKUP(D162,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q162" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="163" spans="1:17" ht="18">
@@ -52960,9 +52802,8 @@
       <c r="P163" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q163" t="str">
-        <f>VLOOKUP(D163,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q163" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="164" spans="1:17" ht="18">
@@ -53013,9 +52854,8 @@
       <c r="P164" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q164" t="str">
-        <f>VLOOKUP(D164,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q164" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="165" spans="1:17" ht="18">
@@ -53066,9 +52906,8 @@
       <c r="P165" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q165" t="str">
-        <f>VLOOKUP(D165,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q165" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="166" spans="1:17" ht="18">
@@ -53119,9 +52958,8 @@
       <c r="P166" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q166" t="str">
-        <f>VLOOKUP(D166,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q166" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="167" spans="1:17" ht="18">
@@ -53172,9 +53010,8 @@
       <c r="P167" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q167" t="str">
-        <f>VLOOKUP(D167,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q167" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="168" spans="1:17" ht="18">
@@ -53225,9 +53062,8 @@
       <c r="P168" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q168" t="str">
-        <f>VLOOKUP(D168,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q168" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="169" spans="1:17" ht="18">
@@ -53278,9 +53114,8 @@
       <c r="P169" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q169" t="str">
-        <f>VLOOKUP(D169,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q169" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="170" spans="1:17" ht="18">
@@ -53331,9 +53166,8 @@
       <c r="P170" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q170" t="str">
-        <f>VLOOKUP(D170,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q170" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="171" spans="1:17" ht="18">
@@ -53384,9 +53218,8 @@
       <c r="P171" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q171" t="str">
-        <f>VLOOKUP(D171,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q171" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="172" spans="1:17" ht="18">
@@ -53437,9 +53270,8 @@
       <c r="P172" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q172" t="str">
-        <f>VLOOKUP(D172,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q172" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="173" spans="1:17" ht="18">
@@ -53490,9 +53322,8 @@
       <c r="P173" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q173" t="str">
-        <f>VLOOKUP(D173,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q173" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="174" spans="1:17" ht="18">
@@ -53543,9 +53374,8 @@
       <c r="P174" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q174" t="str">
-        <f>VLOOKUP(D174,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q174" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="175" spans="1:17" ht="18">
@@ -53596,9 +53426,8 @@
       <c r="P175" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q175" t="str">
-        <f>VLOOKUP(D175,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q175" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="176" spans="1:17" ht="18">
@@ -53643,9 +53472,8 @@
       <c r="P176" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q176" t="str">
-        <f>VLOOKUP(D176,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q176" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="177" spans="1:17" ht="18">
@@ -53696,9 +53524,8 @@
       <c r="P177" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q177" t="str">
-        <f>VLOOKUP(D177,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q177" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="178" spans="1:17" ht="18">
@@ -53747,9 +53574,8 @@
       <c r="P178" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q178" t="str">
-        <f>VLOOKUP(D178,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q178" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="179" spans="1:17" ht="18">
@@ -53800,9 +53626,8 @@
       <c r="P179" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q179" t="str">
-        <f>VLOOKUP(D179,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q179" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="180" spans="1:17" ht="18">
@@ -53853,9 +53678,8 @@
       <c r="P180" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q180" t="str">
-        <f>VLOOKUP(D180,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q180" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="181" spans="1:17" ht="18">
@@ -53906,9 +53730,8 @@
       <c r="P181" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q181" t="str">
-        <f>VLOOKUP(D181,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q181" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="182" spans="1:17" ht="18">
@@ -53959,9 +53782,8 @@
       <c r="P182" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q182" t="str">
-        <f>VLOOKUP(D182,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q182" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="183" spans="1:17" ht="18">
@@ -54012,9 +53834,8 @@
       <c r="P183" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q183" t="str">
-        <f>VLOOKUP(D183,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q183" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="184" spans="1:17" ht="18">
@@ -54065,9 +53886,8 @@
       <c r="P184" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q184" t="str">
-        <f>VLOOKUP(D184,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q184" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="185" spans="1:17" ht="18">
@@ -54118,9 +53938,8 @@
       <c r="P185" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q185" t="str">
-        <f>VLOOKUP(D185,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q185" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="186" spans="1:17" ht="18">
@@ -54169,9 +53988,8 @@
       <c r="P186" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q186" t="str">
-        <f>VLOOKUP(D186,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q186" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="187" spans="1:17" ht="18">
@@ -54222,9 +54040,8 @@
       <c r="P187" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q187" t="str">
-        <f>VLOOKUP(D187,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q187" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="188" spans="1:17" ht="18">
@@ -54275,9 +54092,8 @@
       <c r="P188" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q188" t="str">
-        <f>VLOOKUP(D188,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q188" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="189" spans="1:17" ht="18">
@@ -54328,9 +54144,8 @@
       <c r="P189" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q189" t="str">
-        <f>VLOOKUP(D189,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q189" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="190" spans="1:17" ht="18">
@@ -54381,9 +54196,8 @@
       <c r="P190" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q190" t="str">
-        <f>VLOOKUP(D190,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q190" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="191" spans="1:17" ht="18">
@@ -54434,9 +54248,8 @@
       <c r="P191" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q191" t="str">
-        <f>VLOOKUP(D191,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q191" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="192" spans="1:17" ht="18">
@@ -54487,9 +54300,8 @@
       <c r="P192" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q192" t="str">
-        <f>VLOOKUP(D192,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q192" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="193" spans="1:17" ht="18">
@@ -54538,9 +54350,8 @@
       <c r="P193" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q193" t="str">
-        <f>VLOOKUP(D193,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q193" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="194" spans="1:17" ht="18">
@@ -54589,9 +54400,8 @@
       <c r="P194" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q194" t="str">
-        <f>VLOOKUP(D194,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q194" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="195" spans="1:17" ht="18">
@@ -54638,9 +54448,8 @@
       <c r="P195" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q195" t="str">
-        <f>VLOOKUP(D195,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q195" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="196" spans="1:17" ht="18">
@@ -54691,9 +54500,8 @@
       <c r="P196" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q196" t="str">
-        <f>VLOOKUP(D196,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q196" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="197" spans="1:17" ht="18">
@@ -54738,9 +54546,8 @@
       <c r="P197" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q197" t="str">
-        <f>VLOOKUP(D197,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q197" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="198" spans="1:17" ht="18">
@@ -54791,9 +54598,8 @@
       <c r="P198" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q198" t="str">
-        <f>VLOOKUP(D198,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q198" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="199" spans="1:17" ht="18">
@@ -54844,9 +54650,8 @@
       <c r="P199" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q199" t="str">
-        <f>VLOOKUP(D199,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q199" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="200" spans="1:17" ht="18">
@@ -54897,9 +54702,8 @@
       <c r="P200" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q200" t="str">
-        <f>VLOOKUP(D200,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q200" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="201" spans="1:17" ht="18">
@@ -54950,9 +54754,8 @@
       <c r="P201" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q201" t="str">
-        <f>VLOOKUP(D201,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q201" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="202" spans="1:17" ht="18">
@@ -55003,9 +54806,8 @@
       <c r="P202" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q202" t="str">
-        <f>VLOOKUP(D202,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q202" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="203" spans="1:17" ht="18">
@@ -55056,9 +54858,8 @@
       <c r="P203" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q203" t="str">
-        <f>VLOOKUP(D203,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q203" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="204" spans="1:17" ht="18">
@@ -55103,9 +54904,8 @@
       <c r="P204" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q204" t="str">
-        <f>VLOOKUP(D204,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q204" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="205" spans="1:17" ht="18">
@@ -55156,9 +54956,8 @@
       <c r="P205" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q205" t="str">
-        <f>VLOOKUP(D205,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q205" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="206" spans="1:17" ht="18">
@@ -55209,9 +55008,8 @@
       <c r="P206" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q206" t="str">
-        <f>VLOOKUP(D206,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q206" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="207" spans="1:17" ht="18">
@@ -55262,9 +55060,8 @@
       <c r="P207" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q207" t="str">
-        <f>VLOOKUP(D207,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q207" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="208" spans="1:17" ht="18">
@@ -55315,9 +55112,8 @@
       <c r="P208" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q208" t="str">
-        <f>VLOOKUP(D208,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q208" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="209" spans="1:17" ht="18">
@@ -55368,9 +55164,8 @@
       <c r="P209" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q209" t="str">
-        <f>VLOOKUP(D209,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q209" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="210" spans="1:17" ht="18">
@@ -55421,9 +55216,8 @@
       <c r="P210" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q210" t="str">
-        <f>VLOOKUP(D210,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q210" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="211" spans="1:17" ht="18">
@@ -55474,9 +55268,8 @@
       <c r="P211" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q211" t="str">
-        <f>VLOOKUP(D211,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q211" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="212" spans="1:17" ht="18">
@@ -55527,9 +55320,8 @@
       <c r="P212" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q212" t="str">
-        <f>VLOOKUP(D212,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q212" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="213" spans="1:17" ht="18">
@@ -55580,9 +55372,8 @@
       <c r="P213" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q213" t="str">
-        <f>VLOOKUP(D213,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q213" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="214" spans="1:17" ht="18">
@@ -55633,9 +55424,8 @@
       <c r="P214" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q214" t="str">
-        <f>VLOOKUP(D214,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q214" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="215" spans="1:17" ht="18">
@@ -55686,9 +55476,8 @@
       <c r="P215" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q215" t="str">
-        <f>VLOOKUP(D215,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q215" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="216" spans="1:17" ht="18">
@@ -55739,9 +55528,8 @@
       <c r="P216" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q216" t="str">
-        <f>VLOOKUP(D216,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q216" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="217" spans="1:17" ht="18">
@@ -55792,9 +55580,8 @@
       <c r="P217" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q217" t="str">
-        <f>VLOOKUP(D217,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q217" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="218" spans="1:17" ht="18">
@@ -55845,9 +55632,8 @@
       <c r="P218" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q218" t="str">
-        <f>VLOOKUP(D218,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q218" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="219" spans="1:17" ht="18">
@@ -55898,9 +55684,8 @@
       <c r="P219" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q219" t="str">
-        <f>VLOOKUP(D219,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q219" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="220" spans="1:17" ht="18">
@@ -55951,9 +55736,8 @@
       <c r="P220" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q220" t="str">
-        <f>VLOOKUP(D220,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q220" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="221" spans="1:17" ht="18">
@@ -56004,9 +55788,8 @@
       <c r="P221" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q221" t="str">
-        <f>VLOOKUP(D221,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q221" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="222" spans="1:17" ht="18">
@@ -56057,9 +55840,8 @@
       <c r="P222" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q222" t="str">
-        <f>VLOOKUP(D222,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q222" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="223" spans="1:17" ht="18">
@@ -56110,9 +55892,8 @@
       <c r="P223" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q223" t="str">
-        <f>VLOOKUP(D223,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q223" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="224" spans="1:17" ht="18">
@@ -56163,9 +55944,8 @@
       <c r="P224" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q224" t="str">
-        <f>VLOOKUP(D224,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q224" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="225" spans="1:17" ht="18">
@@ -56216,9 +55996,8 @@
       <c r="P225" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q225" t="str">
-        <f>VLOOKUP(D225,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q225" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="226" spans="1:17" ht="18">
@@ -56269,9 +56048,8 @@
       <c r="P226" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q226" t="str">
-        <f>VLOOKUP(D226,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q226" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="227" spans="1:17" ht="18">
@@ -56322,9 +56100,8 @@
       <c r="P227" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q227" t="str">
-        <f>VLOOKUP(D227,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q227" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="228" spans="1:17" ht="18">
@@ -56375,9 +56152,8 @@
       <c r="P228" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q228" t="str">
-        <f>VLOOKUP(D228,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q228" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="229" spans="1:17" ht="18">
@@ -56428,9 +56204,8 @@
       <c r="P229" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q229" t="str">
-        <f>VLOOKUP(D229,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q229" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="230" spans="1:17" ht="18">
@@ -56481,9 +56256,8 @@
       <c r="P230" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q230" t="str">
-        <f>VLOOKUP(D230,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q230" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="231" spans="1:17" ht="18">
@@ -56528,9 +56302,8 @@
       <c r="P231" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q231" t="str">
-        <f>VLOOKUP(D231,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q231" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="232" spans="1:17" ht="18">
@@ -56579,9 +56352,8 @@
       <c r="P232" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q232" t="str">
-        <f>VLOOKUP(D232,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q232" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="233" spans="1:17" ht="18">
@@ -56632,9 +56404,8 @@
       <c r="P233" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q233" t="str">
-        <f>VLOOKUP(D233,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q233" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="234" spans="1:17" ht="18">
@@ -56679,9 +56450,8 @@
       <c r="P234" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q234" t="str">
-        <f>VLOOKUP(D234,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q234" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="235" spans="1:17" ht="18">
@@ -56730,9 +56500,8 @@
       <c r="P235" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q235" t="str">
-        <f>VLOOKUP(D235,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q235" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="236" spans="1:17" ht="18">
@@ -56779,9 +56548,8 @@
       <c r="P236" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q236" t="str">
-        <f>VLOOKUP(D236,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q236" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="237" spans="1:17" ht="18">
@@ -56832,9 +56600,8 @@
       <c r="P237" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q237" t="str">
-        <f>VLOOKUP(D237,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q237" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="238" spans="1:17" ht="18">
@@ -56885,9 +56652,8 @@
       <c r="P238" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q238" t="str">
-        <f>VLOOKUP(D238,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q238" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="239" spans="1:17" ht="18">
@@ -56938,9 +56704,8 @@
       <c r="P239" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q239" t="str">
-        <f>VLOOKUP(D239,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q239" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="240" spans="1:17" ht="18">
@@ -56989,9 +56754,8 @@
       <c r="P240" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q240" t="str">
-        <f>VLOOKUP(D240,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q240" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="241" spans="1:17" ht="18">
@@ -57040,9 +56804,8 @@
       <c r="P241" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q241" t="str">
-        <f>VLOOKUP(D241,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q241" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="242" spans="1:17" ht="18">
@@ -57089,9 +56852,8 @@
       <c r="P242" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q242" t="str">
-        <f>VLOOKUP(D242,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q242" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="243" spans="1:17" ht="18">
@@ -57142,9 +56904,8 @@
       <c r="P243" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q243" t="str">
-        <f>VLOOKUP(D243,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q243" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="244" spans="1:17" ht="18">
@@ -57189,9 +56950,8 @@
       <c r="P244" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q244" t="str">
-        <f>VLOOKUP(D244,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q244" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="245" spans="1:17" ht="18">
@@ -57242,9 +57002,8 @@
       <c r="P245" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q245" t="str">
-        <f>VLOOKUP(D245,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q245" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="246" spans="1:17" ht="18">
@@ -57295,9 +57054,8 @@
       <c r="P246" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q246" t="str">
-        <f>VLOOKUP(D246,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q246" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="247" spans="1:17" ht="18">
@@ -57348,9 +57106,8 @@
       <c r="P247" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q247" t="str">
-        <f>VLOOKUP(D247,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q247" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="248" spans="1:17" ht="18">
@@ -57397,9 +57154,8 @@
       <c r="P248" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q248" t="str">
-        <f>VLOOKUP(D248,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q248" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="249" spans="1:17" ht="18">
@@ -57448,9 +57204,8 @@
       <c r="P249" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q249" t="str">
-        <f>VLOOKUP(D249,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q249" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="250" spans="1:17" ht="18">
@@ -57499,9 +57254,8 @@
       <c r="P250" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q250" t="str">
-        <f>VLOOKUP(D250,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q250" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="251" spans="1:17" ht="18">
@@ -57546,9 +57300,8 @@
       <c r="P251" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q251" t="str">
-        <f>VLOOKUP(D251,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q251" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="252" spans="1:17" ht="18">
@@ -57599,9 +57352,8 @@
       <c r="P252" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q252" t="str">
-        <f>VLOOKUP(D252,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q252" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="253" spans="1:17" ht="18">
@@ -57652,9 +57404,8 @@
       <c r="P253" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q253" t="str">
-        <f>VLOOKUP(D253,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q253" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="254" spans="1:17" ht="18">
@@ -57699,9 +57450,8 @@
       <c r="P254" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q254" t="str">
-        <f>VLOOKUP(D254,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q254" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="255" spans="1:17" ht="18">
@@ -57750,9 +57500,8 @@
       <c r="P255" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q255" t="str">
-        <f>VLOOKUP(D255,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q255" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="256" spans="1:17" ht="18">
@@ -57801,9 +57550,8 @@
       <c r="P256" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q256" t="str">
-        <f>VLOOKUP(D256,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q256" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="257" spans="1:17" ht="18">
@@ -57854,9 +57602,8 @@
       <c r="P257" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q257" t="str">
-        <f>VLOOKUP(D257,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q257" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="258" spans="1:17" ht="18">
@@ -57905,9 +57652,8 @@
       <c r="P258" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q258" t="str">
-        <f>VLOOKUP(D258,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q258" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="259" spans="1:17" ht="18">
@@ -57956,9 +57702,8 @@
       <c r="P259" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q259" t="str">
-        <f>VLOOKUP(D259,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q259" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="260" spans="1:17" ht="18">
@@ -58009,9 +57754,8 @@
       <c r="P260" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q260" t="str">
-        <f>VLOOKUP(D260,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q260" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="261" spans="1:17" ht="18">
@@ -58060,9 +57804,8 @@
       <c r="P261" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q261" t="str">
-        <f>VLOOKUP(D261,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q261" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="262" spans="1:17" ht="18">
@@ -58113,9 +57856,8 @@
       <c r="P262" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q262" t="str">
-        <f>VLOOKUP(D262,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q262" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="263" spans="1:17" ht="18">
@@ -58166,9 +57908,8 @@
       <c r="P263" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q263" t="str">
-        <f>VLOOKUP(D263,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q263" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="264" spans="1:17" ht="18">
@@ -58219,9 +57960,8 @@
       <c r="P264" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q264" t="str">
-        <f>VLOOKUP(D264,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q264" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="265" spans="1:17" ht="18">
@@ -58270,9 +58010,8 @@
       <c r="P265" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q265" t="str">
-        <f>VLOOKUP(D265,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q265" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="266" spans="1:17" ht="18">
@@ -58321,9 +58060,8 @@
       <c r="P266" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q266" t="str">
-        <f>VLOOKUP(D266,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q266" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="267" spans="1:17" ht="18">
@@ -58374,9 +58112,8 @@
       <c r="P267" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q267" t="str">
-        <f>VLOOKUP(D267,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q267" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="268" spans="1:17" ht="18">
@@ -58427,9 +58164,8 @@
       <c r="P268" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q268" t="str">
-        <f>VLOOKUP(D268,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q268" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="269" spans="1:17" ht="18">
@@ -58480,9 +58216,8 @@
       <c r="P269" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q269" t="str">
-        <f>VLOOKUP(D269,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q269" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="270" spans="1:17" ht="18">
@@ -58533,9 +58268,8 @@
       <c r="P270" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q270" t="str">
-        <f>VLOOKUP(D270,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q270" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="271" spans="1:17" ht="18">
@@ -58578,9 +58312,8 @@
       <c r="P271" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q271" t="str">
-        <f>VLOOKUP(D271,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q271" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="272" spans="1:17" ht="18">
@@ -58631,9 +58364,8 @@
       <c r="P272" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q272" t="str">
-        <f>VLOOKUP(D272,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q272" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="273" spans="1:17" ht="18">
@@ -58676,9 +58408,8 @@
       <c r="P273" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q273" t="str">
-        <f>VLOOKUP(D273,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q273" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="274" spans="1:17" ht="18">
@@ -58726,9 +58457,8 @@
       <c r="P274" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q274" t="str">
-        <f>VLOOKUP(D274,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A5, B1, B2, B5, B8, B9, B10, B11, B14, B15, B15, C9, D16</v>
+      <c r="Q274" t="s">
+        <v>1357</v>
       </c>
     </row>
     <row r="275" spans="1:17" ht="18">
@@ -58779,9 +58509,8 @@
       <c r="P275" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q275" t="str">
-        <f>VLOOKUP(D275,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A5, B1, B2, B5, B8, B9, B10, B11, B14, B15, B15, C9, D16</v>
+      <c r="Q275" t="s">
+        <v>1357</v>
       </c>
     </row>
     <row r="276" spans="1:17" ht="18">
@@ -58832,9 +58561,8 @@
       <c r="P276" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q276" t="str">
-        <f>VLOOKUP(D276,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A5, B1, B2, B5, B8, B9, B10, B11, B14, B15, B15, C9, D16</v>
+      <c r="Q276" t="s">
+        <v>1357</v>
       </c>
     </row>
     <row r="277" spans="1:17" ht="18">
@@ -58879,9 +58607,8 @@
       <c r="P277" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q277" t="str">
-        <f>VLOOKUP(D277,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A5, B1, B2, B5, B8, B9, B10, B11, B14, B15, B15, C9, D16</v>
+      <c r="Q277" t="s">
+        <v>1357</v>
       </c>
     </row>
     <row r="278" spans="1:17" ht="18">
@@ -58932,9 +58659,8 @@
       <c r="P278" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q278" t="str">
-        <f>VLOOKUP(D278,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A5, B1, B2, B5, B8, B9, B10, B11, B14, B15, B15, C9, D16</v>
+      <c r="Q278" t="s">
+        <v>1357</v>
       </c>
     </row>
     <row r="279" spans="1:17" ht="18">
@@ -58985,9 +58711,8 @@
       <c r="P279" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q279" t="str">
-        <f>VLOOKUP(D279,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A5, B1, B2, B5, B8, B9, B10, B11, B14, B15, B15, C9, D16</v>
+      <c r="Q279" t="s">
+        <v>1357</v>
       </c>
     </row>
     <row r="280" spans="1:17" ht="18">
@@ -59038,9 +58763,8 @@
       <c r="P280" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q280" t="str">
-        <f>VLOOKUP(D280,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A5, B1, B2, B5, B8, B9, B10, B11, B14, B15, B15, C9, D16</v>
+      <c r="Q280" t="s">
+        <v>1357</v>
       </c>
     </row>
     <row r="281" spans="1:17" ht="18">
@@ -59091,9 +58815,8 @@
       <c r="P281" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q281" t="str">
-        <f>VLOOKUP(D281,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A5, B1, B2, B5, B8, B9, B10, B11, B14, B15, B15, C9, D16</v>
+      <c r="Q281" t="s">
+        <v>1357</v>
       </c>
     </row>
     <row r="282" spans="1:17" ht="18">
@@ -59144,9 +58867,8 @@
       <c r="P282" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q282" t="str">
-        <f>VLOOKUP(D282,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A5, B1, B2, B5, B8, B9, B10, B11, B14, B15, B15, C9, D16</v>
+      <c r="Q282" t="s">
+        <v>1357</v>
       </c>
     </row>
     <row r="283" spans="1:17" ht="18">
@@ -59197,9 +58919,8 @@
       <c r="P283" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q283" t="str">
-        <f>VLOOKUP(D283,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A5, B1, B2, B5, B8, B9, B10, B11, B14, B15, B15, C9, D16</v>
+      <c r="Q283" t="s">
+        <v>1357</v>
       </c>
     </row>
     <row r="284" spans="1:17" ht="18">
@@ -59250,9 +58971,8 @@
       <c r="P284" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q284" t="str">
-        <f>VLOOKUP(D284,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A5, B1, B2, B5, B8, B9, B10, B11, B14, B15, B15, C9, D16</v>
+      <c r="Q284" t="s">
+        <v>1357</v>
       </c>
     </row>
     <row r="285" spans="1:17" ht="18">
@@ -59303,9 +59023,8 @@
       <c r="P285" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q285" t="str">
-        <f>VLOOKUP(D285,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A5, B1, B2, B5, B8, B9, B10, B11, B14, B15, B15, C9, D16</v>
+      <c r="Q285" t="s">
+        <v>1357</v>
       </c>
     </row>
     <row r="286" spans="1:17" ht="18">
@@ -59356,9 +59075,8 @@
       <c r="P286" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q286" t="str">
-        <f>VLOOKUP(D286,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A5, B1, B2, B5, B8, B9, B10, B11, B14, B15, B15, C9, D16</v>
+      <c r="Q286" t="s">
+        <v>1357</v>
       </c>
     </row>
     <row r="287" spans="1:17" ht="18">
@@ -59409,9 +59127,8 @@
       <c r="P287" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q287" t="str">
-        <f>VLOOKUP(D287,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A5, B1, B2, B5, B8, B9, B10, B11, B14, B15, B15, C9, D16</v>
+      <c r="Q287" t="s">
+        <v>1357</v>
       </c>
     </row>
     <row r="288" spans="1:17" ht="18">
@@ -59462,9 +59179,8 @@
       <c r="P288" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q288" t="str">
-        <f>VLOOKUP(D288,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A5, B1, B2, B5, B8, B9, B10, B11, B14, B15, B15, C9, D16</v>
+      <c r="Q288" t="s">
+        <v>1357</v>
       </c>
     </row>
     <row r="289" spans="1:17" ht="18">
@@ -59515,9 +59231,8 @@
       <c r="P289" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q289" t="str">
-        <f>VLOOKUP(D289,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A5, B1, B2, B5, B8, B9, B10, B11, B14, B15, B15, C9, D16</v>
+      <c r="Q289" t="s">
+        <v>1357</v>
       </c>
     </row>
     <row r="290" spans="1:17" ht="18">
@@ -59568,9 +59283,8 @@
       <c r="P290" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q290" t="str">
-        <f>VLOOKUP(D290,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q290" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="291" spans="1:17" ht="18">
@@ -59621,9 +59335,8 @@
       <c r="P291" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q291" t="str">
-        <f>VLOOKUP(D291,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q291" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="292" spans="1:17" ht="18">
@@ -59674,9 +59387,8 @@
       <c r="P292" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q292" t="str">
-        <f>VLOOKUP(D292,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q292" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="293" spans="1:17" ht="18">
@@ -59727,9 +59439,8 @@
       <c r="P293" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q293" t="str">
-        <f>VLOOKUP(D293,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q293" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="294" spans="1:17" ht="18">
@@ -59776,9 +59487,8 @@
       <c r="P294" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q294" t="str">
-        <f>VLOOKUP(D294,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q294" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="295" spans="1:17" ht="18">
@@ -59829,9 +59539,8 @@
       <c r="P295" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q295" t="str">
-        <f>VLOOKUP(D295,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q295" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="296" spans="1:17" ht="18">
@@ -59880,9 +59589,8 @@
       <c r="P296" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q296" t="str">
-        <f>VLOOKUP(D296,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q296" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="297" spans="1:17" ht="18">
@@ -59931,9 +59639,8 @@
       <c r="P297" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q297" t="str">
-        <f>VLOOKUP(D297,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q297" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="298" spans="1:17" ht="18">
@@ -59982,9 +59689,8 @@
       <c r="P298" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q298" t="str">
-        <f>VLOOKUP(D298,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q298" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="299" spans="1:17" ht="18">
@@ -60029,9 +59735,8 @@
       <c r="P299" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q299" t="str">
-        <f>VLOOKUP(D299,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q299" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="300" spans="1:17" ht="18">
@@ -60082,9 +59787,8 @@
       <c r="P300" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q300" t="str">
-        <f>VLOOKUP(D300,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q300" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="301" spans="1:17" ht="18">
@@ -60135,9 +59839,8 @@
       <c r="P301" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q301" t="str">
-        <f>VLOOKUP(D301,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q301" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="302" spans="1:17" ht="18">
@@ -60188,9 +59891,8 @@
       <c r="P302" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q302" t="str">
-        <f>VLOOKUP(D302,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q302" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="303" spans="1:17" ht="18">
@@ -60235,9 +59937,8 @@
       <c r="P303" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q303" t="str">
-        <f>VLOOKUP(D303,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q303" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="304" spans="1:17" ht="18">
@@ -60288,9 +59989,8 @@
       <c r="P304" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q304" t="str">
-        <f>VLOOKUP(D304,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q304" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="305" spans="1:17" ht="18">
@@ -60339,9 +60039,8 @@
       <c r="P305" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q305" t="str">
-        <f>VLOOKUP(D305,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q305" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="306" spans="1:17" ht="18">
@@ -60390,9 +60089,8 @@
       <c r="P306" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q306" t="str">
-        <f>VLOOKUP(D306,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q306" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="307" spans="1:17" ht="18">
@@ -60443,9 +60141,8 @@
       <c r="P307" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q307" t="str">
-        <f>VLOOKUP(D307,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q307" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="308" spans="1:17" ht="18">
@@ -60498,9 +60195,8 @@
       <c r="P308" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q308" t="str">
-        <f>VLOOKUP(D308,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q308" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="309" spans="1:17" ht="18">
@@ -60547,9 +60243,8 @@
       <c r="P309" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q309" t="str">
-        <f>VLOOKUP(D309,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q309" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="310" spans="1:17" ht="18">
@@ -60600,9 +60295,8 @@
       <c r="P310" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q310" t="str">
-        <f>VLOOKUP(D310,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q310" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="311" spans="1:17" ht="18">
@@ -60651,9 +60345,8 @@
       <c r="P311" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q311" t="str">
-        <f>VLOOKUP(D311,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q311" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="312" spans="1:17" ht="18">
@@ -60698,9 +60391,8 @@
       <c r="P312" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q312" t="str">
-        <f>VLOOKUP(D312,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q312" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="313" spans="1:17" ht="18">
@@ -60745,9 +60437,8 @@
       <c r="P313" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q313" t="str">
-        <f>VLOOKUP(D313,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q313" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="314" spans="1:17" ht="18">
@@ -60794,9 +60485,8 @@
       <c r="P314" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q314" t="str">
-        <f>VLOOKUP(D314,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q314" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="315" spans="1:17" ht="18">
@@ -60847,9 +60537,8 @@
       <c r="P315" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q315" t="str">
-        <f>VLOOKUP(D315,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q315" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="316" spans="1:17" ht="18">
@@ -60898,9 +60587,8 @@
       <c r="P316" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q316" t="str">
-        <f>VLOOKUP(D316,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q316" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="317" spans="1:17" ht="18">
@@ -60949,9 +60637,8 @@
       <c r="P317" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q317" t="str">
-        <f>VLOOKUP(D317,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q317" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="318" spans="1:17" ht="18">
@@ -60998,9 +60685,8 @@
       <c r="P318" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q318" t="str">
-        <f>VLOOKUP(D318,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q318" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="319" spans="1:17" ht="18">
@@ -61051,9 +60737,8 @@
       <c r="P319" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q319" t="str">
-        <f>VLOOKUP(D319,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q319" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="320" spans="1:17" ht="18">
@@ -61102,9 +60787,8 @@
       <c r="P320" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q320" t="str">
-        <f>VLOOKUP(D320,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q320" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="321" spans="1:17" ht="18">
@@ -61153,9 +60837,8 @@
       <c r="P321" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q321" t="str">
-        <f>VLOOKUP(D321,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q321" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="322" spans="1:17" ht="18">
@@ -61202,9 +60885,8 @@
       <c r="P322" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q322" t="str">
-        <f>VLOOKUP(D322,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q322" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="323" spans="1:17" ht="18">
@@ -61253,9 +60935,8 @@
       <c r="P323" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q323" t="str">
-        <f>VLOOKUP(D323,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q323" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="324" spans="1:17" ht="18">
@@ -61304,9 +60985,8 @@
       <c r="P324" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q324" t="str">
-        <f>VLOOKUP(D324,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q324" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="325" spans="1:17" ht="18">
@@ -61355,9 +61035,8 @@
       <c r="P325" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q325" t="str">
-        <f>VLOOKUP(D325,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q325" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="326" spans="1:17" ht="18">
@@ -61402,9 +61081,8 @@
       <c r="P326" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q326" t="str">
-        <f>VLOOKUP(D326,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q326" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="327" spans="1:17" ht="18">
@@ -61453,9 +61131,8 @@
       <c r="P327" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q327" t="str">
-        <f>VLOOKUP(D327,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q327" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="328" spans="1:17" ht="18">
@@ -61506,9 +61183,8 @@
       <c r="P328" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q328" t="str">
-        <f>VLOOKUP(D328,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q328" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="329" spans="1:17" ht="18">
@@ -61559,9 +61235,8 @@
       <c r="P329" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q329" t="str">
-        <f>VLOOKUP(D329,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q329" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="330" spans="1:17" ht="18">
@@ -61612,9 +61287,8 @@
       <c r="P330" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q330" t="str">
-        <f>VLOOKUP(D330,'rak2'!$A$1:$B$6, 2)</f>
-        <v xml:space="preserve"> </v>
+      <c r="Q330" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="331" spans="1:17" ht="18">
@@ -61661,9 +61335,8 @@
       <c r="P331" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q331" t="str">
-        <f>VLOOKUP(D331,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q331" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="332" spans="1:17" ht="18">
@@ -61710,9 +61383,8 @@
       <c r="P332" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q332" t="str">
-        <f>VLOOKUP(D332,'rak2'!$A$1:$B$6, 2)</f>
-        <v>A9, A10, A15, A20, C4, C6, C12, D1, D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D17, D18, D19, D20, E1, E2, E3, E4, E5, E6, E7, E8, E9, E10, E11, E12, E14, E15, E16</v>
+      <c r="Q332" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="333" spans="1:17" ht="18">
@@ -61759,9 +61431,8 @@
       <c r="P333" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q333" t="str">
-        <f>VLOOKUP(D333,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q333" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="334" spans="1:17" ht="18">
@@ -61804,9 +61475,8 @@
       <c r="P334" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q334" t="str">
-        <f>VLOOKUP(D334,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q334" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="335" spans="1:17" ht="18">
@@ -61849,9 +61519,8 @@
       <c r="P335" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q335" t="str">
-        <f>VLOOKUP(D335,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q335" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="336" spans="1:17" ht="18">
@@ -61894,9 +61563,8 @@
       <c r="P336" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q336" t="str">
-        <f>VLOOKUP(D336,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q336" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="337" spans="1:17" ht="18">
@@ -61949,9 +61617,8 @@
       <c r="P337" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q337" t="str">
-        <f>VLOOKUP(D337,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q337" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="338" spans="1:17" ht="18">
@@ -62002,9 +61669,8 @@
       <c r="P338" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q338" t="str">
-        <f>VLOOKUP(D338,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q338" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="339" spans="1:17" ht="18">
@@ -62051,9 +61717,8 @@
       <c r="P339" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q339" t="str">
-        <f>VLOOKUP(D339,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q339" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="340" spans="1:17" ht="18">
@@ -62102,9 +61767,8 @@
       <c r="P340" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q340" t="str">
-        <f>VLOOKUP(D340,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q340" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="341" spans="1:17" ht="18">
@@ -62155,9 +61819,8 @@
       <c r="P341" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q341" t="str">
-        <f>VLOOKUP(D341,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q341" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="342" spans="1:17" ht="18">
@@ -62208,9 +61871,8 @@
       <c r="P342" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q342" t="str">
-        <f>VLOOKUP(D342,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q342" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="343" spans="1:17" ht="18">
@@ -62259,9 +61921,8 @@
       <c r="P343" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q343" t="str">
-        <f>VLOOKUP(D343,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q343" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="344" spans="1:17" ht="18">
@@ -62310,9 +61971,8 @@
       <c r="P344" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q344" t="str">
-        <f>VLOOKUP(D344,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q344" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="345" spans="1:17" ht="18">
@@ -62363,9 +62023,8 @@
       <c r="P345" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q345" t="str">
-        <f>VLOOKUP(D345,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q345" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="346" spans="1:17" ht="18">
@@ -62415,9 +62074,8 @@
       <c r="P346" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q346" t="str">
-        <f>VLOOKUP(D346,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q346" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="347" spans="1:17" ht="18">
@@ -62467,9 +62125,8 @@
       <c r="P347" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q347" t="str">
-        <f>VLOOKUP(D347,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q347" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="348" spans="1:17" ht="18">
@@ -62517,9 +62174,8 @@
       <c r="P348" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q348" t="str">
-        <f>VLOOKUP(D348,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q348" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="349" spans="1:17" ht="18">
@@ -62570,9 +62226,8 @@
       <c r="P349" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q349" t="str">
-        <f>VLOOKUP(D349,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q349" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="350" spans="1:17" ht="18">
@@ -62623,9 +62278,8 @@
       <c r="P350" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q350" t="str">
-        <f>VLOOKUP(D350,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q350" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="351" spans="1:17" ht="18">
@@ -62676,9 +62330,8 @@
       <c r="P351" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q351" t="str">
-        <f>VLOOKUP(D351,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q351" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="352" spans="1:17" ht="18">
@@ -62729,9 +62382,8 @@
       <c r="P352" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q352" t="str">
-        <f>VLOOKUP(D352,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q352" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="353" spans="1:17" ht="18">
@@ -62782,9 +62434,8 @@
       <c r="P353" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q353" t="str">
-        <f>VLOOKUP(D353,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q353" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="354" spans="1:17" ht="18">
@@ -62835,9 +62486,8 @@
       <c r="P354" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q354" t="str">
-        <f>VLOOKUP(D354,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q354" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="355" spans="1:17" ht="18">
@@ -62888,9 +62538,8 @@
       <c r="P355" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q355" t="str">
-        <f>VLOOKUP(D355,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q355" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="356" spans="1:17" ht="18">
@@ -62941,9 +62590,8 @@
       <c r="P356" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q356" t="str">
-        <f>VLOOKUP(D356,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q356" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="357" spans="1:17" ht="18">
@@ -62994,9 +62642,8 @@
       <c r="P357" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q357" t="str">
-        <f>VLOOKUP(D357,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q357" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="358" spans="1:17" ht="18">
@@ -63047,9 +62694,8 @@
       <c r="P358" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q358" t="str">
-        <f>VLOOKUP(D358,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q358" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="359" spans="1:17" ht="18">
@@ -63100,9 +62746,8 @@
       <c r="P359" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q359" t="str">
-        <f>VLOOKUP(D359,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q359" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="360" spans="1:17" ht="18">
@@ -63153,9 +62798,8 @@
       <c r="P360" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q360" t="str">
-        <f>VLOOKUP(D360,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q360" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="361" spans="1:17" ht="18">
@@ -63206,9 +62850,8 @@
       <c r="P361" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q361" t="str">
-        <f>VLOOKUP(D361,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q361" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="362" spans="1:17" ht="18">
@@ -63259,9 +62902,8 @@
       <c r="P362" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q362" t="str">
-        <f>VLOOKUP(D362,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q362" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="363" spans="1:17" ht="18">
@@ -63310,9 +62952,8 @@
       <c r="P363" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q363" t="str">
-        <f>VLOOKUP(D363,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q363" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="364" spans="1:17" ht="18">
@@ -63361,9 +63002,8 @@
       <c r="P364" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q364" t="str">
-        <f>VLOOKUP(D364,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q364" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="365" spans="1:17" ht="18">
@@ -63412,9 +63052,8 @@
       <c r="P365" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q365" t="str">
-        <f>VLOOKUP(D365,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q365" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="366" spans="1:17" ht="18">
@@ -63463,9 +63102,8 @@
       <c r="P366" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q366" t="str">
-        <f>VLOOKUP(D366,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q366" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="367" spans="1:17" ht="18">
@@ -63514,9 +63152,8 @@
       <c r="P367" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q367" t="str">
-        <f>VLOOKUP(D367,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q367" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="368" spans="1:17" ht="18">
@@ -63565,9 +63202,8 @@
       <c r="P368" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q368" t="str">
-        <f>VLOOKUP(D368,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q368" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="369" spans="1:17" ht="18">
@@ -63616,9 +63252,8 @@
       <c r="P369" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q369" t="str">
-        <f>VLOOKUP(D369,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q369" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="370" spans="1:17" ht="18">
@@ -63667,9 +63302,8 @@
       <c r="P370" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q370" t="str">
-        <f>VLOOKUP(D370,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q370" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="371" spans="1:17" ht="18">
@@ -63720,9 +63354,8 @@
       <c r="P371" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q371" t="str">
-        <f>VLOOKUP(D371,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q371" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="372" spans="1:17" ht="18">
@@ -63773,9 +63406,8 @@
       <c r="P372" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q372" t="str">
-        <f>VLOOKUP(D372,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q372" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="373" spans="1:17" ht="18">
@@ -63826,9 +63458,8 @@
       <c r="P373" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q373" t="str">
-        <f>VLOOKUP(D373,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q373" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="374" spans="1:17" ht="18">
@@ -63879,9 +63510,8 @@
       <c r="P374" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Q374" t="str">
-        <f>VLOOKUP(D374,'rak2'!$A$1:$B$6, 2)</f>
-        <v>B4, B6, C10</v>
+      <c r="Q374" t="s">
+        <v>1360</v>
       </c>
     </row>
   </sheetData>

--- a/database/seeders/data/data.xlsx
+++ b/database/seeders/data/data.xlsx
@@ -4431,7 +4431,7 @@
     <numFmt numFmtId="171" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="172" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <sz val="11"/>
@@ -4580,6 +4580,10 @@
       <name val="Cambria"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Cambria"/>
@@ -4930,23 +4934,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="bottom"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
       <alignment vertical="bottom"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="172" fontId="31" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
       <alignment vertical="bottom"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0">
+    <xf numFmtId="172" fontId="32" fillId="0" borderId="0">
       <alignment vertical="bottom"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
+    <xf numFmtId="167" fontId="32" fillId="0" borderId="0">
+      <alignment vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
       <alignment vertical="bottom"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -5435,22 +5439,22 @@
     <xf numFmtId="1" fontId="21" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="25" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5862,15 +5866,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>176006</xdr:colOff>
+      <xdr:colOff>174722</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>969964</xdr:colOff>
+      <xdr:colOff>968679</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>291673</xdr:rowOff>
+      <xdr:rowOff>278249</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5906,15 +5910,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>176006</xdr:colOff>
+      <xdr:colOff>174722</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>969964</xdr:colOff>
+      <xdr:colOff>968679</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>291673</xdr:rowOff>
+      <xdr:rowOff>278249</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5950,15 +5954,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>176006</xdr:colOff>
+      <xdr:colOff>174722</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>969964</xdr:colOff>
+      <xdr:colOff>968679</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>291673</xdr:rowOff>
+      <xdr:rowOff>278249</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5994,15 +5998,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>176006</xdr:colOff>
+      <xdr:colOff>174722</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>969964</xdr:colOff>
+      <xdr:colOff>968679</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>291673</xdr:rowOff>
+      <xdr:rowOff>278249</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6038,15 +6042,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>176006</xdr:colOff>
+      <xdr:colOff>174722</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>969964</xdr:colOff>
+      <xdr:colOff>968679</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>291673</xdr:rowOff>
+      <xdr:rowOff>278249</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6082,15 +6086,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>176006</xdr:colOff>
+      <xdr:colOff>174722</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>969964</xdr:colOff>
+      <xdr:colOff>968679</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>291673</xdr:rowOff>
+      <xdr:rowOff>278249</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6126,15 +6130,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>176006</xdr:colOff>
+      <xdr:colOff>174722</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>969964</xdr:colOff>
+      <xdr:colOff>968679</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>291673</xdr:rowOff>
+      <xdr:rowOff>278249</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6170,15 +6174,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>176006</xdr:colOff>
+      <xdr:colOff>174722</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>969964</xdr:colOff>
+      <xdr:colOff>968679</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>291673</xdr:rowOff>
+      <xdr:rowOff>278249</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6214,15 +6218,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>176006</xdr:colOff>
+      <xdr:colOff>174722</xdr:colOff>
       <xdr:row>52</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>969964</xdr:colOff>
+      <xdr:colOff>968679</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>291673</xdr:rowOff>
+      <xdr:rowOff>278249</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6258,15 +6262,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>176006</xdr:colOff>
+      <xdr:colOff>174722</xdr:colOff>
       <xdr:row>52</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>969964</xdr:colOff>
+      <xdr:colOff>968679</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>291673</xdr:rowOff>
+      <xdr:rowOff>278249</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6304,13 +6308,13 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>148415</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>12203</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>148415</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>37653</xdr:rowOff>
+      <xdr:rowOff>24817</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -6358,15 +6362,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>3854</xdr:colOff>
+      <xdr:colOff>2569</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>12501</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>1130197</xdr:colOff>
+      <xdr:colOff>1128923</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>25003</xdr:rowOff>
+      <xdr:rowOff>12501</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -6416,13 +6420,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>25003</xdr:rowOff>
+      <xdr:rowOff>12501</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>1125100</xdr:colOff>
+      <xdr:colOff>1123826</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>25003</xdr:rowOff>
+      <xdr:rowOff>12501</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -6472,13 +6476,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>25151</xdr:rowOff>
+      <xdr:rowOff>12575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>1113633</xdr:colOff>
+      <xdr:colOff>1112358</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>37727</xdr:rowOff>
+      <xdr:rowOff>25151</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -6528,11 +6532,11 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>12501</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>1080504</xdr:colOff>
+      <xdr:colOff>1079230</xdr:colOff>
       <xdr:row>51</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
@@ -6944,7 +6948,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q88"/>
+  <dimension ref="A1:R88"/>
   <sheetFormatPr defaultRowHeight="16.5" defaultColWidth="9"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="9.425781" style="1"/>
@@ -11026,50 +11030,50 @@
     <row r="88" spans="8:8" ht="8.1" customHeight="1"/>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="N65:O65"/>
-    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="J57:K57"/>
     <mergeCell ref="B73:C73"/>
     <mergeCell ref="N57:O57"/>
-    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="N81:O81"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="J65:K65"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="B17:C17"/>
     <mergeCell ref="N41:O41"/>
-    <mergeCell ref="J17:K17"/>
     <mergeCell ref="F57:G57"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="F81:G81"/>
     <mergeCell ref="B81:C81"/>
-    <mergeCell ref="N73:O73"/>
-    <mergeCell ref="J73:K73"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="N81:O81"/>
-    <mergeCell ref="J81:K81"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="N49:O49"/>
-    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J49:K49"/>
     <mergeCell ref="J41:K41"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="B57:C57"/>
     <mergeCell ref="J33:K33"/>
-    <mergeCell ref="F25:G25"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="J57:K57"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="B25:C25"/>
+    <mergeCell ref="J73:K73"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="N65:O65"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="N73:O73"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="J81:K81"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B1:C1"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.0" right="0.0" top="0.0" bottom="0.0" header="0.0" footer="0.0"/>
@@ -11079,7 +11083,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="47.85547" style="0"/>
@@ -12079,7 +12083,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q88"/>
+  <dimension ref="A1:R88"/>
   <sheetFormatPr defaultRowHeight="16.5" defaultColWidth="9"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="9.425781" style="1"/>
@@ -16161,50 +16165,50 @@
     <row r="88" spans="8:8" ht="8.1" customHeight="1"/>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="N65:O65"/>
-    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="J57:K57"/>
     <mergeCell ref="B73:C73"/>
     <mergeCell ref="N57:O57"/>
-    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="N81:O81"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="J65:K65"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="B17:C17"/>
     <mergeCell ref="N41:O41"/>
-    <mergeCell ref="J17:K17"/>
     <mergeCell ref="F57:G57"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="F81:G81"/>
     <mergeCell ref="B81:C81"/>
-    <mergeCell ref="N73:O73"/>
-    <mergeCell ref="J73:K73"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="N81:O81"/>
-    <mergeCell ref="J81:K81"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="N49:O49"/>
-    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J49:K49"/>
     <mergeCell ref="J41:K41"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="B57:C57"/>
     <mergeCell ref="J33:K33"/>
-    <mergeCell ref="F25:G25"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="J57:K57"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="B25:C25"/>
+    <mergeCell ref="J73:K73"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="N65:O65"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="N73:O73"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="J81:K81"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B1:C1"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.0" right="0.0" top="0.0" bottom="0.0" header="0.0" footer="0.0"/>
@@ -16217,7 +16221,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q88"/>
+  <dimension ref="A1:R88"/>
   <sheetFormatPr defaultRowHeight="16.5" defaultColWidth="9"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="9.425781" style="1"/>
@@ -20299,50 +20303,50 @@
     <row r="88" spans="8:8" ht="8.1" customHeight="1"/>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="N65:O65"/>
-    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="J57:K57"/>
     <mergeCell ref="B73:C73"/>
     <mergeCell ref="N57:O57"/>
-    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="N81:O81"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="J65:K65"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="B17:C17"/>
     <mergeCell ref="N41:O41"/>
-    <mergeCell ref="J17:K17"/>
     <mergeCell ref="F57:G57"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="F81:G81"/>
     <mergeCell ref="B81:C81"/>
-    <mergeCell ref="N73:O73"/>
-    <mergeCell ref="J73:K73"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="N81:O81"/>
-    <mergeCell ref="J81:K81"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="N49:O49"/>
-    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J49:K49"/>
     <mergeCell ref="J41:K41"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="B57:C57"/>
     <mergeCell ref="J33:K33"/>
-    <mergeCell ref="F25:G25"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="J57:K57"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="B25:C25"/>
+    <mergeCell ref="J73:K73"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="N65:O65"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="N73:O73"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="J81:K81"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B1:C1"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.0" right="0.0" top="0.0" bottom="0.0" header="0.0" footer="0.0"/>
@@ -20355,7 +20359,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q88"/>
+  <dimension ref="A1:R88"/>
   <sheetFormatPr defaultRowHeight="16.5" defaultColWidth="9"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="9.425781" style="1"/>
@@ -24437,50 +24441,50 @@
     <row r="88" spans="8:8" ht="8.1" customHeight="1"/>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="N65:O65"/>
-    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="J57:K57"/>
     <mergeCell ref="B73:C73"/>
     <mergeCell ref="N57:O57"/>
-    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="N81:O81"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="J65:K65"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="B17:C17"/>
     <mergeCell ref="N41:O41"/>
-    <mergeCell ref="J17:K17"/>
     <mergeCell ref="F57:G57"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="F81:G81"/>
     <mergeCell ref="B81:C81"/>
-    <mergeCell ref="N73:O73"/>
-    <mergeCell ref="J73:K73"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="N81:O81"/>
-    <mergeCell ref="J81:K81"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="N49:O49"/>
-    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J49:K49"/>
     <mergeCell ref="J41:K41"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="B57:C57"/>
     <mergeCell ref="J33:K33"/>
-    <mergeCell ref="F25:G25"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="J57:K57"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="B25:C25"/>
+    <mergeCell ref="J73:K73"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="N65:O65"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="N73:O73"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="J81:K81"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B1:C1"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.0" right="0.0" top="0.0" bottom="0.0" header="0.0" footer="0.0"/>
@@ -24490,7 +24494,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:P64"/>
   <sheetFormatPr defaultRowHeight="17.25" defaultColWidth="9"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="16.710938" style="21"/>
@@ -26111,156 +26115,156 @@
     </row>
   </sheetData>
   <mergeCells count="150">
+    <mergeCell ref="M10:M11"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="I53:M53"/>
+    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="F29:F31"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="I40:M40"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="J50:K50"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="M59:M61"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="H64:M64"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="L62:L63"/>
+    <mergeCell ref="F46:F48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="L49:L50"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="M46:M48"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="J54:L54"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="L36:L37"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="I14:M14"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="F62:F63"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="M49:M50"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="F55:F57"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="M42:M44"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="M29:M31"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="E36:E37"/>
     <mergeCell ref="L23:L24"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="J31:L31"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="F33:F35"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="M33:M35"/>
+    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="I1:M1"/>
+    <mergeCell ref="J62:K62"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="M3:M5"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="J63:K63"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="M55:M57"/>
+    <mergeCell ref="F59:F61"/>
+    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="M16:M18"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="I27:M27"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="C63:D63"/>
     <mergeCell ref="A62:B62"/>
-    <mergeCell ref="H64:M64"/>
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="M62:M63"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="C4:E4"/>
     <mergeCell ref="M20:M22"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="E10:E11"/>
     <mergeCell ref="E23:E24"/>
     <mergeCell ref="J2:L2"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="M10:M11"/>
-    <mergeCell ref="M16:M18"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="M59:M61"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="M62:M63"/>
-    <mergeCell ref="J63:K63"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="A64:F64"/>
-    <mergeCell ref="M36:M37"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="F16:F18"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="M3:M5"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="I14:M14"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="F59:F61"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="J61:K61"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="M55:M57"/>
-    <mergeCell ref="J62:K62"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="I27:M27"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="J29:L29"/>
     <mergeCell ref="F20:F22"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J18:L18"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F33:F35"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="J28:L28"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="M29:M31"/>
-    <mergeCell ref="M46:M48"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="L49:L50"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="J54:L54"/>
-    <mergeCell ref="F62:F63"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="L36:L37"/>
-    <mergeCell ref="L62:L63"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="M49:M50"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="J30:L30"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="F46:F48"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="F55:F57"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="M42:M44"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="J48:K48"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="M33:M35"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="F42:F44"/>
-    <mergeCell ref="J17:L17"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="I40:M40"/>
-    <mergeCell ref="L10:L11"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="I53:M53"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="J44:L44"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="F29:F31"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="J50:K50"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="J31:L31"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="M23:M24"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="I1:M1"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="C41:E41"/>
   </mergeCells>
   <pageMargins left="0.275590551181102" right="0.118110236220472" top="0.18" bottom="0.0" header="0.0" footer="0.0"/>
   <pageSetup paperSize="9" scale="68"/>
@@ -26270,7 +26274,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:R375"/>
+  <dimension ref="A1:S375"/>
   <sheetFormatPr defaultRowHeight="18.0" customHeight="1" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="9.140625" style="65"/>
@@ -26936,7 +26940,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="8:8" s="93" ht="18.0" customFormat="1" customHeight="1">
+    <row r="16" spans="8:8" s="93" ht="17.35" customFormat="1">
       <c r="A16" s="94" t="s">
         <v>92</v>
       </c>
@@ -44315,60 +44319,60 @@
   <mergeCells count="13">
     <mergeCell ref="P3:P4"/>
     <mergeCell ref="I3:M3"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="N3:N4"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="A1:N2"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="A1:N2"/>
   </mergeCells>
+  <conditionalFormatting sqref="B333">
+    <cfRule type="duplicateValues" priority="15" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="14" dxfId="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B329:B330">
-    <cfRule type="duplicateValues" priority="17" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="17" dxfId="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B334:B335">
+    <cfRule type="duplicateValues" priority="12" dxfId="3"/>
+    <cfRule type="duplicateValues" priority="13" dxfId="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B338">
+    <cfRule type="duplicateValues" priority="5" dxfId="5"/>
+    <cfRule type="duplicateValues" priority="6" dxfId="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H331:H332">
+    <cfRule type="duplicateValues" priority="9" dxfId="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H343:H348">
+    <cfRule type="duplicateValues" priority="35" dxfId="8"/>
+    <cfRule type="duplicateValues" priority="34" dxfId="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B339:B375">
+    <cfRule type="duplicateValues" priority="30" dxfId="10"/>
+    <cfRule type="duplicateValues" priority="31" dxfId="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B337">
+    <cfRule type="duplicateValues" priority="7" dxfId="12"/>
+    <cfRule type="duplicateValues" priority="8" dxfId="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B327">
+    <cfRule type="duplicateValues" priority="23" dxfId="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328">
-    <cfRule type="duplicateValues" priority="18" dxfId="1"/>
+    <cfRule type="duplicateValues" priority="18" dxfId="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H343:H348">
-    <cfRule type="duplicateValues" priority="34" dxfId="2"/>
-    <cfRule type="duplicateValues" priority="35" dxfId="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B339:B375">
-    <cfRule type="duplicateValues" priority="30" dxfId="4"/>
-    <cfRule type="duplicateValues" priority="31" dxfId="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B333">
-    <cfRule type="duplicateValues" priority="14" dxfId="6"/>
-    <cfRule type="duplicateValues" priority="15" dxfId="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B337">
-    <cfRule type="duplicateValues" priority="7" dxfId="8"/>
-    <cfRule type="duplicateValues" priority="8" dxfId="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B338">
-    <cfRule type="duplicateValues" priority="6" dxfId="10"/>
-    <cfRule type="duplicateValues" priority="5" dxfId="11"/>
+  <conditionalFormatting sqref="B331:B332">
+    <cfRule type="duplicateValues" priority="16" dxfId="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B336">
-    <cfRule type="duplicateValues" priority="11" dxfId="12"/>
-    <cfRule type="duplicateValues" priority="10" dxfId="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B334:B335">
-    <cfRule type="duplicateValues" priority="12" dxfId="14"/>
-    <cfRule type="duplicateValues" priority="13" dxfId="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B327">
-    <cfRule type="duplicateValues" priority="23" dxfId="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H331:H332">
-    <cfRule type="duplicateValues" priority="9" dxfId="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B331:B332">
-    <cfRule type="duplicateValues" priority="16" dxfId="18"/>
+    <cfRule type="duplicateValues" priority="11" dxfId="17"/>
+    <cfRule type="duplicateValues" priority="10" dxfId="18"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.15748031496063" right="0.15748031496063" top="0.354330708661417" bottom="0.15748031496063" header="0.0" footer="0.0"/>
@@ -44378,7 +44382,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="9"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="3.8554688" style="0"/>
@@ -44641,7 +44645,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:S374"/>
+  <dimension ref="A1:T374"/>
   <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
   <cols>
     <col min="7" max="7" customWidth="1" width="16.710938" style="0"/>
@@ -44748,7 +44752,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="5" spans="8:8" ht="18.0">
+    <row r="5" spans="8:8" ht="16.9">
       <c r="A5" s="94" t="s">
         <v>49</v>
       </c>
@@ -44778,7 +44782,7 @@
       <c r="J5" s="149">
         <v>26.2</v>
       </c>
-      <c r="K5" s="104">
+      <c r="K5">
         <f>(I5+(J5*E5))/1000</f>
         <v>6.044</v>
       </c>
@@ -44800,7 +44804,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="6" spans="8:8" ht="18.0">
+    <row r="6" spans="8:8" ht="16.9">
       <c r="A6" s="94" t="s">
         <v>56</v>
       </c>
@@ -44830,7 +44834,7 @@
       <c r="J6" s="149">
         <v>38.6</v>
       </c>
-      <c r="K6" s="104">
+      <c r="K6">
         <f>(I6+(J6*E6))/1000</f>
         <v>8.772</v>
       </c>
@@ -44852,7 +44856,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="7" spans="8:8" ht="18.0">
+    <row r="7" spans="8:8" ht="16.9">
       <c r="A7" s="94" t="s">
         <v>59</v>
       </c>
@@ -44882,7 +44886,7 @@
       <c r="J7" s="149">
         <v>26.2</v>
       </c>
-      <c r="K7" s="104">
+      <c r="K7">
         <f>(I7+(J7*E7))/1000</f>
         <v>6.044</v>
       </c>
@@ -44904,7 +44908,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="8" spans="8:8" ht="18.0">
+    <row r="8" spans="8:8" ht="16.9">
       <c r="A8" s="94" t="s">
         <v>62</v>
       </c>
@@ -44934,7 +44938,7 @@
       <c r="J8" s="149">
         <v>38.6</v>
       </c>
-      <c r="K8" s="104">
+      <c r="K8">
         <f>(I8+(J8*E8))/1000</f>
         <v>8.772</v>
       </c>
@@ -44956,7 +44960,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="9" spans="8:8" ht="18.0">
+    <row r="9" spans="8:8" ht="16.9">
       <c r="A9" s="94" t="s">
         <v>65</v>
       </c>
@@ -44986,7 +44990,7 @@
       <c r="J9" s="149">
         <v>1650.4</v>
       </c>
-      <c r="K9" s="104">
+      <c r="K9">
         <f>(I9+(J9*E9))/1000</f>
         <v>27.354400000000002</v>
       </c>
@@ -45008,7 +45012,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="10" spans="8:8" ht="18.0">
+    <row r="10" spans="8:8" ht="16.9">
       <c r="A10" s="94" t="s">
         <v>69</v>
       </c>
@@ -45038,7 +45042,7 @@
       <c r="J10" s="149">
         <v>170.0</v>
       </c>
-      <c r="K10" s="104">
+      <c r="K10">
         <f>(I10+(J10*E10))/1000</f>
         <v>7.566</v>
       </c>
@@ -45060,7 +45064,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="11" spans="8:8" ht="18.0">
+    <row r="11" spans="8:8" ht="16.9">
       <c r="A11" s="94" t="s">
         <v>73</v>
       </c>
@@ -45090,7 +45094,7 @@
       <c r="J11" s="149">
         <v>68.2</v>
       </c>
-      <c r="K11" s="104">
+      <c r="K11">
         <f>(I11+(J11*E11))/1000</f>
         <v>4.372</v>
       </c>
@@ -45112,7 +45116,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="12" spans="8:8" ht="18.0">
+    <row r="12" spans="8:8" ht="16.9">
       <c r="A12" s="94" t="s">
         <v>76</v>
       </c>
@@ -45140,7 +45144,7 @@
       <c r="J12" s="149">
         <v>5076.8</v>
       </c>
-      <c r="K12" s="104">
+      <c r="K12">
         <f>(I12+(J12*E12))/1000</f>
         <v>101.536</v>
       </c>
@@ -45162,7 +45166,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="13" spans="8:8" ht="18.0">
+    <row r="13" spans="8:8" ht="16.9">
       <c r="A13" s="94" t="s">
         <v>80</v>
       </c>
@@ -45192,7 +45196,7 @@
       <c r="J13" s="149">
         <v>411.0</v>
       </c>
-      <c r="K13" s="104">
+      <c r="K13">
         <f>(I13+(J13*E13))/1000</f>
         <v>12.76</v>
       </c>
@@ -45214,7 +45218,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="14" spans="8:8" ht="18.0">
+    <row r="14" spans="8:8" ht="16.9">
       <c r="A14" s="94" t="s">
         <v>84</v>
       </c>
@@ -45244,7 +45248,7 @@
       <c r="J14" s="149">
         <v>411.0</v>
       </c>
-      <c r="K14" s="104">
+      <c r="K14">
         <f>(I14+(J14*E14))/1000</f>
         <v>12.76</v>
       </c>
@@ -45268,7 +45272,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="15" spans="8:8" ht="18.0">
+    <row r="15" spans="8:8" ht="16.9">
       <c r="A15" s="94" t="s">
         <v>88</v>
       </c>
@@ -45298,7 +45302,7 @@
       <c r="J15" s="149">
         <v>437.8</v>
       </c>
-      <c r="K15" s="104">
+      <c r="K15">
         <f>(I15+(J15*E15))/1000</f>
         <v>12.6364</v>
       </c>
@@ -45320,7 +45324,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="16" spans="8:8" ht="18.0">
+    <row r="16" spans="8:8" ht="16.9">
       <c r="A16" s="94" t="s">
         <v>92</v>
       </c>
@@ -45350,7 +45354,7 @@
       <c r="J16" s="149">
         <v>91.0</v>
       </c>
-      <c r="K16" s="104">
+      <c r="K16">
         <f>(I16+(J16*E16))/1000</f>
         <v>9.38</v>
       </c>
@@ -45372,7 +45376,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="17" spans="8:8" ht="18.0">
+    <row r="17" spans="8:8" ht="16.9">
       <c r="A17" s="94" t="s">
         <v>95</v>
       </c>
@@ -45402,7 +45406,7 @@
       <c r="J17" s="149">
         <v>91.0</v>
       </c>
-      <c r="K17" s="104">
+      <c r="K17">
         <f>(I17+(J17*E17))/1000</f>
         <v>9.38</v>
       </c>
@@ -45424,7 +45428,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="18" spans="8:8" ht="18.0">
+    <row r="18" spans="8:8" ht="16.9">
       <c r="A18" s="94" t="s">
         <v>98</v>
       </c>
@@ -45454,7 +45458,7 @@
       <c r="J18" s="149">
         <v>1034.0</v>
       </c>
-      <c r="K18" s="104">
+      <c r="K18">
         <f>(I18+(J18*E18))/1000</f>
         <v>21.26</v>
       </c>
@@ -45476,7 +45480,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="19" spans="8:8" ht="18.0">
+    <row r="19" spans="8:8" ht="16.9">
       <c r="A19" s="94" t="s">
         <v>102</v>
       </c>
@@ -45506,7 +45510,7 @@
       <c r="J19" s="149">
         <v>1034.0</v>
       </c>
-      <c r="K19" s="104">
+      <c r="K19">
         <f>(I19+(J19*E19))/1000</f>
         <v>21.26</v>
       </c>
@@ -45528,7 +45532,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="20" spans="8:8" ht="18.0">
+    <row r="20" spans="8:8" ht="16.9">
       <c r="A20" s="94" t="s">
         <v>105</v>
       </c>
@@ -45558,7 +45562,7 @@
       <c r="J20" s="149">
         <v>610.0</v>
       </c>
-      <c r="K20" s="104">
+      <c r="K20">
         <f>(I20+(J20*E20))/1000</f>
         <v>8.086</v>
       </c>
@@ -45580,7 +45584,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="21" spans="8:8" ht="18.0">
+    <row r="21" spans="8:8" ht="16.9">
       <c r="A21" s="94" t="s">
         <v>108</v>
       </c>
@@ -45610,7 +45614,7 @@
       <c r="J21" s="149">
         <v>724.0</v>
       </c>
-      <c r="K21" s="104">
+      <c r="K21">
         <f>(I21+(J21*E21))/1000</f>
         <v>29.338</v>
       </c>
@@ -45632,7 +45636,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="22" spans="8:8" ht="18.0">
+    <row r="22" spans="8:8" ht="16.9">
       <c r="A22" s="94" t="s">
         <v>111</v>
       </c>
@@ -45662,7 +45666,7 @@
       <c r="J22" s="149">
         <v>26.0</v>
       </c>
-      <c r="K22" s="104">
+      <c r="K22">
         <f>(I22+(J22*E22))/1000</f>
         <v>9.64</v>
       </c>
@@ -45684,7 +45688,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="23" spans="8:8" ht="18.0">
+    <row r="23" spans="8:8" ht="16.9">
       <c r="A23" s="94" t="s">
         <v>114</v>
       </c>
@@ -45714,7 +45718,7 @@
       <c r="J23" s="149">
         <v>26.8</v>
       </c>
-      <c r="K23" s="104">
+      <c r="K23">
         <f>(I23+(J23*E23))/1000</f>
         <v>9.928</v>
       </c>
@@ -45736,7 +45740,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="24" spans="8:8" ht="18.0">
+    <row r="24" spans="8:8" ht="16.9">
       <c r="A24" s="94" t="s">
         <v>117</v>
       </c>
@@ -45766,7 +45770,7 @@
       <c r="J24" s="149">
         <v>26.0</v>
       </c>
-      <c r="K24" s="104">
+      <c r="K24">
         <f>(I24+(J24*E24))/1000</f>
         <v>9.64</v>
       </c>
@@ -45788,7 +45792,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="25" spans="8:8" ht="18.0">
+    <row r="25" spans="8:8" ht="16.9">
       <c r="A25" s="94" t="s">
         <v>120</v>
       </c>
@@ -45818,7 +45822,7 @@
       <c r="J25" s="149">
         <v>26.8</v>
       </c>
-      <c r="K25" s="104">
+      <c r="K25">
         <f>(I25+(J25*E25))/1000</f>
         <v>9.928</v>
       </c>
@@ -45840,7 +45844,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="26" spans="8:8" ht="18.0">
+    <row r="26" spans="8:8" ht="16.9">
       <c r="A26" s="94" t="s">
         <v>123</v>
       </c>
@@ -45870,7 +45874,7 @@
       <c r="J26" s="152">
         <v>1076.0</v>
       </c>
-      <c r="K26" s="104">
+      <c r="K26">
         <f>(I26+(J26*E26))/1000</f>
         <v>22.648</v>
       </c>
@@ -45892,7 +45896,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="27" spans="8:8" ht="18.0">
+    <row r="27" spans="8:8" ht="16.9">
       <c r="A27" s="94" t="s">
         <v>127</v>
       </c>
@@ -45922,7 +45926,7 @@
       <c r="J27" s="152">
         <v>1076.0</v>
       </c>
-      <c r="K27" s="104">
+      <c r="K27">
         <f>(I27+(J27*E27))/1000</f>
         <v>22.648</v>
       </c>
@@ -45944,7 +45948,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="28" spans="8:8" ht="18.0">
+    <row r="28" spans="8:8" ht="16.9">
       <c r="A28" s="94" t="s">
         <v>130</v>
       </c>
@@ -45974,7 +45978,7 @@
       <c r="J28" s="149">
         <v>120.0</v>
       </c>
-      <c r="K28" s="104">
+      <c r="K28">
         <f>(I28+(J28*E28))/1000</f>
         <v>18.28</v>
       </c>
@@ -45996,7 +46000,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="29" spans="8:8" ht="18.0">
+    <row r="29" spans="8:8" ht="16.9">
       <c r="A29" s="94" t="s">
         <v>133</v>
       </c>
@@ -46026,7 +46030,7 @@
       <c r="J29" s="149">
         <v>120.0</v>
       </c>
-      <c r="K29" s="104">
+      <c r="K29">
         <f>(I29+(J29*E29))/1000</f>
         <v>18.28</v>
       </c>
@@ -46048,7 +46052,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="30" spans="8:8" ht="18.0">
+    <row r="30" spans="8:8" ht="16.9">
       <c r="A30" s="94" t="s">
         <v>136</v>
       </c>
@@ -46078,7 +46082,7 @@
       <c r="J30" s="152">
         <v>1873.4</v>
       </c>
-      <c r="K30" s="104">
+      <c r="K30">
         <f>(I30+(J30*E30))/1000</f>
         <v>12.280400000000002</v>
       </c>
@@ -46100,7 +46104,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="31" spans="8:8" ht="18.0">
+    <row r="31" spans="8:8" ht="16.9">
       <c r="A31" s="94" t="s">
         <v>140</v>
       </c>
@@ -46130,7 +46134,7 @@
       <c r="J31" s="149">
         <v>236.0</v>
       </c>
-      <c r="K31" s="104">
+      <c r="K31">
         <f>(I31+(J31*E31))/1000</f>
         <v>6.042</v>
       </c>
@@ -46152,7 +46156,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="32" spans="8:8" ht="18.0">
+    <row r="32" spans="8:8" ht="16.9">
       <c r="A32" s="94" t="s">
         <v>143</v>
       </c>
@@ -46182,7 +46186,7 @@
       <c r="J32" s="149">
         <v>34.6</v>
       </c>
-      <c r="K32" s="104">
+      <c r="K32">
         <f>(I32+(J32*E32))/1000</f>
         <v>8.682</v>
       </c>
@@ -46204,7 +46208,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="33" spans="8:8" ht="18.0">
+    <row r="33" spans="8:8" ht="16.9">
       <c r="A33" s="94" t="s">
         <v>146</v>
       </c>
@@ -46234,7 +46238,7 @@
       <c r="J33" s="149">
         <v>17.4</v>
       </c>
-      <c r="K33" s="104">
+      <c r="K33">
         <f>(I33+(J33*E33))/1000</f>
         <v>9.078</v>
       </c>
@@ -46256,7 +46260,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="34" spans="8:8" ht="18.0">
+    <row r="34" spans="8:8" ht="16.9">
       <c r="A34" s="94" t="s">
         <v>149</v>
       </c>
@@ -46286,7 +46290,7 @@
       <c r="J34" s="149">
         <v>1071.8</v>
       </c>
-      <c r="K34" s="104">
+      <c r="K34">
         <f>(I34+(J34*E34))/1000</f>
         <v>13.809599999999998</v>
       </c>
@@ -46308,7 +46312,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="35" spans="8:8" ht="18.0">
+    <row r="35" spans="8:8" ht="16.9">
       <c r="A35" s="94" t="s">
         <v>152</v>
       </c>
@@ -46338,7 +46342,7 @@
       <c r="J35" s="149">
         <v>57.6</v>
       </c>
-      <c r="K35" s="104">
+      <c r="K35">
         <f>(I35+(J35*E35))/1000</f>
         <v>3.834</v>
       </c>
@@ -46360,7 +46364,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="36" spans="8:8" ht="18.0">
+    <row r="36" spans="8:8" ht="16.9">
       <c r="A36" s="94" t="s">
         <v>155</v>
       </c>
@@ -46390,7 +46394,7 @@
       <c r="J36" s="149">
         <v>60.4</v>
       </c>
-      <c r="K36" s="104">
+      <c r="K36">
         <f>(I36+(J36*E36))/1000</f>
         <v>6.32</v>
       </c>
@@ -46412,7 +46416,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="37" spans="8:8" ht="18.0">
+    <row r="37" spans="8:8" ht="16.9">
       <c r="A37" s="94" t="s">
         <v>158</v>
       </c>
@@ -46442,7 +46446,7 @@
       <c r="J37" s="149">
         <v>75.4</v>
       </c>
-      <c r="K37" s="104">
+      <c r="K37">
         <f>(I37+(J37*E37))/1000</f>
         <v>2.6908000000000003</v>
       </c>
@@ -46464,7 +46468,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="38" spans="8:8" ht="18.0">
+    <row r="38" spans="8:8" ht="16.9">
       <c r="A38" s="94" t="s">
         <v>162</v>
       </c>
@@ -46494,7 +46498,7 @@
       <c r="J38" s="149">
         <v>66.2</v>
       </c>
-      <c r="K38" s="104">
+      <c r="K38">
         <f>(I38+(J38*E38))/1000</f>
         <v>8.224</v>
       </c>
@@ -46516,7 +46520,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="39" spans="8:8" ht="18.0">
+    <row r="39" spans="8:8" ht="16.9">
       <c r="A39" s="94" t="s">
         <v>165</v>
       </c>
@@ -46546,7 +46550,7 @@
       <c r="J39" s="149">
         <v>19.0</v>
       </c>
-      <c r="K39" s="104">
+      <c r="K39">
         <f>(I39+(J39*E39))/1000</f>
         <v>19.28</v>
       </c>
@@ -46568,7 +46572,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="40" spans="8:8" ht="18.0">
+    <row r="40" spans="8:8" ht="16.9">
       <c r="A40" s="94" t="s">
         <v>168</v>
       </c>
@@ -46598,7 +46602,7 @@
       <c r="J40" s="149">
         <v>9.4</v>
       </c>
-      <c r="K40" s="104">
+      <c r="K40">
         <f>(I40+(J40*E40))/1000</f>
         <v>4.98</v>
       </c>
@@ -46620,7 +46624,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="41" spans="8:8" ht="18.0">
+    <row r="41" spans="8:8" ht="16.9">
       <c r="A41" s="94" t="s">
         <v>171</v>
       </c>
@@ -46650,7 +46654,7 @@
       <c r="J41" s="149">
         <v>21.6</v>
       </c>
-      <c r="K41" s="104">
+      <c r="K41">
         <f>(I41+(J41*E41))/1000</f>
         <v>11.08</v>
       </c>
@@ -46672,7 +46676,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="42" spans="8:8" ht="18.0">
+    <row r="42" spans="8:8" ht="16.9">
       <c r="A42" s="94" t="s">
         <v>174</v>
       </c>
@@ -46702,7 +46706,7 @@
       <c r="J42" s="149">
         <v>33.2</v>
       </c>
-      <c r="K42" s="104">
+      <c r="K42">
         <f>(I42+(J42*E42))/1000</f>
         <v>3.6000000000000005</v>
       </c>
@@ -46724,7 +46728,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="43" spans="8:8" ht="18.0">
+    <row r="43" spans="8:8" ht="16.9">
       <c r="A43" s="94" t="s">
         <v>177</v>
       </c>
@@ -46754,7 +46758,7 @@
       <c r="J43" s="149">
         <v>44.4</v>
       </c>
-      <c r="K43" s="104">
+      <c r="K43">
         <f>(I43+(J43*E43))/1000</f>
         <v>1.7988</v>
       </c>
@@ -46776,7 +46780,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="44" spans="8:8" ht="18.0">
+    <row r="44" spans="8:8" ht="16.9">
       <c r="A44" s="94" t="s">
         <v>180</v>
       </c>
@@ -46806,7 +46810,7 @@
       <c r="J44" s="149">
         <v>43.2</v>
       </c>
-      <c r="K44" s="104">
+      <c r="K44">
         <f>(I44+(J44*E44))/1000</f>
         <v>11.08</v>
       </c>
@@ -46828,7 +46832,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="45" spans="8:8" ht="18.0">
+    <row r="45" spans="8:8" ht="16.9">
       <c r="A45" s="94" t="s">
         <v>183</v>
       </c>
@@ -46858,7 +46862,7 @@
       <c r="J45" s="149">
         <v>38.0</v>
       </c>
-      <c r="K45" s="104">
+      <c r="K45">
         <f>(I45+(J45*E45))/1000</f>
         <v>7.12</v>
       </c>
@@ -46880,7 +46884,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="46" spans="8:8" ht="18.0">
+    <row r="46" spans="8:8" ht="16.9">
       <c r="A46" s="94" t="s">
         <v>186</v>
       </c>
@@ -46910,7 +46914,7 @@
       <c r="J46" s="149">
         <v>315.4</v>
       </c>
-      <c r="K46" s="104">
+      <c r="K46">
         <f>(I46+(J46*E46))/1000</f>
         <v>6.686</v>
       </c>
@@ -46932,7 +46936,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="47" spans="8:8" ht="18.0">
+    <row r="47" spans="8:8" ht="16.9">
       <c r="A47" s="94" t="s">
         <v>189</v>
       </c>
@@ -46962,7 +46966,7 @@
       <c r="J47" s="149">
         <v>315.8</v>
       </c>
-      <c r="K47" s="104">
+      <c r="K47">
         <f>(I47+(J47*E47))/1000</f>
         <v>6.694</v>
       </c>
@@ -46984,7 +46988,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="48" spans="8:8" ht="18.0">
+    <row r="48" spans="8:8" ht="16.9">
       <c r="A48" s="94" t="s">
         <v>192</v>
       </c>
@@ -47014,7 +47018,7 @@
       <c r="J48" s="149">
         <v>128.6</v>
       </c>
-      <c r="K48" s="104">
+      <c r="K48">
         <f>(I48+(J48*E48))/1000</f>
         <v>6.71</v>
       </c>
@@ -47036,7 +47040,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="49" spans="8:8" ht="18.0">
+    <row r="49" spans="8:8" ht="16.9">
       <c r="A49" s="94" t="s">
         <v>195</v>
       </c>
@@ -47066,7 +47070,7 @@
       <c r="J49" s="149">
         <v>61.8</v>
       </c>
-      <c r="K49" s="104">
+      <c r="K49">
         <f>(I49+(J49*E49))/1000</f>
         <v>12.64</v>
       </c>
@@ -47088,7 +47092,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="50" spans="8:8" ht="18.0">
+    <row r="50" spans="8:8" ht="16.9">
       <c r="A50" s="94" t="s">
         <v>198</v>
       </c>
@@ -47118,7 +47122,7 @@
       <c r="J50" s="149">
         <v>60.2</v>
       </c>
-      <c r="K50" s="104">
+      <c r="K50">
         <f>(I50+(J50*E50))/1000</f>
         <v>12.32</v>
       </c>
@@ -47140,7 +47144,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="51" spans="8:8" ht="18.0">
+    <row r="51" spans="8:8" ht="16.9">
       <c r="A51" s="94" t="s">
         <v>201</v>
       </c>
@@ -47170,7 +47174,7 @@
       <c r="J51" s="149">
         <v>31.6</v>
       </c>
-      <c r="K51" s="104">
+      <c r="K51">
         <f>(I51+(J51*E51))/1000</f>
         <v>16.08</v>
       </c>
@@ -47192,7 +47196,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="52" spans="8:8" ht="18.0">
+    <row r="52" spans="8:8" ht="16.9">
       <c r="A52" s="94" t="s">
         <v>204</v>
       </c>
@@ -47222,7 +47226,7 @@
       <c r="J52" s="149">
         <v>33.8</v>
       </c>
-      <c r="K52" s="104">
+      <c r="K52">
         <f>(I52+(J52*E52))/1000</f>
         <v>3.6599999999999997</v>
       </c>
@@ -47244,7 +47248,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="53" spans="8:8" ht="18.0">
+    <row r="53" spans="8:8" ht="16.9">
       <c r="A53" s="94" t="s">
         <v>207</v>
       </c>
@@ -47274,7 +47278,7 @@
       <c r="J53" s="149">
         <v>81.8</v>
       </c>
-      <c r="K53" s="104">
+      <c r="K53">
         <f>(I53+(J53*E53))/1000</f>
         <v>16.64</v>
       </c>
@@ -47296,7 +47300,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="54" spans="8:8" ht="18.0">
+    <row r="54" spans="8:8" ht="16.9">
       <c r="A54" s="94" t="s">
         <v>210</v>
       </c>
@@ -47326,7 +47330,7 @@
       <c r="J54" s="149">
         <v>17.8</v>
       </c>
-      <c r="K54" s="104">
+      <c r="K54">
         <f>(I54+(J54*E54))/1000</f>
         <v>3.484</v>
       </c>
@@ -47348,7 +47352,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="55" spans="8:8" ht="18.0">
+    <row r="55" spans="8:8" ht="16.9">
       <c r="A55" s="94" t="s">
         <v>213</v>
       </c>
@@ -47378,7 +47382,7 @@
       <c r="J55" s="149">
         <v>112.2</v>
       </c>
-      <c r="K55" s="104">
+      <c r="K55">
         <f>(I55+(J55*E55))/1000</f>
         <v>2.522</v>
       </c>
@@ -47400,7 +47404,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="56" spans="8:8" ht="18.0">
+    <row r="56" spans="8:8" ht="16.9">
       <c r="A56" s="94" t="s">
         <v>216</v>
       </c>
@@ -47430,7 +47434,7 @@
       <c r="J56" s="149">
         <v>781.0</v>
       </c>
-      <c r="K56" s="104">
+      <c r="K56">
         <f>(I56+(J56*E56))/1000</f>
         <v>14.614</v>
       </c>
@@ -47452,7 +47456,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="57" spans="8:8" ht="18.0">
+    <row r="57" spans="8:8" ht="16.9">
       <c r="A57" s="94" t="s">
         <v>219</v>
       </c>
@@ -47482,7 +47486,7 @@
       <c r="J57" s="149">
         <v>419.2</v>
       </c>
-      <c r="K57" s="104">
+      <c r="K57">
         <f>(I57+(J57*E57))/1000</f>
         <v>8.664</v>
       </c>
@@ -47504,7 +47508,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="58" spans="8:8" ht="18.0">
+    <row r="58" spans="8:8" ht="16.9">
       <c r="A58" s="94" t="s">
         <v>222</v>
       </c>
@@ -47532,7 +47536,7 @@
       <c r="J58" s="149">
         <v>4152.4</v>
       </c>
-      <c r="K58" s="104">
+      <c r="K58">
         <f>(I58+(J58*E58))/1000</f>
         <v>83.048</v>
       </c>
@@ -47554,7 +47558,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="59" spans="8:8" ht="18.0">
+    <row r="59" spans="8:8" ht="16.9">
       <c r="A59" s="111" t="s">
         <v>225</v>
       </c>
@@ -47584,7 +47588,7 @@
       <c r="J59" s="149">
         <v>110.0</v>
       </c>
-      <c r="K59" s="104">
+      <c r="K59">
         <f>(I59+(J59*E59))/1000</f>
         <v>3.8</v>
       </c>
@@ -47606,7 +47610,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="60" spans="8:8" ht="18.0">
+    <row r="60" spans="8:8" ht="16.9">
       <c r="A60" s="94" t="s">
         <v>228</v>
       </c>
@@ -47636,7 +47640,7 @@
       <c r="J60" s="149">
         <v>332.2</v>
       </c>
-      <c r="K60" s="104">
+      <c r="K60">
         <f>(I60+(J60*E60))/1000</f>
         <v>3.2678</v>
       </c>
@@ -47658,7 +47662,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="61" spans="8:8" ht="18.0">
+    <row r="61" spans="8:8" ht="16.9">
       <c r="A61" s="94" t="s">
         <v>231</v>
       </c>
@@ -47688,7 +47692,7 @@
       <c r="J61" s="149">
         <v>87.4</v>
       </c>
-      <c r="K61" s="104">
+      <c r="K61">
         <f>(I61+(J61*E61))/1000</f>
         <v>22.13</v>
       </c>
@@ -47710,7 +47714,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="62" spans="8:8" ht="18.0">
+    <row r="62" spans="8:8" ht="16.9">
       <c r="A62" s="94" t="s">
         <v>234</v>
       </c>
@@ -47740,7 +47744,7 @@
       <c r="J62" s="149">
         <v>320.0</v>
       </c>
-      <c r="K62" s="104">
+      <c r="K62">
         <f>(I62+(J62*E62))/1000</f>
         <v>3.158</v>
       </c>
@@ -47764,7 +47768,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="63" spans="8:8" ht="18.0">
+    <row r="63" spans="8:8" ht="16.9">
       <c r="A63" s="94" t="s">
         <v>238</v>
       </c>
@@ -47794,7 +47798,7 @@
       <c r="J63" s="149">
         <v>8.4</v>
       </c>
-      <c r="K63" s="104">
+      <c r="K63">
         <f>(I63+(J63*E63))/1000</f>
         <v>5.32</v>
       </c>
@@ -47816,7 +47820,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="64" spans="8:8" ht="18.0">
+    <row r="64" spans="8:8" ht="16.9">
       <c r="A64" s="94" t="s">
         <v>241</v>
       </c>
@@ -47846,7 +47850,7 @@
       <c r="J64" s="149">
         <v>12.4</v>
       </c>
-      <c r="K64" s="104">
+      <c r="K64">
         <f>(I64+(J64*E64))/1000</f>
         <v>5.238</v>
       </c>
@@ -47868,7 +47872,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="65" spans="8:8" ht="18.0">
+    <row r="65" spans="8:8" ht="16.9">
       <c r="A65" s="94" t="s">
         <v>244</v>
       </c>
@@ -47898,7 +47902,7 @@
       <c r="J65" s="149">
         <v>7.8</v>
       </c>
-      <c r="K65" s="104">
+      <c r="K65">
         <f>(I65+(J65*E65))/1000</f>
         <v>4.96</v>
       </c>
@@ -47920,7 +47924,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="66" spans="8:8" ht="18.0">
+    <row r="66" spans="8:8" ht="16.9">
       <c r="A66" s="94" t="s">
         <v>247</v>
       </c>
@@ -47950,7 +47954,7 @@
       <c r="J66" s="149">
         <v>124.4</v>
       </c>
-      <c r="K66" s="104">
+      <c r="K66">
         <f>(I66+(J66*E66))/1000</f>
         <v>4.01</v>
       </c>
@@ -47972,7 +47976,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="67" spans="8:8" ht="18.0">
+    <row r="67" spans="8:8" ht="16.9">
       <c r="A67" s="94" t="s">
         <v>250</v>
       </c>
@@ -48002,7 +48006,7 @@
       <c r="J67" s="149">
         <v>10.0</v>
       </c>
-      <c r="K67" s="104">
+      <c r="K67">
         <f>(I67+(J67*E67))/1000</f>
         <v>10.28</v>
       </c>
@@ -48024,7 +48028,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="68" spans="8:8" ht="18.0">
+    <row r="68" spans="8:8" ht="16.9">
       <c r="A68" s="94" t="s">
         <v>253</v>
       </c>
@@ -48054,7 +48058,7 @@
       <c r="J68" s="149">
         <v>333.6</v>
       </c>
-      <c r="K68" s="104">
+      <c r="K68">
         <f>(I68+(J68*E68))/1000</f>
         <v>10.438</v>
       </c>
@@ -48076,7 +48080,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="69" spans="8:8" ht="18.0">
+    <row r="69" spans="8:8" ht="16.9">
       <c r="A69" s="94" t="s">
         <v>256</v>
       </c>
@@ -48106,7 +48110,7 @@
       <c r="J69" s="149">
         <v>333.6</v>
       </c>
-      <c r="K69" s="104">
+      <c r="K69">
         <f>(I69+(J69*E69))/1000</f>
         <v>10.438</v>
       </c>
@@ -48128,7 +48132,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="70" spans="8:8" ht="18.0">
+    <row r="70" spans="8:8" ht="16.9">
       <c r="A70" s="94" t="s">
         <v>259</v>
       </c>
@@ -48158,7 +48162,7 @@
       <c r="J70" s="149">
         <v>36.0</v>
       </c>
-      <c r="K70" s="104">
+      <c r="K70">
         <f>(I70+(J70*E70))/1000</f>
         <v>3.878</v>
       </c>
@@ -48180,7 +48184,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="71" spans="8:8" ht="18.0">
+    <row r="71" spans="8:8" ht="16.9">
       <c r="A71" s="94" t="s">
         <v>262</v>
       </c>
@@ -48210,7 +48214,7 @@
       <c r="J71" s="149">
         <v>952.4</v>
       </c>
-      <c r="K71" s="104">
+      <c r="K71">
         <f>(I71+(J71*E71))/1000</f>
         <v>19.628</v>
       </c>
@@ -48232,7 +48236,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="72" spans="8:8" ht="18.0">
+    <row r="72" spans="8:8" ht="16.9">
       <c r="A72" s="94" t="s">
         <v>265</v>
       </c>
@@ -48262,7 +48266,7 @@
       <c r="J72" s="149">
         <v>1.6</v>
       </c>
-      <c r="K72" s="104">
+      <c r="K72">
         <f>(I72+(J72*E72))/1000</f>
         <v>1.88</v>
       </c>
@@ -48284,7 +48288,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="73" spans="8:8" ht="18.0">
+    <row r="73" spans="8:8" ht="16.9">
       <c r="A73" s="94" t="s">
         <v>268</v>
       </c>
@@ -48314,7 +48318,7 @@
       <c r="J73" s="149">
         <v>25.0</v>
       </c>
-      <c r="K73" s="104">
+      <c r="K73">
         <f>(I73+(J73*E73))/1000</f>
         <v>12.78</v>
       </c>
@@ -48336,7 +48340,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="74" spans="8:8" ht="18.0">
+    <row r="74" spans="8:8" ht="16.9">
       <c r="A74" s="94" t="s">
         <v>271</v>
       </c>
@@ -48366,7 +48370,7 @@
       <c r="J74" s="149">
         <v>52.8</v>
       </c>
-      <c r="K74" s="104">
+      <c r="K74">
         <f>(I74+(J74*E74))/1000</f>
         <v>9.22</v>
       </c>
@@ -48388,7 +48392,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="75" spans="8:8" ht="18.0">
+    <row r="75" spans="8:8" ht="16.9">
       <c r="A75" s="94" t="s">
         <v>275</v>
       </c>
@@ -48418,7 +48422,7 @@
       <c r="J75" s="149">
         <v>91.4</v>
       </c>
-      <c r="K75" s="104">
+      <c r="K75">
         <f>(I75+(J75*E75))/1000</f>
         <v>23.13</v>
       </c>
@@ -48440,7 +48444,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="76" spans="8:8" ht="18.0">
+    <row r="76" spans="8:8" ht="16.9">
       <c r="A76" s="94" t="s">
         <v>278</v>
       </c>
@@ -48470,7 +48474,7 @@
       <c r="J76" s="149">
         <v>16.0</v>
       </c>
-      <c r="K76" s="104">
+      <c r="K76">
         <f>(I76+(J76*E76))/1000</f>
         <v>3.48</v>
       </c>
@@ -48492,7 +48496,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="77" spans="8:8" ht="18.0">
+    <row r="77" spans="8:8" ht="16.9">
       <c r="A77" s="94" t="s">
         <v>281</v>
       </c>
@@ -48522,7 +48526,7 @@
       <c r="J77" s="149">
         <v>290.0</v>
       </c>
-      <c r="K77" s="104">
+      <c r="K77">
         <f>(I77+(J77*E77))/1000</f>
         <v>9.078</v>
       </c>
@@ -48544,7 +48548,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="78" spans="8:8" ht="18.0">
+    <row r="78" spans="8:8" ht="16.9">
       <c r="A78" s="94" t="s">
         <v>284</v>
       </c>
@@ -48574,7 +48578,7 @@
       <c r="J78" s="149">
         <v>198.8</v>
       </c>
-      <c r="K78" s="104">
+      <c r="K78">
         <f>(I78+(J78*E78))/1000</f>
         <v>7.9228000000000005</v>
       </c>
@@ -48596,7 +48600,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="79" spans="8:8" ht="18.0">
+    <row r="79" spans="8:8" ht="16.9">
       <c r="A79" s="94" t="s">
         <v>287</v>
       </c>
@@ -48626,7 +48630,7 @@
       <c r="J79" s="149">
         <v>198.8</v>
       </c>
-      <c r="K79" s="104">
+      <c r="K79">
         <f>(I79+(J79*E79))/1000</f>
         <v>7.9228000000000005</v>
       </c>
@@ -48650,7 +48654,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="80" spans="8:8" ht="18.0">
+    <row r="80" spans="8:8" ht="16.9">
       <c r="A80" s="94" t="s">
         <v>291</v>
       </c>
@@ -48680,7 +48684,7 @@
       <c r="J80" s="149">
         <v>128.0</v>
       </c>
-      <c r="K80" s="104">
+      <c r="K80">
         <f>(I80+(J80*E80))/1000</f>
         <v>7.678</v>
       </c>
@@ -48702,7 +48706,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="81" spans="8:8" ht="18.0">
+    <row r="81" spans="8:8" ht="16.9">
       <c r="A81" s="94" t="s">
         <v>294</v>
       </c>
@@ -48732,7 +48736,7 @@
       <c r="J81" s="149">
         <v>128.0</v>
       </c>
-      <c r="K81" s="104">
+      <c r="K81">
         <f>(I81+(J81*E81))/1000</f>
         <v>7.678</v>
       </c>
@@ -48754,7 +48758,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="82" spans="8:8" ht="18.0">
+    <row r="82" spans="8:8" ht="16.9">
       <c r="A82" s="94" t="s">
         <v>297</v>
       </c>
@@ -48784,7 +48788,7 @@
       <c r="J82" s="149">
         <v>128.0</v>
       </c>
-      <c r="K82" s="104">
+      <c r="K82">
         <f>(I82+(J82*E82))/1000</f>
         <v>7.678</v>
       </c>
@@ -48806,7 +48810,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="83" spans="8:8" ht="18.0">
+    <row r="83" spans="8:8" ht="16.9">
       <c r="A83" s="94" t="s">
         <v>300</v>
       </c>
@@ -48836,7 +48840,7 @@
       <c r="J83" s="149">
         <v>22.0</v>
       </c>
-      <c r="K83" s="104">
+      <c r="K83">
         <f>(I83+(J83*E83))/1000</f>
         <v>6.88</v>
       </c>
@@ -48858,7 +48862,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="84" spans="8:8" ht="18.0">
+    <row r="84" spans="8:8" ht="16.9">
       <c r="A84" s="94" t="s">
         <v>303</v>
       </c>
@@ -48888,7 +48892,7 @@
       <c r="J84" s="149">
         <v>110.0</v>
       </c>
-      <c r="K84" s="104">
+      <c r="K84">
         <f>(I84+(J84*E84))/1000</f>
         <v>11.28</v>
       </c>
@@ -48910,7 +48914,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="85" spans="8:8" ht="18.0">
+    <row r="85" spans="8:8" ht="16.9">
       <c r="A85" s="94" t="s">
         <v>306</v>
       </c>
@@ -48940,7 +48944,7 @@
       <c r="J85" s="149">
         <v>10.0</v>
       </c>
-      <c r="K85" s="104">
+      <c r="K85">
         <f>(I85+(J85*E85))/1000</f>
         <v>10.28</v>
       </c>
@@ -48962,7 +48966,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="86" spans="8:8" ht="18.0">
+    <row r="86" spans="8:8" ht="16.9">
       <c r="A86" s="94" t="s">
         <v>309</v>
       </c>
@@ -48992,7 +48996,7 @@
       <c r="J86" s="149">
         <v>21.0</v>
       </c>
-      <c r="K86" s="104">
+      <c r="K86">
         <f>(I86+(J86*E86))/1000</f>
         <v>8.68</v>
       </c>
@@ -49014,7 +49018,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="87" spans="8:8" ht="18.0">
+    <row r="87" spans="8:8" ht="16.9">
       <c r="A87" s="94" t="s">
         <v>312</v>
       </c>
@@ -49044,7 +49048,7 @@
       <c r="J87" s="149">
         <v>33.8</v>
       </c>
-      <c r="K87" s="104">
+      <c r="K87">
         <f>(I87+(J87*E87))/1000</f>
         <v>7.037999999999999</v>
       </c>
@@ -49066,7 +49070,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="88" spans="8:8" ht="18.0">
+    <row r="88" spans="8:8" ht="16.9">
       <c r="A88" s="94" t="s">
         <v>315</v>
       </c>
@@ -49096,7 +49100,7 @@
       <c r="J88" s="149">
         <v>40.0</v>
       </c>
-      <c r="K88" s="104">
+      <c r="K88">
         <f>(I88+(J88*E88))/1000</f>
         <v>8.278</v>
       </c>
@@ -49118,7 +49122,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="89" spans="8:8" ht="18.0">
+    <row r="89" spans="8:8" ht="16.9">
       <c r="A89" s="94" t="s">
         <v>318</v>
       </c>
@@ -49148,7 +49152,7 @@
       <c r="J89" s="149">
         <v>32.0</v>
       </c>
-      <c r="K89" s="104">
+      <c r="K89">
         <f>(I89+(J89*E89))/1000</f>
         <v>5.08</v>
       </c>
@@ -49172,7 +49176,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="90" spans="8:8" ht="18.0">
+    <row r="90" spans="8:8" ht="16.9">
       <c r="A90" s="94" t="s">
         <v>322</v>
       </c>
@@ -49202,7 +49206,7 @@
       <c r="J90" s="149">
         <v>45.0</v>
       </c>
-      <c r="K90" s="104">
+      <c r="K90">
         <f>(I90+(J90*E90))/1000</f>
         <v>7.03</v>
       </c>
@@ -49224,7 +49228,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="91" spans="8:8" ht="18.0">
+    <row r="91" spans="8:8" ht="16.9">
       <c r="A91" s="94" t="s">
         <v>325</v>
       </c>
@@ -49254,7 +49258,7 @@
       <c r="J91" s="149">
         <v>118.0</v>
       </c>
-      <c r="K91" s="104">
+      <c r="K91">
         <f>(I91+(J91*E91))/1000</f>
         <v>11.606</v>
       </c>
@@ -49276,7 +49280,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="92" spans="8:8" ht="18.0">
+    <row r="92" spans="8:8" ht="16.9">
       <c r="A92" s="94" t="s">
         <v>328</v>
       </c>
@@ -49306,7 +49310,7 @@
       <c r="J92" s="149">
         <v>90.0</v>
       </c>
-      <c r="K92" s="104">
+      <c r="K92">
         <f>(I92+(J92*E92))/1000</f>
         <v>18.28</v>
       </c>
@@ -49328,7 +49332,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="93" spans="8:8" ht="18.0">
+    <row r="93" spans="8:8" ht="16.9">
       <c r="A93" s="94" t="s">
         <v>331</v>
       </c>
@@ -49358,7 +49362,7 @@
       <c r="J93" s="149">
         <v>126.6</v>
       </c>
-      <c r="K93" s="104">
+      <c r="K93">
         <f>(I93+(J93*E93))/1000</f>
         <v>4.8172</v>
       </c>
@@ -49380,7 +49384,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="94" spans="8:8" ht="18.0">
+    <row r="94" spans="8:8" ht="16.9">
       <c r="A94" s="94" t="s">
         <v>334</v>
       </c>
@@ -49410,7 +49414,7 @@
       <c r="J94" s="149">
         <v>46.6</v>
       </c>
-      <c r="K94" s="104">
+      <c r="K94">
         <f>(I94+(J94*E94))/1000</f>
         <v>14.26</v>
       </c>
@@ -49432,7 +49436,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="95" spans="8:8" ht="18.0">
+    <row r="95" spans="8:8" ht="16.9">
       <c r="A95" s="94" t="s">
         <v>337</v>
       </c>
@@ -49462,7 +49466,7 @@
       <c r="J95" s="149">
         <v>46.6</v>
       </c>
-      <c r="K95" s="104">
+      <c r="K95">
         <f>(I95+(J95*E95))/1000</f>
         <v>14.26</v>
       </c>
@@ -49486,7 +49490,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="96" spans="8:8" ht="18.0">
+    <row r="96" spans="8:8" ht="16.9">
       <c r="A96" s="94" t="s">
         <v>341</v>
       </c>
@@ -49516,7 +49520,7 @@
       <c r="J96" s="149">
         <v>419.6</v>
       </c>
-      <c r="K96" s="104">
+      <c r="K96">
         <f>(I96+(J96*E96))/1000</f>
         <v>5.465200000000001</v>
       </c>
@@ -49538,7 +49542,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="97" spans="8:8" ht="18.0">
+    <row r="97" spans="8:8" ht="16.9">
       <c r="A97" s="94" t="s">
         <v>344</v>
       </c>
@@ -49568,7 +49572,7 @@
       <c r="J97" s="149">
         <v>14.8</v>
       </c>
-      <c r="K97" s="104">
+      <c r="K97">
         <f>(I97+(J97*E97))/1000</f>
         <v>3.832</v>
       </c>
@@ -49590,7 +49594,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="98" spans="8:8" ht="18.0">
+    <row r="98" spans="8:8" ht="16.9">
       <c r="A98" s="94" t="s">
         <v>347</v>
       </c>
@@ -49620,7 +49624,7 @@
       <c r="J98" s="149">
         <v>20.0</v>
       </c>
-      <c r="K98" s="104">
+      <c r="K98">
         <f>(I98+(J98*E98))/1000</f>
         <v>12.28</v>
       </c>
@@ -49642,7 +49646,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="99" spans="8:8" ht="18.0">
+    <row r="99" spans="8:8" ht="16.9">
       <c r="A99" s="94" t="s">
         <v>350</v>
       </c>
@@ -49672,7 +49676,7 @@
       <c r="J99" s="149">
         <v>20.0</v>
       </c>
-      <c r="K99" s="104">
+      <c r="K99">
         <f>(I99+(J99*E99))/1000</f>
         <v>12.28</v>
       </c>
@@ -49694,7 +49698,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="100" spans="8:8" ht="18.0">
+    <row r="100" spans="8:8" ht="16.9">
       <c r="A100" s="94" t="s">
         <v>353</v>
       </c>
@@ -49724,7 +49728,7 @@
       <c r="J100" s="149">
         <v>8.6</v>
       </c>
-      <c r="K100" s="104">
+      <c r="K100">
         <f>(I100+(J100*E100))/1000</f>
         <v>8.88</v>
       </c>
@@ -49746,7 +49750,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="101" spans="8:8" ht="18.0">
+    <row r="101" spans="8:8" ht="16.9">
       <c r="A101" s="94" t="s">
         <v>356</v>
       </c>
@@ -49776,7 +49780,7 @@
       <c r="J101" s="149">
         <v>14.0</v>
       </c>
-      <c r="K101" s="104">
+      <c r="K101">
         <f>(I101+(J101*E101))/1000</f>
         <v>14.28</v>
       </c>
@@ -49798,7 +49802,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="102" spans="8:8" ht="18.0">
+    <row r="102" spans="8:8" ht="16.9">
       <c r="A102" s="94" t="s">
         <v>359</v>
       </c>
@@ -49828,7 +49832,7 @@
       <c r="J102" s="149">
         <v>36.0</v>
       </c>
-      <c r="K102" s="104">
+      <c r="K102">
         <f>(I102+(J102*E102))/1000</f>
         <v>3.52</v>
       </c>
@@ -49850,7 +49854,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="103" spans="8:8" ht="18.0">
+    <row r="103" spans="8:8" ht="16.9">
       <c r="A103" s="94" t="s">
         <v>362</v>
       </c>
@@ -49880,7 +49884,7 @@
       <c r="J103" s="149">
         <v>36.0</v>
       </c>
-      <c r="K103" s="104">
+      <c r="K103">
         <f>(I103+(J103*E103))/1000</f>
         <v>3.52</v>
       </c>
@@ -49902,7 +49906,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="104" spans="8:8" ht="18.0">
+    <row r="104" spans="8:8" ht="16.9">
       <c r="A104" s="94" t="s">
         <v>365</v>
       </c>
@@ -49932,7 +49936,7 @@
       <c r="J104" s="149">
         <v>34.4</v>
       </c>
-      <c r="K104" s="104">
+      <c r="K104">
         <f>(I104+(J104*E104))/1000</f>
         <v>3.376</v>
       </c>
@@ -49954,7 +49958,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="105" spans="8:8" ht="18.0">
+    <row r="105" spans="8:8" ht="16.9">
       <c r="A105" s="94" t="s">
         <v>368</v>
       </c>
@@ -49984,7 +49988,7 @@
       <c r="J105" s="149">
         <v>34.4</v>
       </c>
-      <c r="K105" s="104">
+      <c r="K105">
         <f>(I105+(J105*E105))/1000</f>
         <v>3.376</v>
       </c>
@@ -50006,7 +50010,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="106" spans="8:8" ht="18.0">
+    <row r="106" spans="8:8" ht="16.9">
       <c r="A106" s="94" t="s">
         <v>371</v>
       </c>
@@ -50036,7 +50040,7 @@
       <c r="J106" s="149">
         <v>44.0</v>
       </c>
-      <c r="K106" s="104">
+      <c r="K106">
         <f>(I106+(J106*E106))/1000</f>
         <v>20.044</v>
       </c>
@@ -50058,7 +50062,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="107" spans="8:8" ht="18.0">
+    <row r="107" spans="8:8" ht="16.9">
       <c r="A107" s="94" t="s">
         <v>374</v>
       </c>
@@ -50088,7 +50092,7 @@
       <c r="J107" s="149">
         <v>44.0</v>
       </c>
-      <c r="K107" s="104">
+      <c r="K107">
         <f>(I107+(J107*E107))/1000</f>
         <v>20.044</v>
       </c>
@@ -50110,7 +50114,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="108" spans="8:8" ht="18.0">
+    <row r="108" spans="8:8" ht="16.9">
       <c r="A108" s="94" t="s">
         <v>377</v>
       </c>
@@ -50140,7 +50144,7 @@
       <c r="J108" s="149">
         <v>5.8</v>
       </c>
-      <c r="K108" s="104">
+      <c r="K108">
         <f>(I108+(J108*E108))/1000</f>
         <v>6.08</v>
       </c>
@@ -50162,7 +50166,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="109" spans="8:8" ht="18.0">
+    <row r="109" spans="8:8" ht="16.9">
       <c r="A109" s="94" t="s">
         <v>380</v>
       </c>
@@ -50192,7 +50196,7 @@
       <c r="J109" s="149">
         <v>38.8</v>
       </c>
-      <c r="K109" s="104">
+      <c r="K109">
         <f>(I109+(J109*E109))/1000</f>
         <v>2.1403999999999996</v>
       </c>
@@ -50214,7 +50218,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="110" spans="8:8" ht="18.0">
+    <row r="110" spans="8:8" ht="16.9">
       <c r="A110" s="94" t="s">
         <v>383</v>
       </c>
@@ -50244,7 +50248,7 @@
       <c r="J110" s="149">
         <v>163.6</v>
       </c>
-      <c r="K110" s="104">
+      <c r="K110">
         <f>(I110+(J110*E110))/1000</f>
         <v>11.890799999999999</v>
       </c>
@@ -50266,7 +50270,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="111" spans="8:8" ht="18.0">
+    <row r="111" spans="8:8" ht="16.9">
       <c r="A111" s="94" t="s">
         <v>386</v>
       </c>
@@ -50296,7 +50300,7 @@
       <c r="J111" s="149">
         <v>163.6</v>
       </c>
-      <c r="K111" s="104">
+      <c r="K111">
         <f>(I111+(J111*E111))/1000</f>
         <v>11.890799999999999</v>
       </c>
@@ -50320,7 +50324,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="112" spans="8:8" ht="18.0">
+    <row r="112" spans="8:8" ht="16.9">
       <c r="A112" s="94" t="s">
         <v>390</v>
       </c>
@@ -50350,7 +50354,7 @@
       <c r="J112" s="149">
         <v>163.6</v>
       </c>
-      <c r="K112" s="104">
+      <c r="K112">
         <f>(I112+(J112*E112))/1000</f>
         <v>11.890799999999999</v>
       </c>
@@ -50372,7 +50376,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="113" spans="8:8" ht="18.0">
+    <row r="113" spans="8:8" ht="16.9">
       <c r="A113" s="94" t="s">
         <v>393</v>
       </c>
@@ -50402,7 +50406,7 @@
       <c r="J113" s="149">
         <v>163.6</v>
       </c>
-      <c r="K113" s="104">
+      <c r="K113">
         <f>(I113+(J113*E113))/1000</f>
         <v>11.890799999999999</v>
       </c>
@@ -50426,7 +50430,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="114" spans="8:8" ht="18.0">
+    <row r="114" spans="8:8" ht="16.9">
       <c r="A114" s="94" t="s">
         <v>397</v>
       </c>
@@ -50456,7 +50460,7 @@
       <c r="J114" s="149">
         <v>308.2</v>
       </c>
-      <c r="K114" s="104">
+      <c r="K114">
         <f>(I114+(J114*E114))/1000</f>
         <v>11.3752</v>
       </c>
@@ -50478,7 +50482,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="115" spans="8:8" ht="18.0">
+    <row r="115" spans="8:8" ht="16.9">
       <c r="A115" s="94" t="s">
         <v>400</v>
       </c>
@@ -50508,7 +50512,7 @@
       <c r="J115" s="149">
         <v>308.2</v>
       </c>
-      <c r="K115" s="104">
+      <c r="K115">
         <f>(I115+(J115*E115))/1000</f>
         <v>11.3752</v>
       </c>
@@ -50530,7 +50534,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="116" spans="8:8" ht="18.0">
+    <row r="116" spans="8:8" ht="16.9">
       <c r="A116" s="94" t="s">
         <v>403</v>
       </c>
@@ -50560,7 +50564,7 @@
       <c r="J116" s="149">
         <v>92.0</v>
       </c>
-      <c r="K116" s="104">
+      <c r="K116">
         <f>(I116+(J116*E116))/1000</f>
         <v>16.938</v>
       </c>
@@ -50582,7 +50586,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="117" spans="8:8" ht="18.0">
+    <row r="117" spans="8:8" ht="16.9">
       <c r="A117" s="94" t="s">
         <v>406</v>
       </c>
@@ -50612,7 +50616,7 @@
       <c r="J117" s="149">
         <v>17.4</v>
       </c>
-      <c r="K117" s="104">
+      <c r="K117">
         <f>(I117+(J117*E117))/1000</f>
         <v>8.98</v>
       </c>
@@ -50634,7 +50638,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="118" spans="8:8" ht="18.0">
+    <row r="118" spans="8:8" ht="16.9">
       <c r="A118" s="94" t="s">
         <v>409</v>
       </c>
@@ -50664,7 +50668,7 @@
       <c r="J118" s="149">
         <v>7.2</v>
       </c>
-      <c r="K118" s="104">
+      <c r="K118">
         <f>(I118+(J118*E118))/1000</f>
         <v>7.48</v>
       </c>
@@ -50686,7 +50690,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="119" spans="8:8" ht="18.0">
+    <row r="119" spans="8:8" ht="16.9">
       <c r="A119" s="94" t="s">
         <v>412</v>
       </c>
@@ -50716,7 +50720,7 @@
       <c r="J119" s="149">
         <v>15.0</v>
       </c>
-      <c r="K119" s="104">
+      <c r="K119">
         <f>(I119+(J119*E119))/1000</f>
         <v>4.78</v>
       </c>
@@ -50738,7 +50742,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="120" spans="8:8" ht="18.0">
+    <row r="120" spans="8:8" ht="16.9">
       <c r="A120" s="94" t="s">
         <v>415</v>
       </c>
@@ -50768,7 +50772,7 @@
       <c r="J120" s="149">
         <v>93.0</v>
       </c>
-      <c r="K120" s="104">
+      <c r="K120">
         <f>(I120+(J120*E120))/1000</f>
         <v>10.696</v>
       </c>
@@ -50790,7 +50794,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="121" spans="8:8" ht="18.0">
+    <row r="121" spans="8:8" ht="16.9">
       <c r="A121" s="94" t="s">
         <v>418</v>
       </c>
@@ -50820,7 +50824,7 @@
       <c r="J121" s="149">
         <v>28.0</v>
       </c>
-      <c r="K121" s="104">
+      <c r="K121">
         <f>(I121+(J121*E121))/1000</f>
         <v>8.644</v>
       </c>
@@ -50842,7 +50846,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="122" spans="8:8" ht="18.0">
+    <row r="122" spans="8:8" ht="16.9">
       <c r="A122" s="94" t="s">
         <v>421</v>
       </c>
@@ -50872,7 +50876,7 @@
       <c r="J122" s="149">
         <v>388.2</v>
       </c>
-      <c r="K122" s="104">
+      <c r="K122">
         <f>(I122+(J122*E122))/1000</f>
         <v>3.4836</v>
       </c>
@@ -50894,7 +50898,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="123" spans="8:8" ht="18.0">
+    <row r="123" spans="8:8" ht="16.9">
       <c r="A123" s="94" t="s">
         <v>424</v>
       </c>
@@ -50924,7 +50928,7 @@
       <c r="J123" s="149">
         <v>10.2</v>
       </c>
-      <c r="K123" s="104">
+      <c r="K123">
         <f>(I123+(J123*E123))/1000</f>
         <v>10.48</v>
       </c>
@@ -50946,7 +50950,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="124" spans="8:8" ht="18.0">
+    <row r="124" spans="8:8" ht="16.9">
       <c r="A124" s="94" t="s">
         <v>427</v>
       </c>
@@ -50976,7 +50980,7 @@
       <c r="J124" s="149">
         <v>92.14</v>
       </c>
-      <c r="K124" s="104">
+      <c r="K124">
         <f>(I124+(J124*E124))/1000</f>
         <v>7.6512</v>
       </c>
@@ -50998,7 +51002,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="125" spans="8:8" ht="18.0">
+    <row r="125" spans="8:8" ht="16.9">
       <c r="A125" s="94" t="s">
         <v>430</v>
       </c>
@@ -51028,7 +51032,7 @@
       <c r="J125" s="149">
         <v>91.6</v>
       </c>
-      <c r="K125" s="104">
+      <c r="K125">
         <f>(I125+(J125*E125))/1000</f>
         <v>7.608</v>
       </c>
@@ -51050,7 +51054,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="126" spans="8:8" ht="18.0">
+    <row r="126" spans="8:8" ht="16.9">
       <c r="A126" s="94" t="s">
         <v>433</v>
       </c>
@@ -51080,7 +51084,7 @@
       <c r="J126" s="149">
         <v>212.2</v>
       </c>
-      <c r="K126" s="104">
+      <c r="K126">
         <f>(I126+(J126*E126))/1000</f>
         <v>7.168399999999999</v>
       </c>
@@ -51102,7 +51106,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="127" spans="8:8" ht="18.0">
+    <row r="127" spans="8:8" ht="16.9">
       <c r="A127" s="94" t="s">
         <v>436</v>
       </c>
@@ -51132,7 +51136,7 @@
       <c r="J127" s="149">
         <v>212.2</v>
       </c>
-      <c r="K127" s="104">
+      <c r="K127">
         <f>(I127+(J127*E127))/1000</f>
         <v>7.168399999999999</v>
       </c>
@@ -51154,7 +51158,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="128" spans="8:8" ht="18.0">
+    <row r="128" spans="8:8" ht="16.9">
       <c r="A128" s="94" t="s">
         <v>439</v>
       </c>
@@ -51184,7 +51188,7 @@
       <c r="J128" s="149">
         <v>24.6</v>
       </c>
-      <c r="K128" s="104">
+      <c r="K128">
         <f>(I128+(J128*E128))/1000</f>
         <v>4.214</v>
       </c>
@@ -51206,7 +51210,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="129" spans="8:8" ht="18.0">
+    <row r="129" spans="8:8" ht="16.9">
       <c r="A129" s="94" t="s">
         <v>442</v>
       </c>
@@ -51236,7 +51240,7 @@
       <c r="J129" s="149">
         <v>13.4</v>
       </c>
-      <c r="K129" s="104">
+      <c r="K129">
         <f>(I129+(J129*E129))/1000</f>
         <v>6.98</v>
       </c>
@@ -51258,7 +51262,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="130" spans="8:8" ht="18.0">
+    <row r="130" spans="8:8" ht="16.9">
       <c r="A130" s="94" t="s">
         <v>445</v>
       </c>
@@ -51288,7 +51292,7 @@
       <c r="J130" s="149">
         <v>414.2</v>
       </c>
-      <c r="K130" s="104">
+      <c r="K130">
         <f>(I130+(J130*E130))/1000</f>
         <v>16.946</v>
       </c>
@@ -51310,7 +51314,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="131" spans="8:8" ht="18.0">
+    <row r="131" spans="8:8" ht="16.9">
       <c r="A131" s="94" t="s">
         <v>448</v>
       </c>
@@ -51340,7 +51344,7 @@
       <c r="J131" s="149">
         <v>422.8</v>
       </c>
-      <c r="K131" s="104">
+      <c r="K131">
         <f>(I131+(J131*E131))/1000</f>
         <v>17.29</v>
       </c>
@@ -51362,7 +51366,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="132" spans="8:8" ht="18.0">
+    <row r="132" spans="8:8" ht="16.9">
       <c r="A132" s="94" t="s">
         <v>451</v>
       </c>
@@ -51392,7 +51396,7 @@
       <c r="J132" s="149">
         <v>414.2</v>
       </c>
-      <c r="K132" s="104">
+      <c r="K132">
         <f>(I132+(J132*E132))/1000</f>
         <v>16.946</v>
       </c>
@@ -51414,7 +51418,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="133" spans="8:8" ht="18.0">
+    <row r="133" spans="8:8" ht="16.9">
       <c r="A133" s="94" t="s">
         <v>454</v>
       </c>
@@ -51444,7 +51448,7 @@
       <c r="J133" s="149">
         <v>422.8</v>
       </c>
-      <c r="K133" s="104">
+      <c r="K133">
         <f>(I133+(J133*E133))/1000</f>
         <v>17.29</v>
       </c>
@@ -51466,7 +51470,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="134" spans="8:8" ht="18.0">
+    <row r="134" spans="8:8" ht="16.9">
       <c r="A134" s="94" t="s">
         <v>457</v>
       </c>
@@ -51496,7 +51500,7 @@
       <c r="J134" s="149">
         <v>33.6</v>
       </c>
-      <c r="K134" s="104">
+      <c r="K134">
         <f>(I134+(J134*E134))/1000</f>
         <v>33.88</v>
       </c>
@@ -51520,7 +51524,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="135" spans="8:8" ht="18.0">
+    <row r="135" spans="8:8" ht="16.9">
       <c r="A135" s="94" t="s">
         <v>461</v>
       </c>
@@ -51550,7 +51554,7 @@
       <c r="J135" s="149">
         <v>23.6</v>
       </c>
-      <c r="K135" s="104">
+      <c r="K135">
         <f>(I135+(J135*E135))/1000</f>
         <v>23.88</v>
       </c>
@@ -51572,7 +51576,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="136" spans="8:8" ht="18.0">
+    <row r="136" spans="8:8" ht="16.9">
       <c r="A136" s="94" t="s">
         <v>464</v>
       </c>
@@ -51602,7 +51606,7 @@
       <c r="J136" s="149">
         <v>21.6</v>
       </c>
-      <c r="K136" s="104">
+      <c r="K136">
         <f>(I136+(J136*E136))/1000</f>
         <v>21.88</v>
       </c>
@@ -51624,7 +51628,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="137" spans="8:8" ht="18.0">
+    <row r="137" spans="8:8" ht="16.9">
       <c r="A137" s="94" t="s">
         <v>467</v>
       </c>
@@ -51654,7 +51658,7 @@
       <c r="J137" s="149">
         <v>62.4</v>
       </c>
-      <c r="K137" s="104">
+      <c r="K137">
         <f>(I137+(J137*E137))/1000</f>
         <v>15.88</v>
       </c>
@@ -51676,7 +51680,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="138" spans="8:8" ht="18.0">
+    <row r="138" spans="8:8" ht="16.9">
       <c r="A138" s="94" t="s">
         <v>470</v>
       </c>
@@ -51706,7 +51710,7 @@
       <c r="J138" s="149">
         <v>10.8</v>
       </c>
-      <c r="K138" s="104">
+      <c r="K138">
         <f>(I138+(J138*E138))/1000</f>
         <v>11.08</v>
       </c>
@@ -51728,7 +51732,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="139" spans="8:8" ht="18.0">
+    <row r="139" spans="8:8" ht="16.9">
       <c r="A139" s="94" t="s">
         <v>473</v>
       </c>
@@ -51758,7 +51762,7 @@
       <c r="J139" s="149">
         <v>40.8</v>
       </c>
-      <c r="K139" s="104">
+      <c r="K139">
         <f>(I139+(J139*E139))/1000</f>
         <v>18.604</v>
       </c>
@@ -51780,7 +51784,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="140" spans="8:8" ht="18.0">
+    <row r="140" spans="8:8" ht="16.9">
       <c r="A140" s="94" t="s">
         <v>476</v>
       </c>
@@ -51810,7 +51814,7 @@
       <c r="J140" s="149">
         <v>40.8</v>
       </c>
-      <c r="K140" s="104">
+      <c r="K140">
         <f>(I140+(J140*E140))/1000</f>
         <v>18.604</v>
       </c>
@@ -51832,7 +51836,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="141" spans="8:8" ht="18.0">
+    <row r="141" spans="8:8" ht="16.9">
       <c r="A141" s="94" t="s">
         <v>479</v>
       </c>
@@ -51862,7 +51866,7 @@
       <c r="J141" s="149">
         <v>101.8</v>
       </c>
-      <c r="K141" s="104">
+      <c r="K141">
         <f>(I141+(J141*E141))/1000</f>
         <v>102.08</v>
       </c>
@@ -51884,7 +51888,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="142" spans="8:8" ht="18.0">
+    <row r="142" spans="8:8" ht="16.9">
       <c r="A142" s="94" t="s">
         <v>482</v>
       </c>
@@ -51914,7 +51918,7 @@
       <c r="J142" s="149">
         <v>72.0</v>
       </c>
-      <c r="K142" s="104">
+      <c r="K142">
         <f>(I142+(J142*E142))/1000</f>
         <v>4.312</v>
       </c>
@@ -51936,7 +51940,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="143" spans="8:8" ht="18.0">
+    <row r="143" spans="8:8" ht="16.9">
       <c r="A143" s="94" t="s">
         <v>485</v>
       </c>
@@ -51966,7 +51970,7 @@
       <c r="J143" s="149">
         <v>0.2</v>
       </c>
-      <c r="K143" s="104">
+      <c r="K143">
         <f>(I143+(J143*E143))/1000</f>
         <v>0.68</v>
       </c>
@@ -51988,7 +51992,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="144" spans="8:8" ht="18.0">
+    <row r="144" spans="8:8" ht="16.9">
       <c r="A144" s="94" t="s">
         <v>488</v>
       </c>
@@ -52018,7 +52022,7 @@
       <c r="J144" s="149">
         <v>224.8</v>
       </c>
-      <c r="K144" s="104">
+      <c r="K144">
         <f>(I144+(J144*E144))/1000</f>
         <v>13.732</v>
       </c>
@@ -52040,7 +52044,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="145" spans="8:8" ht="18.0">
+    <row r="145" spans="8:8" ht="16.9">
       <c r="A145" s="94" t="s">
         <v>491</v>
       </c>
@@ -52070,7 +52074,7 @@
       <c r="J145" s="149">
         <v>40.2</v>
       </c>
-      <c r="K145" s="104">
+      <c r="K145">
         <f>(I145+(J145*E145))/1000</f>
         <v>18.37</v>
       </c>
@@ -52092,7 +52096,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="146" spans="8:8" ht="18.0">
+    <row r="146" spans="8:8" ht="16.9">
       <c r="A146" s="94" t="s">
         <v>494</v>
       </c>
@@ -52122,7 +52126,7 @@
       <c r="J146" s="149">
         <v>106.8</v>
       </c>
-      <c r="K146" s="104">
+      <c r="K146">
         <f>(I146+(J146*E146))/1000</f>
         <v>4.55</v>
       </c>
@@ -52144,7 +52148,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="147" spans="8:8" ht="18.0">
+    <row r="147" spans="8:8" ht="16.9">
       <c r="A147" s="94" t="s">
         <v>497</v>
       </c>
@@ -52174,7 +52178,7 @@
       <c r="J147" s="149">
         <v>72.0</v>
       </c>
-      <c r="K147" s="104">
+      <c r="K147">
         <f>(I147+(J147*E147))/1000</f>
         <v>14.678</v>
       </c>
@@ -52196,7 +52200,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="148" spans="8:8" ht="18.0">
+    <row r="148" spans="8:8" ht="16.9">
       <c r="A148" s="94" t="s">
         <v>500</v>
       </c>
@@ -52226,7 +52230,7 @@
       <c r="J148" s="149">
         <v>11.2</v>
       </c>
-      <c r="K148" s="104">
+      <c r="K148">
         <f>(I148+(J148*E148))/1000</f>
         <v>8.68</v>
       </c>
@@ -52248,7 +52252,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="149" spans="8:8" ht="18.0">
+    <row r="149" spans="8:8" ht="16.9">
       <c r="A149" s="94" t="s">
         <v>503</v>
       </c>
@@ -52278,7 +52282,7 @@
       <c r="J149" s="149">
         <v>10.8</v>
       </c>
-      <c r="K149" s="104">
+      <c r="K149">
         <f>(I149+(J149*E149))/1000</f>
         <v>8.92</v>
       </c>
@@ -52300,7 +52304,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="150" spans="8:8" ht="18.0">
+    <row r="150" spans="8:8" ht="16.9">
       <c r="A150" s="94" t="s">
         <v>506</v>
       </c>
@@ -52330,7 +52334,7 @@
       <c r="J150" s="149">
         <v>28.6</v>
       </c>
-      <c r="K150" s="104">
+      <c r="K150">
         <f>(I150+(J150*E150))/1000</f>
         <v>11.72</v>
       </c>
@@ -52352,7 +52356,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="151" spans="8:8" ht="18.0">
+    <row r="151" spans="8:8" ht="16.9">
       <c r="A151" s="94" t="s">
         <v>509</v>
       </c>
@@ -52382,7 +52386,7 @@
       <c r="J151" s="149">
         <v>261.4</v>
       </c>
-      <c r="K151" s="104">
+      <c r="K151">
         <f>(I151+(J151*E151))/1000</f>
         <v>15.963999999999999</v>
       </c>
@@ -52404,7 +52408,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="152" spans="8:8" ht="18.0">
+    <row r="152" spans="8:8" ht="16.9">
       <c r="A152" s="94" t="s">
         <v>512</v>
       </c>
@@ -52434,7 +52438,7 @@
       <c r="J152" s="149">
         <v>700.8</v>
       </c>
-      <c r="K152" s="104">
+      <c r="K152">
         <f>(I152+(J152*E152))/1000</f>
         <v>15.847599999999998</v>
       </c>
@@ -52456,7 +52460,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="153" spans="8:8" ht="18.0">
+    <row r="153" spans="8:8" ht="16.9">
       <c r="A153" s="94" t="s">
         <v>515</v>
       </c>
@@ -52486,7 +52490,7 @@
       <c r="J153" s="149">
         <v>896.4</v>
       </c>
-      <c r="K153" s="104">
+      <c r="K153">
         <f>(I153+(J153*E153))/1000</f>
         <v>14.7724</v>
       </c>
@@ -52508,7 +52512,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="154" spans="8:8" ht="18.0">
+    <row r="154" spans="8:8" ht="16.9">
       <c r="A154" s="94" t="s">
         <v>518</v>
       </c>
@@ -52538,7 +52542,7 @@
       <c r="J154" s="149">
         <v>450.0</v>
       </c>
-      <c r="K154" s="104">
+      <c r="K154">
         <f>(I154+(J154*E154))/1000</f>
         <v>10.33</v>
       </c>
@@ -52560,7 +52564,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="155" spans="8:8" ht="18.0">
+    <row r="155" spans="8:8" ht="16.9">
       <c r="A155" s="94" t="s">
         <v>521</v>
       </c>
@@ -52590,7 +52594,7 @@
       <c r="J155" s="149">
         <v>34.6</v>
       </c>
-      <c r="K155" s="104">
+      <c r="K155">
         <f>(I155+(J155*E155))/1000</f>
         <v>8.93</v>
       </c>
@@ -52612,7 +52616,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="156" spans="8:8" ht="18.0">
+    <row r="156" spans="8:8" ht="16.9">
       <c r="A156" s="94" t="s">
         <v>524</v>
       </c>
@@ -52642,7 +52646,7 @@
       <c r="J156" s="149">
         <v>45.0</v>
       </c>
-      <c r="K156" s="104">
+      <c r="K156">
         <f>(I156+(J156*E156))/1000</f>
         <v>3.878</v>
       </c>
@@ -52664,7 +52668,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="157" spans="8:8" ht="18.0">
+    <row r="157" spans="8:8" ht="16.9">
       <c r="A157" s="94" t="s">
         <v>527</v>
       </c>
@@ -52694,7 +52698,7 @@
       <c r="J157" s="149">
         <v>50.0</v>
       </c>
-      <c r="K157" s="104">
+      <c r="K157">
         <f>(I157+(J157*E157))/1000</f>
         <v>10.378</v>
       </c>
@@ -52716,7 +52720,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="158" spans="8:8" ht="18.0">
+    <row r="158" spans="8:8" ht="16.9">
       <c r="A158" s="94" t="s">
         <v>530</v>
       </c>
@@ -52746,7 +52750,7 @@
       <c r="J158" s="149">
         <v>178.2</v>
       </c>
-      <c r="K158" s="104">
+      <c r="K158">
         <f>(I158+(J158*E158))/1000</f>
         <v>12.754</v>
       </c>
@@ -52768,7 +52772,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="159" spans="8:8" ht="18.0">
+    <row r="159" spans="8:8" ht="16.9">
       <c r="A159" s="94" t="s">
         <v>533</v>
       </c>
@@ -52798,7 +52802,7 @@
       <c r="J159" s="149">
         <v>90.0</v>
       </c>
-      <c r="K159" s="104">
+      <c r="K159">
         <f>(I159+(J159*E159))/1000</f>
         <v>2.438</v>
       </c>
@@ -52820,7 +52824,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="160" spans="8:8" ht="18.0">
+    <row r="160" spans="8:8" ht="16.9">
       <c r="A160" s="94" t="s">
         <v>536</v>
       </c>
@@ -52850,7 +52854,7 @@
       <c r="J160" s="149">
         <v>129.6</v>
       </c>
-      <c r="K160" s="104">
+      <c r="K160">
         <f>(I160+(J160*E160))/1000</f>
         <v>6.0804</v>
       </c>
@@ -52872,7 +52876,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="161" spans="8:8" ht="18.0">
+    <row r="161" spans="8:8" ht="16.9">
       <c r="A161" s="94" t="s">
         <v>539</v>
       </c>
@@ -52902,7 +52906,7 @@
       <c r="J161" s="149">
         <v>20.4</v>
       </c>
-      <c r="K161" s="104">
+      <c r="K161">
         <f>(I161+(J161*E161))/1000</f>
         <v>4.36</v>
       </c>
@@ -52924,7 +52928,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="162" spans="8:8" ht="18.0">
+    <row r="162" spans="8:8" ht="16.9">
       <c r="A162" s="94" t="s">
         <v>542</v>
       </c>
@@ -52954,7 +52958,7 @@
       <c r="J162" s="149">
         <v>253.2</v>
       </c>
-      <c r="K162" s="104">
+      <c r="K162">
         <f>(I162+(J162*E162))/1000</f>
         <v>10.506</v>
       </c>
@@ -52976,7 +52980,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="163" spans="8:8" ht="18.0">
+    <row r="163" spans="8:8" ht="16.9">
       <c r="A163" s="94" t="s">
         <v>545</v>
       </c>
@@ -53006,7 +53010,7 @@
       <c r="J163" s="149">
         <v>18.2</v>
       </c>
-      <c r="K163" s="104">
+      <c r="K163">
         <f>(I163+(J163*E163))/1000</f>
         <v>2.828</v>
       </c>
@@ -53028,7 +53032,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="164" spans="8:8" ht="18.0">
+    <row r="164" spans="8:8" ht="16.9">
       <c r="A164" s="94" t="s">
         <v>548</v>
       </c>
@@ -53058,7 +53062,7 @@
       <c r="J164" s="149">
         <v>18.0</v>
       </c>
-      <c r="K164" s="104">
+      <c r="K164">
         <f>(I164+(J164*E164))/1000</f>
         <v>2.8</v>
       </c>
@@ -53080,7 +53084,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="165" spans="8:8" ht="18.0">
+    <row r="165" spans="8:8" ht="16.9">
       <c r="A165" s="94" t="s">
         <v>551</v>
       </c>
@@ -53110,7 +53114,7 @@
       <c r="J165" s="149">
         <v>267.6</v>
       </c>
-      <c r="K165" s="104">
+      <c r="K165">
         <f>(I165+(J165*E165))/1000</f>
         <v>9.9136</v>
       </c>
@@ -53132,7 +53136,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="166" spans="8:8" ht="18.0">
+    <row r="166" spans="8:8" ht="16.9">
       <c r="A166" s="94" t="s">
         <v>554</v>
       </c>
@@ -53162,7 +53166,7 @@
       <c r="J166" s="149">
         <v>267.6</v>
       </c>
-      <c r="K166" s="104">
+      <c r="K166">
         <f>(I166+(J166*E166))/1000</f>
         <v>9.9136</v>
       </c>
@@ -53184,7 +53188,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="167" spans="8:8" ht="18.0">
+    <row r="167" spans="8:8" ht="16.9">
       <c r="A167" s="94" t="s">
         <v>557</v>
       </c>
@@ -53214,7 +53218,7 @@
       <c r="J167" s="149">
         <v>31.8</v>
       </c>
-      <c r="K167" s="104">
+      <c r="K167">
         <f>(I167+(J167*E167))/1000</f>
         <v>6.004</v>
       </c>
@@ -53236,7 +53240,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="168" spans="8:8" ht="18.0">
+    <row r="168" spans="8:8" ht="16.9">
       <c r="A168" s="94" t="s">
         <v>560</v>
       </c>
@@ -53266,7 +53270,7 @@
       <c r="J168" s="149">
         <v>11.8</v>
       </c>
-      <c r="K168" s="104">
+      <c r="K168">
         <f>(I168+(J168*E168))/1000</f>
         <v>9.72</v>
       </c>
@@ -53288,7 +53292,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="169" spans="8:8" ht="18.0">
+    <row r="169" spans="8:8" ht="16.9">
       <c r="A169" s="94" t="s">
         <v>563</v>
       </c>
@@ -53318,7 +53322,7 @@
       <c r="J169" s="149">
         <v>1642.2</v>
       </c>
-      <c r="K169" s="104">
+      <c r="K169">
         <f>(I169+(J169*E169))/1000</f>
         <v>9.427</v>
       </c>
@@ -53340,7 +53344,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="170" spans="8:8" ht="18.0">
+    <row r="170" spans="8:8" ht="16.9">
       <c r="A170" s="94" t="s">
         <v>567</v>
       </c>
@@ -53370,7 +53374,7 @@
       <c r="J170" s="149">
         <v>14.8</v>
       </c>
-      <c r="K170" s="104">
+      <c r="K170">
         <f>(I170+(J170*E170))/1000</f>
         <v>15.08</v>
       </c>
@@ -53392,7 +53396,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="171" spans="8:8" ht="18.0">
+    <row r="171" spans="8:8" ht="16.9">
       <c r="A171" s="94" t="s">
         <v>571</v>
       </c>
@@ -53422,7 +53426,7 @@
       <c r="J171" s="149">
         <v>14.8</v>
       </c>
-      <c r="K171" s="104">
+      <c r="K171">
         <f>(I171+(J171*E171))/1000</f>
         <v>15.08</v>
       </c>
@@ -53444,7 +53448,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="172" spans="8:8" ht="18.0">
+    <row r="172" spans="8:8" ht="16.9">
       <c r="A172" s="94" t="s">
         <v>573</v>
       </c>
@@ -53474,7 +53478,7 @@
       <c r="J172" s="149">
         <v>13.4</v>
       </c>
-      <c r="K172" s="104">
+      <c r="K172">
         <f>(I172+(J172*E172))/1000</f>
         <v>13.68</v>
       </c>
@@ -53496,7 +53500,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="173" spans="8:8" ht="18.0">
+    <row r="173" spans="8:8" ht="16.9">
       <c r="A173" s="94" t="s">
         <v>576</v>
       </c>
@@ -53526,7 +53530,7 @@
       <c r="J173" s="149">
         <v>11.2</v>
       </c>
-      <c r="K173" s="104">
+      <c r="K173">
         <f>(I173+(J173*E173))/1000</f>
         <v>7.0</v>
       </c>
@@ -53548,7 +53552,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="174" spans="8:8" ht="18.0">
+    <row r="174" spans="8:8" ht="16.9">
       <c r="A174" s="94" t="s">
         <v>579</v>
       </c>
@@ -53578,7 +53582,7 @@
       <c r="J174" s="149">
         <v>20.0</v>
       </c>
-      <c r="K174" s="104">
+      <c r="K174">
         <f>(I174+(J174*E174))/1000</f>
         <v>16.28</v>
       </c>
@@ -53600,7 +53604,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="175" spans="8:8" ht="18.0">
+    <row r="175" spans="8:8" ht="16.9">
       <c r="A175" s="94" t="s">
         <v>582</v>
       </c>
@@ -53630,7 +53634,7 @@
       <c r="J175" s="149">
         <v>4.8</v>
       </c>
-      <c r="K175" s="104">
+      <c r="K175">
         <f>(I175+(J175*E175))/1000</f>
         <v>5.08</v>
       </c>
@@ -53652,7 +53656,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="176" spans="8:8" ht="18.0">
+    <row r="176" spans="8:8" ht="16.9">
       <c r="A176" s="94" t="s">
         <v>584</v>
       </c>
@@ -53680,7 +53684,7 @@
       <c r="J176" s="149">
         <v>6.2</v>
       </c>
-      <c r="K176" s="104">
+      <c r="K176">
         <f>(I176+(J176*E176))/1000</f>
         <v>6.2</v>
       </c>
@@ -53698,7 +53702,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="177" spans="8:8" ht="18.0">
+    <row r="177" spans="8:8" ht="16.9">
       <c r="A177" s="94" t="s">
         <v>587</v>
       </c>
@@ -53728,7 +53732,7 @@
       <c r="J177" s="149">
         <v>42.0</v>
       </c>
-      <c r="K177" s="104">
+      <c r="K177">
         <f>(I177+(J177*E177))/1000</f>
         <v>22.96</v>
       </c>
@@ -53750,7 +53754,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="178" spans="8:8" ht="18.0">
+    <row r="178" spans="8:8" ht="16.9">
       <c r="A178" s="94" t="s">
         <v>589</v>
       </c>
@@ -53780,7 +53784,7 @@
       <c r="J178" s="149">
         <v>6.8</v>
       </c>
-      <c r="K178" s="104">
+      <c r="K178">
         <f>(I178+(J178*E178))/1000</f>
         <v>7.08</v>
       </c>
@@ -53800,7 +53804,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="179" spans="8:8" ht="18.0">
+    <row r="179" spans="8:8" ht="16.9">
       <c r="A179" s="94" t="s">
         <v>592</v>
       </c>
@@ -53830,7 +53834,7 @@
       <c r="J179" s="149">
         <v>12.4</v>
       </c>
-      <c r="K179" s="104">
+      <c r="K179">
         <f>(I179+(J179*E179))/1000</f>
         <v>8.96</v>
       </c>
@@ -53852,7 +53856,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="180" spans="8:8" ht="18.0">
+    <row r="180" spans="8:8" ht="16.9">
       <c r="A180" s="94" t="s">
         <v>595</v>
       </c>
@@ -53882,7 +53886,7 @@
       <c r="J180" s="149">
         <v>29.4</v>
       </c>
-      <c r="K180" s="104">
+      <c r="K180">
         <f>(I180+(J180*E180))/1000</f>
         <v>13.508</v>
       </c>
@@ -53904,7 +53908,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="181" spans="8:8" ht="18.0">
+    <row r="181" spans="8:8" ht="16.9">
       <c r="A181" s="94" t="s">
         <v>598</v>
       </c>
@@ -53934,7 +53938,7 @@
       <c r="J181" s="149">
         <v>24.8</v>
       </c>
-      <c r="K181" s="104">
+      <c r="K181">
         <f>(I181+(J181*E181))/1000</f>
         <v>18.134</v>
       </c>
@@ -53956,7 +53960,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="182" spans="8:8" ht="18.0">
+    <row r="182" spans="8:8" ht="16.9">
       <c r="A182" s="94" t="s">
         <v>601</v>
       </c>
@@ -53986,7 +53990,7 @@
       <c r="J182" s="149">
         <v>25.2</v>
       </c>
-      <c r="K182" s="104">
+      <c r="K182">
         <f>(I182+(J182*E182))/1000</f>
         <v>11.368</v>
       </c>
@@ -54008,7 +54012,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="183" spans="8:8" ht="18.0">
+    <row r="183" spans="8:8" ht="16.9">
       <c r="A183" s="94" t="s">
         <v>604</v>
       </c>
@@ -54038,7 +54042,7 @@
       <c r="J183" s="149">
         <v>23.0</v>
       </c>
-      <c r="K183" s="104">
+      <c r="K183">
         <f>(I183+(J183*E183))/1000</f>
         <v>10.63</v>
       </c>
@@ -54060,7 +54064,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="184" spans="8:8" ht="18.0">
+    <row r="184" spans="8:8" ht="16.9">
       <c r="A184" s="94" t="s">
         <v>607</v>
       </c>
@@ -54090,7 +54094,7 @@
       <c r="J184" s="149">
         <v>74.0</v>
       </c>
-      <c r="K184" s="104">
+      <c r="K184">
         <f>(I184+(J184*E184))/1000</f>
         <v>22.48</v>
       </c>
@@ -54112,7 +54116,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="185" spans="8:8" ht="18.0">
+    <row r="185" spans="8:8" ht="16.9">
       <c r="A185" s="94" t="s">
         <v>609</v>
       </c>
@@ -54142,7 +54146,7 @@
       <c r="J185" s="149">
         <v>27.6</v>
       </c>
-      <c r="K185" s="104">
+      <c r="K185">
         <f>(I185+(J185*E185))/1000</f>
         <v>9.9952</v>
       </c>
@@ -54164,7 +54168,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="186" spans="8:8" ht="18.0">
+    <row r="186" spans="8:8" ht="16.9">
       <c r="A186" s="94" t="s">
         <v>612</v>
       </c>
@@ -54194,7 +54198,7 @@
       <c r="J186" s="149">
         <v>25.4</v>
       </c>
-      <c r="K186" s="104">
+      <c r="K186">
         <f>(I186+(J186*E186))/1000</f>
         <v>11.71</v>
       </c>
@@ -54214,7 +54218,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="187" spans="8:8" ht="18.0">
+    <row r="187" spans="8:8" ht="16.9">
       <c r="A187" s="94" t="s">
         <v>615</v>
       </c>
@@ -54244,7 +54248,7 @@
       <c r="J187" s="149">
         <v>131.0</v>
       </c>
-      <c r="K187" s="104">
+      <c r="K187">
         <f>(I187+(J187*E187))/1000</f>
         <v>13.38</v>
       </c>
@@ -54266,7 +54270,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="188" spans="8:8" ht="18.0">
+    <row r="188" spans="8:8" ht="16.9">
       <c r="A188" s="94" t="s">
         <v>618</v>
       </c>
@@ -54296,7 +54300,7 @@
       <c r="J188" s="149">
         <v>32.6</v>
       </c>
-      <c r="K188" s="104">
+      <c r="K188">
         <f>(I188+(J188*E188))/1000</f>
         <v>14.948</v>
       </c>
@@ -54318,7 +54322,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="189" spans="8:8" ht="18.0">
+    <row r="189" spans="8:8" ht="16.9">
       <c r="A189" s="94" t="s">
         <v>621</v>
       </c>
@@ -54348,7 +54352,7 @@
       <c r="J189" s="149">
         <v>208.8</v>
       </c>
-      <c r="K189" s="104">
+      <c r="K189">
         <f>(I189+(J189*E189))/1000</f>
         <v>4.456</v>
       </c>
@@ -54370,7 +54374,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="190" spans="8:8" ht="18.0">
+    <row r="190" spans="8:8" ht="16.9">
       <c r="A190" s="94" t="s">
         <v>624</v>
       </c>
@@ -54400,7 +54404,7 @@
       <c r="J190" s="149">
         <v>15.0</v>
       </c>
-      <c r="K190" s="104">
+      <c r="K190">
         <f>(I190+(J190*E190))/1000</f>
         <v>16.03</v>
       </c>
@@ -54422,7 +54426,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="191" spans="8:8" ht="18.0">
+    <row r="191" spans="8:8" ht="16.9">
       <c r="A191" s="94" t="s">
         <v>627</v>
       </c>
@@ -54452,7 +54456,7 @@
       <c r="J191" s="149">
         <v>32.4</v>
       </c>
-      <c r="K191" s="104">
+      <c r="K191">
         <f>(I191+(J191*E191))/1000</f>
         <v>8.056</v>
       </c>
@@ -54474,7 +54478,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="192" spans="8:8" ht="18.0">
+    <row r="192" spans="8:8" ht="16.9">
       <c r="A192" s="94" t="s">
         <v>630</v>
       </c>
@@ -54504,7 +54508,7 @@
       <c r="J192" s="149">
         <v>32.0</v>
       </c>
-      <c r="K192" s="104">
+      <c r="K192">
         <f>(I192+(J192*E192))/1000</f>
         <v>7.96</v>
       </c>
@@ -54526,7 +54530,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="193" spans="8:8" ht="18.0">
+    <row r="193" spans="8:8" ht="16.9">
       <c r="A193" s="94" t="s">
         <v>633</v>
       </c>
@@ -54554,7 +54558,7 @@
       <c r="J193" s="149">
         <v>17.4</v>
       </c>
-      <c r="K193" s="104">
+      <c r="K193">
         <f>(I193+(J193*E193))/1000</f>
         <v>10.44</v>
       </c>
@@ -54576,7 +54580,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="194" spans="8:8" ht="18.0">
+    <row r="194" spans="8:8" ht="16.9">
       <c r="A194" s="94" t="s">
         <v>636</v>
       </c>
@@ -54604,7 +54608,7 @@
       <c r="J194" s="149">
         <v>17.4</v>
       </c>
-      <c r="K194" s="104">
+      <c r="K194">
         <f>(I194+(J194*E194))/1000</f>
         <v>10.44</v>
       </c>
@@ -54626,7 +54630,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="195" spans="8:8" ht="18.0">
+    <row r="195" spans="8:8" ht="16.9">
       <c r="A195" s="94" t="s">
         <v>638</v>
       </c>
@@ -54654,7 +54658,7 @@
       <c r="J195" s="149">
         <v>12.6</v>
       </c>
-      <c r="K195" s="104">
+      <c r="K195">
         <f>(I195+(J195*E195))/1000</f>
         <v>7.56</v>
       </c>
@@ -54674,7 +54678,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="196" spans="8:8" ht="18.0">
+    <row r="196" spans="8:8" ht="16.9">
       <c r="A196" s="94" t="s">
         <v>641</v>
       </c>
@@ -54704,7 +54708,7 @@
       <c r="J196" s="149">
         <v>20.8</v>
       </c>
-      <c r="K196" s="104">
+      <c r="K196">
         <f>(I196+(J196*E196))/1000</f>
         <v>3.4</v>
       </c>
@@ -54726,7 +54730,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="197" spans="8:8" ht="18.0">
+    <row r="197" spans="8:8" ht="16.9">
       <c r="A197" s="94" t="s">
         <v>644</v>
       </c>
@@ -54754,7 +54758,7 @@
       <c r="J197" s="149">
         <v>70.0</v>
       </c>
-      <c r="K197" s="104">
+      <c r="K197">
         <f>(I197+(J197*E197))/1000</f>
         <v>17.5</v>
       </c>
@@ -54772,7 +54776,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="198" spans="8:8" ht="18.0">
+    <row r="198" spans="8:8" ht="16.9">
       <c r="A198" s="94" t="s">
         <v>647</v>
       </c>
@@ -54802,7 +54806,7 @@
       <c r="J198" s="149">
         <v>42.4</v>
       </c>
-      <c r="K198" s="104">
+      <c r="K198">
         <f>(I198+(J198*E198))/1000</f>
         <v>21.48</v>
       </c>
@@ -54824,7 +54828,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="199" spans="8:8" ht="18.0">
+    <row r="199" spans="8:8" ht="16.9">
       <c r="A199" s="94" t="s">
         <v>650</v>
       </c>
@@ -54854,7 +54858,7 @@
       <c r="J199" s="149">
         <v>35.4</v>
       </c>
-      <c r="K199" s="104">
+      <c r="K199">
         <f>(I199+(J199*E199))/1000</f>
         <v>19.396</v>
       </c>
@@ -54876,7 +54880,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="200" spans="8:8" ht="18.0">
+    <row r="200" spans="8:8" ht="16.9">
       <c r="A200" s="94" t="s">
         <v>653</v>
       </c>
@@ -54906,7 +54910,7 @@
       <c r="J200" s="149">
         <v>35.4</v>
       </c>
-      <c r="K200" s="104">
+      <c r="K200">
         <f>(I200+(J200*E200))/1000</f>
         <v>19.396</v>
       </c>
@@ -54928,7 +54932,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="201" spans="8:8" ht="18.0">
+    <row r="201" spans="8:8" ht="16.9">
       <c r="A201" s="94" t="s">
         <v>655</v>
       </c>
@@ -54956,7 +54960,7 @@
       <c r="J201" s="149">
         <v>163.9</v>
       </c>
-      <c r="K201" s="104">
+      <c r="K201">
         <f>(I201+(J201*E201))/1000</f>
         <v>1.639</v>
       </c>
@@ -54980,7 +54984,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="202" spans="8:8" ht="18.0">
+    <row r="202" spans="8:8" ht="16.9">
       <c r="A202" s="94" t="s">
         <v>660</v>
       </c>
@@ -55008,7 +55012,7 @@
       <c r="J202" s="149">
         <v>310.2</v>
       </c>
-      <c r="K202" s="104">
+      <c r="K202">
         <f>(I202+(J202*E202))/1000</f>
         <v>3.102</v>
       </c>
@@ -55032,7 +55036,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="203" spans="8:8" ht="18.0">
+    <row r="203" spans="8:8" ht="16.9">
       <c r="A203" s="94" t="s">
         <v>664</v>
       </c>
@@ -55060,7 +55064,7 @@
       <c r="J203" s="149">
         <v>163.0</v>
       </c>
-      <c r="K203" s="104">
+      <c r="K203">
         <f>(I203+(J203*E203))/1000</f>
         <v>1.63</v>
       </c>
@@ -55084,7 +55088,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="204" spans="8:8" ht="18.0">
+    <row r="204" spans="8:8" ht="16.9">
       <c r="A204" s="94" t="s">
         <v>667</v>
       </c>
@@ -55110,7 +55114,7 @@
       <c r="J204" s="149">
         <v>44.0</v>
       </c>
-      <c r="K204" s="104">
+      <c r="K204">
         <f>(I204+(J204*E204))/1000</f>
         <v>0.0</v>
       </c>
@@ -55130,7 +55134,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="205" spans="8:8" ht="18.0">
+    <row r="205" spans="8:8" ht="16.9">
       <c r="A205" s="94" t="s">
         <v>670</v>
       </c>
@@ -55160,7 +55164,7 @@
       <c r="J205" s="149">
         <v>10.8</v>
       </c>
-      <c r="K205" s="104">
+      <c r="K205">
         <f>(I205+(J205*E205))/1000</f>
         <v>11.044</v>
       </c>
@@ -55182,7 +55186,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="206" spans="8:8" ht="18.0">
+    <row r="206" spans="8:8" ht="16.9">
       <c r="A206" s="94" t="s">
         <v>673</v>
       </c>
@@ -55212,7 +55216,7 @@
       <c r="J206" s="149">
         <v>10.2</v>
       </c>
-      <c r="K206" s="104">
+      <c r="K206">
         <f>(I206+(J206*E206))/1000</f>
         <v>10.444</v>
       </c>
@@ -55234,7 +55238,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="207" spans="8:8" ht="18.0">
+    <row r="207" spans="8:8" ht="16.9">
       <c r="A207" s="94" t="s">
         <v>676</v>
       </c>
@@ -55264,7 +55268,7 @@
       <c r="J207" s="149">
         <v>8.8</v>
       </c>
-      <c r="K207" s="104">
+      <c r="K207">
         <f>(I207+(J207*E207))/1000</f>
         <v>9.044</v>
       </c>
@@ -55286,7 +55290,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="208" spans="8:8" ht="18.0">
+    <row r="208" spans="8:8" ht="16.9">
       <c r="A208" s="94" t="s">
         <v>679</v>
       </c>
@@ -55316,7 +55320,7 @@
       <c r="J208" s="149">
         <v>8.2</v>
       </c>
-      <c r="K208" s="104">
+      <c r="K208">
         <f>(I208+(J208*E208))/1000</f>
         <v>8.444</v>
       </c>
@@ -55338,7 +55342,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="209" spans="8:8" ht="18.0">
+    <row r="209" spans="8:8" ht="16.9">
       <c r="A209" s="94" t="s">
         <v>682</v>
       </c>
@@ -55368,7 +55372,7 @@
       <c r="J209" s="149">
         <v>8.2</v>
       </c>
-      <c r="K209" s="104">
+      <c r="K209">
         <f>(I209+(J209*E209))/1000</f>
         <v>8.444</v>
       </c>
@@ -55390,7 +55394,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="210" spans="8:8" ht="18.0">
+    <row r="210" spans="8:8" ht="16.9">
       <c r="A210" s="94" t="s">
         <v>685</v>
       </c>
@@ -55420,7 +55424,7 @@
       <c r="J210" s="149">
         <v>11.4</v>
       </c>
-      <c r="K210" s="104">
+      <c r="K210">
         <f>(I210+(J210*E210))/1000</f>
         <v>11.644</v>
       </c>
@@ -55442,7 +55446,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="211" spans="8:8" ht="18.0">
+    <row r="211" spans="8:8" ht="16.9">
       <c r="A211" s="94" t="s">
         <v>688</v>
       </c>
@@ -55472,7 +55476,7 @@
       <c r="J211" s="149">
         <v>61.2</v>
       </c>
-      <c r="K211" s="104">
+      <c r="K211">
         <f>(I211+(J211*E211))/1000</f>
         <v>21.7</v>
       </c>
@@ -55494,7 +55498,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="212" spans="8:8" ht="18.0">
+    <row r="212" spans="8:8" ht="16.9">
       <c r="A212" s="94" t="s">
         <v>691</v>
       </c>
@@ -55524,7 +55528,7 @@
       <c r="J212" s="149">
         <v>11.6</v>
       </c>
-      <c r="K212" s="104">
+      <c r="K212">
         <f>(I212+(J212*E212))/1000</f>
         <v>11.844</v>
       </c>
@@ -55546,7 +55550,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="213" spans="8:8" ht="18.0">
+    <row r="213" spans="8:8" ht="16.9">
       <c r="A213" s="94" t="s">
         <v>694</v>
       </c>
@@ -55576,7 +55580,7 @@
       <c r="J213" s="149">
         <v>11.2</v>
       </c>
-      <c r="K213" s="104">
+      <c r="K213">
         <f>(I213+(J213*E213))/1000</f>
         <v>11.444</v>
       </c>
@@ -55598,7 +55602,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="214" spans="8:8" ht="18.0">
+    <row r="214" spans="8:8" ht="16.9">
       <c r="A214" s="94" t="s">
         <v>697</v>
       </c>
@@ -55628,7 +55632,7 @@
       <c r="J214" s="149">
         <v>10.4</v>
       </c>
-      <c r="K214" s="104">
+      <c r="K214">
         <f>(I214+(J214*E214))/1000</f>
         <v>10.644</v>
       </c>
@@ -55650,7 +55654,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="215" spans="8:8" ht="18.0">
+    <row r="215" spans="8:8" ht="16.9">
       <c r="A215" s="94" t="s">
         <v>700</v>
       </c>
@@ -55680,7 +55684,7 @@
       <c r="J215" s="149">
         <v>9.6</v>
       </c>
-      <c r="K215" s="104">
+      <c r="K215">
         <f>(I215+(J215*E215))/1000</f>
         <v>9.844</v>
       </c>
@@ -55702,7 +55706,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="216" spans="8:8" ht="18.0">
+    <row r="216" spans="8:8" ht="16.9">
       <c r="A216" s="94" t="s">
         <v>703</v>
       </c>
@@ -55732,7 +55736,7 @@
       <c r="J216" s="149">
         <v>12.6</v>
       </c>
-      <c r="K216" s="104">
+      <c r="K216">
         <f>(I216+(J216*E216))/1000</f>
         <v>12.844</v>
       </c>
@@ -55754,7 +55758,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="217" spans="8:8" ht="18.0">
+    <row r="217" spans="8:8" ht="16.9">
       <c r="A217" s="94" t="s">
         <v>705</v>
       </c>
@@ -55784,7 +55788,7 @@
       <c r="J217" s="149">
         <v>12.4</v>
       </c>
-      <c r="K217" s="104">
+      <c r="K217">
         <f>(I217+(J217*E217))/1000</f>
         <v>12.644</v>
       </c>
@@ -55806,7 +55810,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="218" spans="8:8" ht="18.0">
+    <row r="218" spans="8:8" ht="16.9">
       <c r="A218" s="94" t="s">
         <v>708</v>
       </c>
@@ -55836,7 +55840,7 @@
       <c r="J218" s="149">
         <v>11.6</v>
       </c>
-      <c r="K218" s="104">
+      <c r="K218">
         <f>(I218+(J218*E218))/1000</f>
         <v>11.844</v>
       </c>
@@ -55858,7 +55862,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="219" spans="8:8" ht="18.0">
+    <row r="219" spans="8:8" ht="16.9">
       <c r="A219" s="94" t="s">
         <v>710</v>
       </c>
@@ -55888,7 +55892,7 @@
       <c r="J219" s="149">
         <v>10.4</v>
       </c>
-      <c r="K219" s="104">
+      <c r="K219">
         <f>(I219+(J219*E219))/1000</f>
         <v>10.644</v>
       </c>
@@ -55910,7 +55914,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="220" spans="8:8" ht="18.0">
+    <row r="220" spans="8:8" ht="16.9">
       <c r="A220" s="94" t="s">
         <v>713</v>
       </c>
@@ -55940,7 +55944,7 @@
       <c r="J220" s="149">
         <v>22.2</v>
       </c>
-      <c r="K220" s="104">
+      <c r="K220">
         <f>(I220+(J220*E220))/1000</f>
         <v>18.004</v>
       </c>
@@ -55962,7 +55966,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="221" spans="8:8" ht="18.0">
+    <row r="221" spans="8:8" ht="16.9">
       <c r="A221" s="94" t="s">
         <v>716</v>
       </c>
@@ -55992,7 +55996,7 @@
       <c r="J221" s="149">
         <v>20.8</v>
       </c>
-      <c r="K221" s="104">
+      <c r="K221">
         <f>(I221+(J221*E221))/1000</f>
         <v>16.884</v>
       </c>
@@ -56014,7 +56018,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="222" spans="8:8" ht="18.0">
+    <row r="222" spans="8:8" ht="16.9">
       <c r="A222" s="94" t="s">
         <v>719</v>
       </c>
@@ -56044,7 +56048,7 @@
       <c r="J222" s="149">
         <v>19.2</v>
       </c>
-      <c r="K222" s="104">
+      <c r="K222">
         <f>(I222+(J222*E222))/1000</f>
         <v>15.604</v>
       </c>
@@ -56066,7 +56070,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="223" spans="8:8" ht="18.0">
+    <row r="223" spans="8:8" ht="16.9">
       <c r="A223" s="94" t="s">
         <v>722</v>
       </c>
@@ -56096,7 +56100,7 @@
       <c r="J223" s="149">
         <v>27.6</v>
       </c>
-      <c r="K223" s="104">
+      <c r="K223">
         <f>(I223+(J223*E223))/1000</f>
         <v>22.324</v>
       </c>
@@ -56118,7 +56122,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="224" spans="8:8" ht="18.0">
+    <row r="224" spans="8:8" ht="16.9">
       <c r="A224" s="94" t="s">
         <v>725</v>
       </c>
@@ -56148,7 +56152,7 @@
       <c r="J224" s="149">
         <v>23.6</v>
       </c>
-      <c r="K224" s="104">
+      <c r="K224">
         <f>(I224+(J224*E224))/1000</f>
         <v>19.124</v>
       </c>
@@ -56170,7 +56174,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="225" spans="8:8" ht="18.0">
+    <row r="225" spans="8:8" ht="16.9">
       <c r="A225" s="94" t="s">
         <v>728</v>
       </c>
@@ -56200,7 +56204,7 @@
       <c r="J225" s="149">
         <v>13.2</v>
       </c>
-      <c r="K225" s="104">
+      <c r="K225">
         <f>(I225+(J225*E225))/1000</f>
         <v>13.444</v>
       </c>
@@ -56222,7 +56226,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="226" spans="8:8" ht="18.0">
+    <row r="226" spans="8:8" ht="16.9">
       <c r="A226" s="94" t="s">
         <v>731</v>
       </c>
@@ -56252,7 +56256,7 @@
       <c r="J226" s="149">
         <v>12.2</v>
       </c>
-      <c r="K226" s="104">
+      <c r="K226">
         <f>(I226+(J226*E226))/1000</f>
         <v>12.444</v>
       </c>
@@ -56274,7 +56278,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="227" spans="8:8" ht="18.0">
+    <row r="227" spans="8:8" ht="16.9">
       <c r="A227" s="94" t="s">
         <v>733</v>
       </c>
@@ -56304,7 +56308,7 @@
       <c r="J227" s="149">
         <v>12.0</v>
       </c>
-      <c r="K227" s="104">
+      <c r="K227">
         <f>(I227+(J227*E227))/1000</f>
         <v>12.244</v>
       </c>
@@ -56326,7 +56330,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="228" spans="8:8" ht="18.0">
+    <row r="228" spans="8:8" ht="16.9">
       <c r="A228" s="94" t="s">
         <v>735</v>
       </c>
@@ -56356,7 +56360,7 @@
       <c r="J228" s="149">
         <v>10.6</v>
       </c>
-      <c r="K228" s="104">
+      <c r="K228">
         <f>(I228+(J228*E228))/1000</f>
         <v>10.844</v>
       </c>
@@ -56378,7 +56382,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="229" spans="8:8" ht="18.0">
+    <row r="229" spans="8:8" ht="16.9">
       <c r="A229" s="94" t="s">
         <v>737</v>
       </c>
@@ -56408,7 +56412,7 @@
       <c r="J229" s="149">
         <v>3.5</v>
       </c>
-      <c r="K229" s="104">
+      <c r="K229">
         <f>(I229+(J229*E229))/1000</f>
         <v>3.78</v>
       </c>
@@ -56430,7 +56434,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="230" spans="8:8" ht="18.0">
+    <row r="230" spans="8:8" ht="16.9">
       <c r="A230" s="94" t="s">
         <v>17</v>
       </c>
@@ -56460,7 +56464,7 @@
       <c r="J230" s="149">
         <v>4.2</v>
       </c>
-      <c r="K230" s="104">
+      <c r="K230">
         <f>(I230+(J230*E230))/1000</f>
         <v>4.48</v>
       </c>
@@ -56482,7 +56486,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="231" spans="8:8" ht="18.0">
+    <row r="231" spans="8:8" ht="16.9">
       <c r="A231" s="94" t="s">
         <v>742</v>
       </c>
@@ -56510,7 +56514,7 @@
       <c r="J231" s="149">
         <v>624.2</v>
       </c>
-      <c r="K231" s="104">
+      <c r="K231">
         <f>(I231+(J231*E231))/1000</f>
         <v>4.993600000000001</v>
       </c>
@@ -56528,7 +56532,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="232" spans="8:8" ht="18.0">
+    <row r="232" spans="8:8" ht="16.9">
       <c r="A232" s="94" t="s">
         <v>745</v>
       </c>
@@ -56558,7 +56562,7 @@
       <c r="J232" s="149">
         <v>832.8</v>
       </c>
-      <c r="K232" s="104">
+      <c r="K232">
         <f>(I232+(J232*E232))/1000</f>
         <v>4.93</v>
       </c>
@@ -56578,7 +56582,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="233" spans="8:8" ht="18.0">
+    <row r="233" spans="8:8" ht="16.9">
       <c r="A233" s="94" t="s">
         <v>748</v>
       </c>
@@ -56608,7 +56612,7 @@
       <c r="J233" s="149">
         <v>65.4</v>
       </c>
-      <c r="K233" s="104">
+      <c r="K233">
         <f>(I233+(J233*E233))/1000</f>
         <v>8.128</v>
       </c>
@@ -56630,7 +56634,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="234" spans="8:8" ht="18.0">
+    <row r="234" spans="8:8" ht="16.9">
       <c r="A234" s="94" t="s">
         <v>751</v>
       </c>
@@ -56658,7 +56662,7 @@
       <c r="J234" s="149">
         <v>4.8</v>
       </c>
-      <c r="K234" s="104" t="e">
+      <c r="K234" t="e">
         <f>(I234+(J234*E234))/1000</f>
         <v>#VALUE!</v>
       </c>
@@ -56676,7 +56680,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="235" spans="8:8" ht="18.0">
+    <row r="235" spans="8:8" ht="16.9">
       <c r="A235" s="94" t="s">
         <v>754</v>
       </c>
@@ -56706,7 +56710,7 @@
       <c r="J235" s="149">
         <v>30.0</v>
       </c>
-      <c r="K235" s="104">
+      <c r="K235">
         <f>(I235+(J235*E235))/1000</f>
         <v>15.28</v>
       </c>
@@ -56726,7 +56730,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="236" spans="8:8" ht="18.0">
+    <row r="236" spans="8:8" ht="16.9">
       <c r="A236" s="94" t="s">
         <v>757</v>
       </c>
@@ -56754,7 +56758,7 @@
       <c r="J236" s="149">
         <v>161.0</v>
       </c>
-      <c r="K236" s="104">
+      <c r="K236">
         <f>(I236+(J236*E236))/1000</f>
         <v>3.22</v>
       </c>
@@ -56774,7 +56778,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="237" spans="8:8" ht="18.0">
+    <row r="237" spans="8:8" ht="16.9">
       <c r="A237" s="94" t="s">
         <v>762</v>
       </c>
@@ -56804,7 +56808,7 @@
       <c r="J237" s="149">
         <v>10.8</v>
       </c>
-      <c r="K237" s="104" t="e">
+      <c r="K237" t="e">
         <f>(I237+(J237*E237))/1000</f>
         <v>#VALUE!</v>
       </c>
@@ -56826,7 +56830,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="238" spans="8:8" ht="18.0">
+    <row r="238" spans="8:8" ht="16.9">
       <c r="A238" s="94" t="s">
         <v>766</v>
       </c>
@@ -56856,7 +56860,7 @@
       <c r="J238" s="149">
         <v>12.6</v>
       </c>
-      <c r="K238" s="104">
+      <c r="K238">
         <f>(I238+(J238*E238))/1000</f>
         <v>12.844</v>
       </c>
@@ -56878,7 +56882,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="239" spans="8:8" ht="18.0">
+    <row r="239" spans="8:8" ht="16.9">
       <c r="A239" s="94" t="s">
         <v>769</v>
       </c>
@@ -56908,7 +56912,7 @@
       <c r="J239" s="149">
         <v>11.6</v>
       </c>
-      <c r="K239" s="104">
+      <c r="K239">
         <f>(I239+(J239*E239))/1000</f>
         <v>11.844</v>
       </c>
@@ -56930,7 +56934,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="240" spans="8:8" ht="18.0">
+    <row r="240" spans="8:8" ht="16.9">
       <c r="A240" s="94" t="s">
         <v>772</v>
       </c>
@@ -56960,7 +56964,7 @@
       <c r="J240" s="149">
         <v>86.0</v>
       </c>
-      <c r="K240" s="104">
+      <c r="K240">
         <f>(I240+(J240*E240))/1000</f>
         <v>5.44</v>
       </c>
@@ -56980,7 +56984,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="241" spans="8:8" ht="18.0">
+    <row r="241" spans="8:8" ht="16.9">
       <c r="A241" s="94" t="s">
         <v>775</v>
       </c>
@@ -57010,7 +57014,7 @@
       <c r="J241" s="149">
         <v>512.4</v>
       </c>
-      <c r="K241" s="104">
+      <c r="K241">
         <f>(I241+(J241*E241))/1000</f>
         <v>15.952</v>
       </c>
@@ -57030,7 +57034,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="242" spans="8:8" ht="18.0">
+    <row r="242" spans="8:8" ht="16.9">
       <c r="A242" s="94" t="s">
         <v>779</v>
       </c>
@@ -57058,7 +57062,7 @@
       <c r="J242" s="149">
         <v>217.2</v>
       </c>
-      <c r="K242" s="104">
+      <c r="K242">
         <f>(I242+(J242*E242))/1000</f>
         <v>21.72</v>
       </c>
@@ -57078,7 +57082,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="243" spans="8:8" ht="18.0">
+    <row r="243" spans="8:8" ht="16.9">
       <c r="A243" s="94" t="s">
         <v>783</v>
       </c>
@@ -57108,7 +57112,7 @@
       <c r="J243" s="149">
         <v>13.8</v>
       </c>
-      <c r="K243" s="104">
+      <c r="K243">
         <f>(I243+(J243*E243))/1000</f>
         <v>5.898</v>
       </c>
@@ -57130,7 +57134,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="244" spans="8:8" ht="18.0">
+    <row r="244" spans="8:8" ht="16.9">
       <c r="A244" s="94" t="s">
         <v>787</v>
       </c>
@@ -57158,7 +57162,7 @@
       <c r="J244" s="149">
         <v>21.2</v>
       </c>
-      <c r="K244" s="104">
+      <c r="K244">
         <f>(I244+(J244*E244))/1000</f>
         <v>12.72</v>
       </c>
@@ -57176,7 +57180,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="245" spans="8:8" ht="18.0">
+    <row r="245" spans="8:8" ht="16.9">
       <c r="A245" s="94" t="s">
         <v>791</v>
       </c>
@@ -57206,7 +57210,7 @@
       <c r="J245" s="149">
         <v>1.6</v>
       </c>
-      <c r="K245" s="104">
+      <c r="K245">
         <f>(I245+(J245*E245))/1000</f>
         <v>3.48</v>
       </c>
@@ -57228,7 +57232,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="246" spans="8:8" ht="18.0">
+    <row r="246" spans="8:8" ht="16.9">
       <c r="A246" s="94" t="s">
         <v>795</v>
       </c>
@@ -57258,7 +57262,7 @@
       <c r="J246" s="149">
         <v>13.4</v>
       </c>
-      <c r="K246" s="104">
+      <c r="K246">
         <f>(I246+(J246*E246))/1000</f>
         <v>4.3</v>
       </c>
@@ -57280,7 +57284,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="247" spans="8:8" ht="18.0">
+    <row r="247" spans="8:8" ht="16.9">
       <c r="A247" s="94" t="s">
         <v>799</v>
       </c>
@@ -57310,7 +57314,7 @@
       <c r="J247" s="149">
         <v>185.0</v>
       </c>
-      <c r="K247" s="104">
+      <c r="K247">
         <f>(I247+(J247*E247))/1000</f>
         <v>4.078</v>
       </c>
@@ -57332,7 +57336,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="248" spans="8:8" ht="18.0">
+    <row r="248" spans="8:8" ht="16.9">
       <c r="A248" s="94" t="s">
         <v>803</v>
       </c>
@@ -57360,7 +57364,7 @@
       <c r="J248" s="149">
         <v>61.0</v>
       </c>
-      <c r="K248" s="104">
+      <c r="K248">
         <f>(I248+(J248*E248))/1000</f>
         <v>0.244</v>
       </c>
@@ -57380,7 +57384,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="249" spans="8:8" ht="18.0">
+    <row r="249" spans="8:8" ht="16.9">
       <c r="A249" s="94" t="s">
         <v>805</v>
       </c>
@@ -57408,7 +57412,7 @@
       <c r="J249" s="149">
         <v>154.0</v>
       </c>
-      <c r="K249" s="104">
+      <c r="K249">
         <f>(I249+(J249*E249))/1000</f>
         <v>15.4</v>
       </c>
@@ -57430,7 +57434,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="250" spans="8:8" ht="18.0">
+    <row r="250" spans="8:8" ht="16.9">
       <c r="A250" s="94" t="s">
         <v>809</v>
       </c>
@@ -57460,7 +57464,7 @@
       <c r="J250" s="149">
         <v>98.0</v>
       </c>
-      <c r="K250" s="104">
+      <c r="K250">
         <f>(I250+(J250*E250))/1000</f>
         <v>17.92</v>
       </c>
@@ -57480,7 +57484,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="251" spans="8:8" ht="18.0">
+    <row r="251" spans="8:8" ht="16.9">
       <c r="A251" s="94" t="s">
         <v>813</v>
       </c>
@@ -57508,7 +57512,7 @@
       <c r="J251" s="149">
         <v>270.0</v>
       </c>
-      <c r="K251" s="104">
+      <c r="K251">
         <f>(I251+(J251*E251))/1000</f>
         <v>3.24</v>
       </c>
@@ -57526,7 +57530,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="252" spans="8:8" ht="18.0">
+    <row r="252" spans="8:8" ht="16.9">
       <c r="A252" s="94" t="s">
         <v>817</v>
       </c>
@@ -57556,7 +57560,7 @@
       <c r="J252" s="149">
         <v>35.4</v>
       </c>
-      <c r="K252" s="104">
+      <c r="K252">
         <f>(I252+(J252*E252))/1000</f>
         <v>19.396</v>
       </c>
@@ -57578,7 +57582,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="253" spans="8:8" ht="18.0">
+    <row r="253" spans="8:8" ht="16.9">
       <c r="A253" s="94" t="s">
         <v>819</v>
       </c>
@@ -57608,7 +57612,7 @@
       <c r="J253" s="149">
         <v>35.4</v>
       </c>
-      <c r="K253" s="104">
+      <c r="K253">
         <f>(I253+(J253*E253))/1000</f>
         <v>19.396</v>
       </c>
@@ -57630,7 +57634,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="254" spans="8:8" ht="18.0">
+    <row r="254" spans="8:8" ht="16.9">
       <c r="A254" s="94" t="s">
         <v>821</v>
       </c>
@@ -57658,7 +57662,7 @@
       <c r="J254" s="154">
         <v>1.064</v>
       </c>
-      <c r="K254" s="104">
+      <c r="K254">
         <f>(I254+(J254*E254))/1000</f>
         <v>0.029792000000000003</v>
       </c>
@@ -57676,7 +57680,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="255" spans="8:8" ht="18.0">
+    <row r="255" spans="8:8" ht="16.9">
       <c r="A255" s="94" t="s">
         <v>824</v>
       </c>
@@ -57706,7 +57710,7 @@
       <c r="J255" s="149">
         <v>1271.8</v>
       </c>
-      <c r="K255" s="104">
+      <c r="K255">
         <f>(I255+(J255*E255))/1000</f>
         <v>7.125</v>
       </c>
@@ -57726,7 +57730,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="256" spans="8:8" ht="18.0">
+    <row r="256" spans="8:8" ht="16.9">
       <c r="A256" s="94" t="s">
         <v>827</v>
       </c>
@@ -57756,7 +57760,7 @@
       <c r="J256" s="149">
         <v>520.4</v>
       </c>
-      <c r="K256" s="104">
+      <c r="K256">
         <f>(I256+(J256*E256))/1000</f>
         <v>13.8104</v>
       </c>
@@ -57776,7 +57780,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="257" spans="8:8" ht="18.0">
+    <row r="257" spans="8:8" ht="16.9">
       <c r="A257" s="94" t="s">
         <v>830</v>
       </c>
@@ -57806,7 +57810,7 @@
       <c r="J257" s="149">
         <v>210.4</v>
       </c>
-      <c r="K257" s="104">
+      <c r="K257">
         <f>(I257+(J257*E257))/1000</f>
         <v>15.106</v>
       </c>
@@ -57828,7 +57832,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="258" spans="8:8" ht="18.0">
+    <row r="258" spans="8:8" ht="16.9">
       <c r="A258" s="94" t="s">
         <v>833</v>
       </c>
@@ -57858,7 +57862,7 @@
       <c r="J258" s="149">
         <v>164.6</v>
       </c>
-      <c r="K258" s="104">
+      <c r="K258">
         <f>(I258+(J258*E258))/1000</f>
         <v>2.3531999999999997</v>
       </c>
@@ -57878,7 +57882,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="259" spans="8:8" ht="18.0">
+    <row r="259" spans="8:8" ht="16.9">
       <c r="A259" s="94" t="s">
         <v>836</v>
       </c>
@@ -57908,7 +57912,7 @@
       <c r="J259" s="155">
         <v>1.555</v>
       </c>
-      <c r="K259" s="104">
+      <c r="K259">
         <f>(I259+(J259*E259))/1000</f>
         <v>0.773775</v>
       </c>
@@ -57928,7 +57932,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="260" spans="8:8" ht="18.0">
+    <row r="260" spans="8:8" ht="16.9">
       <c r="A260" s="94" t="s">
         <v>838</v>
       </c>
@@ -57958,7 +57962,7 @@
       <c r="J260" s="149">
         <v>11.2</v>
       </c>
-      <c r="K260" s="104">
+      <c r="K260">
         <f>(I260+(J260*E260))/1000</f>
         <v>1.364</v>
       </c>
@@ -57980,7 +57984,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="261" spans="8:8" ht="18.0">
+    <row r="261" spans="8:8" ht="16.9">
       <c r="A261" s="94" t="s">
         <v>841</v>
       </c>
@@ -58010,7 +58014,7 @@
       <c r="J261" s="149">
         <v>65.2</v>
       </c>
-      <c r="K261" s="104">
+      <c r="K261">
         <f>(I261+(J261*E261))/1000</f>
         <v>4.592</v>
       </c>
@@ -58030,7 +58034,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="262" spans="8:8" ht="18.0">
+    <row r="262" spans="8:8" ht="16.9">
       <c r="A262" s="94" t="s">
         <v>844</v>
       </c>
@@ -58060,7 +58064,7 @@
       <c r="J262" s="149">
         <v>26.4</v>
       </c>
-      <c r="K262" s="104">
+      <c r="K262">
         <f>(I262+(J262*E262))/1000</f>
         <v>11.896</v>
       </c>
@@ -58082,7 +58086,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="263" spans="8:8" ht="18.0">
+    <row r="263" spans="8:8" ht="16.9">
       <c r="A263" s="94" t="s">
         <v>847</v>
       </c>
@@ -58112,7 +58116,7 @@
       <c r="J263" s="149">
         <v>24.0</v>
       </c>
-      <c r="K263" s="104">
+      <c r="K263">
         <f>(I263+(J263*E263))/1000</f>
         <v>11.08</v>
       </c>
@@ -58134,7 +58138,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="264" spans="8:8" ht="18.0">
+    <row r="264" spans="8:8" ht="16.9">
       <c r="A264" s="94" t="s">
         <v>849</v>
       </c>
@@ -58164,7 +58168,7 @@
       <c r="J264" s="149">
         <v>52.2</v>
       </c>
-      <c r="K264" s="104">
+      <c r="K264">
         <f>(I264+(J264*E264))/1000</f>
         <v>13.33</v>
       </c>
@@ -58186,7 +58190,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="265" spans="8:8" ht="18.0">
+    <row r="265" spans="8:8" ht="16.9">
       <c r="A265" s="94" t="s">
         <v>852</v>
       </c>
@@ -58216,7 +58220,7 @@
       <c r="J265" s="149">
         <v>542.6</v>
       </c>
-      <c r="K265" s="104">
+      <c r="K265">
         <f>(I265+(J265*E265))/1000</f>
         <v>16.858</v>
       </c>
@@ -58236,7 +58240,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="266" spans="8:8" ht="18.0">
+    <row r="266" spans="8:8" ht="16.9">
       <c r="A266" s="94" t="s">
         <v>856</v>
       </c>
@@ -58264,7 +58268,7 @@
         <v>280.0</v>
       </c>
       <c r="J266" s="158"/>
-      <c r="K266" s="131">
+      <c r="K266">
         <f>(I266+(J266*E266))/1000</f>
         <v>0.28</v>
       </c>
@@ -58286,7 +58290,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="267" spans="8:8" ht="18.0">
+    <row r="267" spans="8:8" ht="16.9">
       <c r="A267" s="94" t="s">
         <v>858</v>
       </c>
@@ -58316,7 +58320,7 @@
       <c r="J267" s="149">
         <v>153.5</v>
       </c>
-      <c r="K267" s="104">
+      <c r="K267">
         <f>(I267+(J267*E267))/1000</f>
         <v>6.418</v>
       </c>
@@ -58338,7 +58342,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="268" spans="8:8" ht="18.0">
+    <row r="268" spans="8:8" ht="16.9">
       <c r="A268" s="94" t="s">
         <v>862</v>
       </c>
@@ -58368,7 +58372,7 @@
       <c r="J268" s="149">
         <v>20.0</v>
       </c>
-      <c r="K268" s="104">
+      <c r="K268">
         <f>(I268+(J268*E268))/1000</f>
         <v>12.28</v>
       </c>
@@ -58390,7 +58394,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="269" spans="8:8" ht="18.0">
+    <row r="269" spans="8:8" ht="16.9">
       <c r="A269" s="94" t="s">
         <v>865</v>
       </c>
@@ -58420,7 +58424,7 @@
       <c r="J269" s="149">
         <v>153.4</v>
       </c>
-      <c r="K269" s="104">
+      <c r="K269">
         <f>(I269+(J269*E269))/1000</f>
         <v>18.786</v>
       </c>
@@ -58442,7 +58446,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="270" spans="8:8" ht="18.0">
+    <row r="270" spans="8:8" ht="16.9">
       <c r="A270" s="94" t="s">
         <v>869</v>
       </c>
@@ -58472,7 +58476,7 @@
       <c r="J270" s="149">
         <v>153.4</v>
       </c>
-      <c r="K270" s="104">
+      <c r="K270">
         <f>(I270+(J270*E270))/1000</f>
         <v>18.786</v>
       </c>
@@ -58494,7 +58498,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="271" spans="8:8" ht="18.0">
+    <row r="271" spans="8:8" ht="16.9">
       <c r="A271" s="94" t="s">
         <v>872</v>
       </c>
@@ -58520,7 +58524,7 @@
       <c r="J271" s="149">
         <v>20.0</v>
       </c>
-      <c r="K271" s="104">
+      <c r="K271">
         <f>(I271+(J271*E271))/1000</f>
         <v>0.0</v>
       </c>
@@ -58538,7 +58542,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="272" spans="8:8" ht="18.0">
+    <row r="272" spans="8:8" ht="16.9">
       <c r="A272" s="94" t="s">
         <v>876</v>
       </c>
@@ -58568,7 +58572,7 @@
       <c r="J272" s="149">
         <v>74.7</v>
       </c>
-      <c r="K272" s="104">
+      <c r="K272">
         <f>(I272+(J272*E272))/1000</f>
         <v>15.22</v>
       </c>
@@ -58590,7 +58594,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="273" spans="8:8" ht="18.0">
+    <row r="273" spans="8:8" ht="16.9">
       <c r="A273" s="94" t="s">
         <v>880</v>
       </c>
@@ -58616,7 +58620,7 @@
       <c r="J273" s="149">
         <v>212.4</v>
       </c>
-      <c r="K273" s="104">
+      <c r="K273">
         <f>(I273+(J273*E273))/1000</f>
         <v>0.0</v>
       </c>
@@ -58634,7 +58638,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="274" spans="8:8" ht="18.0">
+    <row r="274" spans="8:8" ht="16.9">
       <c r="A274" s="94" t="s">
         <v>883</v>
       </c>
@@ -58664,7 +58668,7 @@
       <c r="J274" s="149">
         <v>1046.2</v>
       </c>
-      <c r="K274" s="104">
+      <c r="K274">
         <f>(I274+(J274*E274))/1000</f>
         <v>17.319200000000002</v>
       </c>
@@ -58683,7 +58687,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="275" spans="8:8" ht="18.0">
+    <row r="275" spans="8:8" ht="16.9">
       <c r="A275" s="94" t="s">
         <v>888</v>
       </c>
@@ -58713,7 +58717,7 @@
       <c r="J275" s="149">
         <v>828.2</v>
       </c>
-      <c r="K275" s="104">
+      <c r="K275">
         <f>(I275+(J275*E275))/1000</f>
         <v>8.416</v>
       </c>
@@ -58735,7 +58739,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="276" spans="8:8" ht="18.0">
+    <row r="276" spans="8:8" ht="16.9">
       <c r="A276" s="94" t="s">
         <v>892</v>
       </c>
@@ -58765,7 +58769,7 @@
       <c r="J276" s="149">
         <v>824.6</v>
       </c>
-      <c r="K276" s="104">
+      <c r="K276">
         <f>(I276+(J276*E276))/1000</f>
         <v>8.38</v>
       </c>
@@ -58787,7 +58791,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="277" spans="8:8" ht="18.0">
+    <row r="277" spans="8:8" ht="16.9">
       <c r="A277" s="94" t="s">
         <v>895</v>
       </c>
@@ -58815,7 +58819,7 @@
       <c r="J277" s="149">
         <v>1287.8</v>
       </c>
-      <c r="K277" s="104">
+      <c r="K277">
         <f>(I277+(J277*E277))/1000</f>
         <v>12.878</v>
       </c>
@@ -58833,7 +58837,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="278" spans="8:8" ht="18.0">
+    <row r="278" spans="8:8" ht="16.9">
       <c r="A278" s="94" t="s">
         <v>898</v>
       </c>
@@ -58863,7 +58867,7 @@
       <c r="J278" s="149">
         <v>112.0</v>
       </c>
-      <c r="K278" s="104">
+      <c r="K278">
         <f>(I278+(J278*E278))/1000</f>
         <v>11.444</v>
       </c>
@@ -58885,7 +58889,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="279" spans="8:8" ht="18.0">
+    <row r="279" spans="8:8" ht="16.9">
       <c r="A279" s="94" t="s">
         <v>901</v>
       </c>
@@ -58915,7 +58919,7 @@
       <c r="J279" s="149">
         <v>112.8</v>
       </c>
-      <c r="K279" s="104">
+      <c r="K279">
         <f>(I279+(J279*E279))/1000</f>
         <v>11.524</v>
       </c>
@@ -58937,7 +58941,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="280" spans="8:8" ht="18.0">
+    <row r="280" spans="8:8" ht="16.9">
       <c r="A280" s="94" t="s">
         <v>904</v>
       </c>
@@ -58967,7 +58971,7 @@
       <c r="J280" s="149">
         <v>114.2</v>
       </c>
-      <c r="K280" s="104">
+      <c r="K280">
         <f>(I280+(J280*E280))/1000</f>
         <v>11.664</v>
       </c>
@@ -58989,7 +58993,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="281" spans="8:8" ht="18.0">
+    <row r="281" spans="8:8" ht="16.9">
       <c r="A281" s="94" t="s">
         <v>907</v>
       </c>
@@ -59019,7 +59023,7 @@
       <c r="J281" s="149">
         <v>114.2</v>
       </c>
-      <c r="K281" s="104">
+      <c r="K281">
         <f>(I281+(J281*E281))/1000</f>
         <v>11.664</v>
       </c>
@@ -59041,7 +59045,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="282" spans="8:8" ht="18.0">
+    <row r="282" spans="8:8" ht="16.9">
       <c r="A282" s="94" t="s">
         <v>910</v>
       </c>
@@ -59071,7 +59075,7 @@
       <c r="J282" s="149">
         <v>504.0</v>
       </c>
-      <c r="K282" s="104">
+      <c r="K282">
         <f>(I282+(J282*E282))/1000</f>
         <v>7.822</v>
       </c>
@@ -59093,7 +59097,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="283" spans="8:8" ht="18.0">
+    <row r="283" spans="8:8" ht="16.9">
       <c r="A283" s="94" t="s">
         <v>913</v>
       </c>
@@ -59123,7 +59127,7 @@
       <c r="J283" s="149">
         <v>32.0</v>
       </c>
-      <c r="K283" s="104">
+      <c r="K283">
         <f>(I283+(J283*E283))/1000</f>
         <v>6.68</v>
       </c>
@@ -59145,7 +59149,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="284" spans="8:8" ht="18.0">
+    <row r="284" spans="8:8" ht="16.9">
       <c r="A284" s="94" t="s">
         <v>916</v>
       </c>
@@ -59175,7 +59179,7 @@
       <c r="J284" s="149">
         <v>33.0</v>
       </c>
-      <c r="K284" s="104">
+      <c r="K284">
         <f>(I284+(J284*E284))/1000</f>
         <v>5.23</v>
       </c>
@@ -59197,7 +59201,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="285" spans="8:8" ht="18.0">
+    <row r="285" spans="8:8" ht="16.9">
       <c r="A285" s="94" t="s">
         <v>919</v>
       </c>
@@ -59227,7 +59231,7 @@
       <c r="J285" s="149">
         <v>33.0</v>
       </c>
-      <c r="K285" s="104">
+      <c r="K285">
         <f>(I285+(J285*E285))/1000</f>
         <v>5.23</v>
       </c>
@@ -59249,7 +59253,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="286" spans="8:8" ht="18.0">
+    <row r="286" spans="8:8" ht="16.9">
       <c r="A286" s="94" t="s">
         <v>922</v>
       </c>
@@ -59279,7 +59283,7 @@
       <c r="J286" s="149">
         <v>31.6</v>
       </c>
-      <c r="K286" s="104">
+      <c r="K286">
         <f>(I286+(J286*E286))/1000</f>
         <v>5.02</v>
       </c>
@@ -59301,7 +59305,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="287" spans="8:8" ht="18.0">
+    <row r="287" spans="8:8" ht="16.9">
       <c r="A287" s="94" t="s">
         <v>925</v>
       </c>
@@ -59331,7 +59335,7 @@
       <c r="J287" s="149">
         <v>31.4</v>
       </c>
-      <c r="K287" s="104">
+      <c r="K287">
         <f>(I287+(J287*E287))/1000</f>
         <v>6.56</v>
       </c>
@@ -59353,7 +59357,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="288" spans="8:8" ht="18.0">
+    <row r="288" spans="8:8" ht="16.9">
       <c r="A288" s="94" t="s">
         <v>928</v>
       </c>
@@ -59383,7 +59387,7 @@
       <c r="J288" s="149">
         <v>597.0</v>
       </c>
-      <c r="K288" s="104">
+      <c r="K288">
         <f>(I288+(J288*E288))/1000</f>
         <v>7.93</v>
       </c>
@@ -59405,7 +59409,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="289" spans="8:8" ht="18.0">
+    <row r="289" spans="8:8" ht="16.9">
       <c r="A289" s="94" t="s">
         <v>931</v>
       </c>
@@ -59435,7 +59439,7 @@
       <c r="J289" s="149">
         <v>123.4</v>
       </c>
-      <c r="K289" s="104">
+      <c r="K289">
         <f>(I289+(J289*E289))/1000</f>
         <v>17.556</v>
       </c>
@@ -59457,7 +59461,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="290" spans="8:8" ht="18.0">
+    <row r="290" spans="8:8" ht="16.9">
       <c r="A290" s="94" t="s">
         <v>934</v>
       </c>
@@ -59487,7 +59491,7 @@
       <c r="J290" s="149">
         <v>16.4</v>
       </c>
-      <c r="K290" s="104">
+      <c r="K290">
         <f>(I290+(J290*E290))/1000</f>
         <v>17.5</v>
       </c>
@@ -59509,7 +59513,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="291" spans="8:8" ht="18.0">
+    <row r="291" spans="8:8" ht="16.9">
       <c r="A291" s="94" t="s">
         <v>938</v>
       </c>
@@ -59539,7 +59543,7 @@
       <c r="J291" s="149">
         <v>206.0</v>
       </c>
-      <c r="K291" s="104">
+      <c r="K291">
         <f>(I291+(J291*E291))/1000</f>
         <v>10.166</v>
       </c>
@@ -59561,7 +59565,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="292" spans="8:8" ht="18.0">
+    <row r="292" spans="8:8" ht="16.9">
       <c r="A292" s="94" t="s">
         <v>941</v>
       </c>
@@ -59591,7 +59595,7 @@
       <c r="J292" s="149">
         <v>12.6</v>
       </c>
-      <c r="K292" s="104">
+      <c r="K292">
         <f>(I292+(J292*E292))/1000</f>
         <v>11.62</v>
       </c>
@@ -59613,7 +59617,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="293" spans="8:8" ht="18.0">
+    <row r="293" spans="8:8" ht="16.9">
       <c r="A293" s="94" t="s">
         <v>945</v>
       </c>
@@ -59643,7 +59647,7 @@
       <c r="J293" s="149">
         <v>28.0</v>
       </c>
-      <c r="K293" s="104">
+      <c r="K293">
         <f>(I293+(J293*E293))/1000</f>
         <v>8.68</v>
       </c>
@@ -59665,7 +59669,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="294" spans="8:8" ht="18.0">
+    <row r="294" spans="8:8" ht="16.9">
       <c r="A294" s="94" t="s">
         <v>948</v>
       </c>
@@ -59693,7 +59697,7 @@
       <c r="J294" s="149">
         <v>69.6</v>
       </c>
-      <c r="K294" s="104">
+      <c r="K294">
         <f>(I294+(J294*E294))/1000</f>
         <v>24.359999999999996</v>
       </c>
@@ -59713,7 +59717,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="295" spans="8:8" ht="18.0">
+    <row r="295" spans="8:8" ht="16.9">
       <c r="A295" s="94" t="s">
         <v>951</v>
       </c>
@@ -59743,7 +59747,7 @@
       <c r="J295" s="149">
         <v>36.0</v>
       </c>
-      <c r="K295" s="104">
+      <c r="K295">
         <f>(I295+(J295*E295))/1000</f>
         <v>12.88</v>
       </c>
@@ -59765,7 +59769,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="296" spans="8:8" ht="18.0">
+    <row r="296" spans="8:8" ht="16.9">
       <c r="A296" s="94" t="s">
         <v>954</v>
       </c>
@@ -59795,7 +59799,7 @@
       <c r="J296" s="149">
         <v>64.8</v>
       </c>
-      <c r="K296" s="104">
+      <c r="K296">
         <f>(I296+(J296*E296))/1000</f>
         <v>13.238</v>
       </c>
@@ -59815,7 +59819,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="297" spans="8:8" ht="18.0">
+    <row r="297" spans="8:8" ht="16.9">
       <c r="A297" s="94" t="s">
         <v>958</v>
       </c>
@@ -59845,7 +59849,7 @@
       <c r="J297" s="149">
         <v>18.0</v>
       </c>
-      <c r="K297" s="104">
+      <c r="K297">
         <f>(I297+(J297*E297))/1000</f>
         <v>8.38</v>
       </c>
@@ -59865,7 +59869,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="298" spans="8:8" ht="18.0">
+    <row r="298" spans="8:8" ht="16.9">
       <c r="A298" s="94" t="s">
         <v>961</v>
       </c>
@@ -59895,7 +59899,7 @@
       <c r="J298" s="149">
         <v>18.0</v>
       </c>
-      <c r="K298" s="104">
+      <c r="K298">
         <f>(I298+(J298*E298))/1000</f>
         <v>8.38</v>
       </c>
@@ -59915,7 +59919,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="299" spans="8:8" ht="18.0">
+    <row r="299" spans="8:8" ht="16.9">
       <c r="A299" s="94" t="s">
         <v>963</v>
       </c>
@@ -59943,7 +59947,7 @@
       <c r="J299" s="149">
         <v>160.8</v>
       </c>
-      <c r="K299" s="104">
+      <c r="K299">
         <f>(I299+(J299*E299))/1000</f>
         <v>16.080000000000002</v>
       </c>
@@ -59961,7 +59965,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="300" spans="8:8" ht="18.0">
+    <row r="300" spans="8:8" ht="16.9">
       <c r="A300" s="94" t="s">
         <v>966</v>
       </c>
@@ -59991,7 +59995,7 @@
       <c r="J300" s="154">
         <v>0.22</v>
       </c>
-      <c r="K300" s="104">
+      <c r="K300">
         <f>(I300+(J300*E300))/1000</f>
         <v>11.28</v>
       </c>
@@ -60013,7 +60017,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="301" spans="8:8" ht="18.0">
+    <row r="301" spans="8:8" ht="16.9">
       <c r="A301" s="94" t="s">
         <v>970</v>
       </c>
@@ -60043,7 +60047,7 @@
       <c r="J301" s="154">
         <v>0.25</v>
       </c>
-      <c r="K301" s="104">
+      <c r="K301">
         <f>(I301+(J301*E301))/1000</f>
         <v>12.78</v>
       </c>
@@ -60065,7 +60069,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="302" spans="8:8" ht="18.0">
+    <row r="302" spans="8:8" ht="16.9">
       <c r="A302" s="94" t="s">
         <v>973</v>
       </c>
@@ -60095,7 +60099,7 @@
       <c r="J302" s="154">
         <v>0.278</v>
       </c>
-      <c r="K302" s="104">
+      <c r="K302">
         <f>(I302+(J302*E302))/1000</f>
         <v>14.180000000000001</v>
       </c>
@@ -60117,7 +60121,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="303" spans="8:8" ht="18.0">
+    <row r="303" spans="8:8" ht="16.9">
       <c r="A303" s="94" t="s">
         <v>976</v>
       </c>
@@ -60145,7 +60149,7 @@
       <c r="J303" s="149">
         <v>3.2</v>
       </c>
-      <c r="K303" s="104">
+      <c r="K303">
         <f>(I303+(J303*E303))/1000</f>
         <v>3.2</v>
       </c>
@@ -60163,7 +60167,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="304" spans="8:8" ht="18.0">
+    <row r="304" spans="8:8" ht="16.9">
       <c r="A304" s="94" t="s">
         <v>980</v>
       </c>
@@ -60193,7 +60197,7 @@
       <c r="J304" s="149">
         <v>12.4</v>
       </c>
-      <c r="K304" s="104">
+      <c r="K304">
         <f>(I304+(J304*E304))/1000</f>
         <v>8.96</v>
       </c>
@@ -60215,7 +60219,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="305" spans="8:8" ht="18.0">
+    <row r="305" spans="8:8" ht="16.9">
       <c r="A305" s="94" t="s">
         <v>983</v>
       </c>
@@ -60245,7 +60249,7 @@
       <c r="J305" s="149">
         <v>18.0</v>
       </c>
-      <c r="K305" s="104">
+      <c r="K305">
         <f>(I305+(J305*E305))/1000</f>
         <v>8.38</v>
       </c>
@@ -60265,7 +60269,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="306" spans="8:8" ht="18.0">
+    <row r="306" spans="8:8" ht="16.9">
       <c r="A306" s="94" t="s">
         <v>985</v>
       </c>
@@ -60295,7 +60299,7 @@
       <c r="J306" s="149">
         <v>18.0</v>
       </c>
-      <c r="K306" s="104">
+      <c r="K306">
         <f>(I306+(J306*E306))/1000</f>
         <v>8.38</v>
       </c>
@@ -60315,7 +60319,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="307" spans="8:8" ht="18.0">
+    <row r="307" spans="8:8" ht="16.9">
       <c r="A307" s="94" t="s">
         <v>987</v>
       </c>
@@ -60345,7 +60349,7 @@
       <c r="J307" s="149">
         <v>14.6</v>
       </c>
-      <c r="K307" s="104">
+      <c r="K307">
         <f>(I307+(J307*E307))/1000</f>
         <v>6.85</v>
       </c>
@@ -60367,7 +60371,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="308" spans="8:8" ht="18.0">
+    <row r="308" spans="8:8" ht="16.9">
       <c r="A308" s="94" t="s">
         <v>990</v>
       </c>
@@ -60397,7 +60401,7 @@
       <c r="J308" s="149">
         <v>3.2</v>
       </c>
-      <c r="K308" s="104">
+      <c r="K308">
         <f>(I308+(J308*E308))/1000</f>
         <v>3.48</v>
       </c>
@@ -60421,7 +60425,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="309" spans="8:8" ht="18.0">
+    <row r="309" spans="8:8" ht="16.9">
       <c r="A309" s="94" t="s">
         <v>994</v>
       </c>
@@ -60449,7 +60453,7 @@
       <c r="J309" s="149">
         <v>20.2</v>
       </c>
-      <c r="K309" s="104">
+      <c r="K309">
         <f>(I309+(J309*E309))/1000</f>
         <v>16.16</v>
       </c>
@@ -60469,7 +60473,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="310" spans="8:8" ht="18.0">
+    <row r="310" spans="8:8" ht="16.9">
       <c r="A310" s="94" t="s">
         <v>997</v>
       </c>
@@ -60499,7 +60503,7 @@
       <c r="J310" s="149">
         <v>8.4</v>
       </c>
-      <c r="K310" s="104">
+      <c r="K310">
         <f>(I310+(J310*E310))/1000</f>
         <v>2.8</v>
       </c>
@@ -60521,7 +60525,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="311" spans="8:8" ht="18.0">
+    <row r="311" spans="8:8" ht="16.9">
       <c r="A311" s="94" t="s">
         <v>1000</v>
       </c>
@@ -60551,7 +60555,7 @@
       <c r="J311" s="149">
         <v>697.0</v>
       </c>
-      <c r="K311" s="104">
+      <c r="K311">
         <f>(I311+(J311*E311))/1000</f>
         <v>20.096</v>
       </c>
@@ -60571,7 +60575,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="312" spans="8:8" ht="18.0">
+    <row r="312" spans="8:8" ht="16.9">
       <c r="A312" s="94" t="s">
         <v>1005</v>
       </c>
@@ -60599,7 +60603,7 @@
       <c r="J312" s="149">
         <v>1023.0</v>
       </c>
-      <c r="K312" s="104">
+      <c r="K312">
         <f>(I312+(J312*E312))/1000</f>
         <v>4.092</v>
       </c>
@@ -60617,7 +60621,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="313" spans="8:8" ht="18.0">
+    <row r="313" spans="8:8" ht="16.9">
       <c r="A313" s="94" t="s">
         <v>1008</v>
       </c>
@@ -60645,7 +60649,7 @@
       <c r="J313" s="149">
         <v>1000.0</v>
       </c>
-      <c r="K313" s="104">
+      <c r="K313">
         <f>(I313+(J313*E313))/1000</f>
         <v>4.0</v>
       </c>
@@ -60663,7 +60667,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="314" spans="8:8" ht="18.0">
+    <row r="314" spans="8:8" ht="16.9">
       <c r="A314" s="94" t="s">
         <v>1011</v>
       </c>
@@ -60691,7 +60695,7 @@
         <v>280.0</v>
       </c>
       <c r="J314" s="158"/>
-      <c r="K314" s="104">
+      <c r="K314">
         <f>(I314+(J314*E314))/1000</f>
         <v>0.28</v>
       </c>
@@ -60711,7 +60715,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="315" spans="8:8" ht="18.0">
+    <row r="315" spans="8:8" ht="16.9">
       <c r="A315" s="94" t="s">
         <v>1015</v>
       </c>
@@ -60741,7 +60745,7 @@
       <c r="J315" s="149">
         <v>36.0</v>
       </c>
-      <c r="K315" s="104">
+      <c r="K315">
         <f>(I315+(J315*E315))/1000</f>
         <v>9.28</v>
       </c>
@@ -60763,7 +60767,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="316" spans="8:8" ht="18.0">
+    <row r="316" spans="8:8" ht="16.9">
       <c r="A316" s="94" t="s">
         <v>1019</v>
       </c>
@@ -60793,7 +60797,7 @@
       <c r="J316" s="149">
         <v>60.6</v>
       </c>
-      <c r="K316" s="104">
+      <c r="K316">
         <f>(I316+(J316*E316))/1000</f>
         <v>1.49</v>
       </c>
@@ -60813,7 +60817,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="317" spans="8:8" ht="18.0">
+    <row r="317" spans="8:8" ht="16.9">
       <c r="A317" s="94" t="s">
         <v>1022</v>
       </c>
@@ -60843,7 +60847,7 @@
       <c r="J317" s="149">
         <v>171.2</v>
       </c>
-      <c r="K317" s="104">
+      <c r="K317">
         <f>(I317+(J317*E317))/1000</f>
         <v>11.038</v>
       </c>
@@ -60863,7 +60867,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="318" spans="8:8" ht="18.0">
+    <row r="318" spans="8:8" ht="16.9">
       <c r="A318" s="94" t="s">
         <v>1025</v>
       </c>
@@ -60891,7 +60895,7 @@
       <c r="J318" s="149">
         <v>67.0</v>
       </c>
-      <c r="K318" s="104">
+      <c r="K318">
         <f>(I318+(J318*E318))/1000</f>
         <v>8.04</v>
       </c>
@@ -60911,7 +60915,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="319" spans="8:8" ht="18.0">
+    <row r="319" spans="8:8" ht="16.9">
       <c r="A319" s="94" t="s">
         <v>1028</v>
       </c>
@@ -60941,7 +60945,7 @@
       <c r="J319" s="149">
         <v>143.2</v>
       </c>
-      <c r="K319" s="104">
+      <c r="K319">
         <f>(I319+(J319*E319))/1000</f>
         <v>12.794799999999999</v>
       </c>
@@ -60963,7 +60967,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="320" spans="8:8" ht="18.0">
+    <row r="320" spans="8:8" ht="16.9">
       <c r="A320" s="94" t="s">
         <v>1031</v>
       </c>
@@ -60993,7 +60997,7 @@
       <c r="J320" s="149">
         <v>164.2</v>
       </c>
-      <c r="K320" s="104">
+      <c r="K320">
         <f>(I320+(J320*E320))/1000</f>
         <v>5.5324</v>
       </c>
@@ -61013,7 +61017,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="321" spans="8:8" ht="18.0">
+    <row r="321" spans="8:8" ht="16.9">
       <c r="A321" s="94" t="s">
         <v>1034</v>
       </c>
@@ -61041,7 +61045,7 @@
       <c r="J321" s="149">
         <v>1.6</v>
       </c>
-      <c r="K321" s="104">
+      <c r="K321">
         <f>(I321+(J321*E321))/1000</f>
         <v>3.2</v>
       </c>
@@ -61063,7 +61067,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="322" spans="8:8" ht="18.0">
+    <row r="322" spans="8:8" ht="16.9">
       <c r="A322" s="94" t="s">
         <v>1037</v>
       </c>
@@ -61091,7 +61095,7 @@
       <c r="J322" s="149">
         <v>33.6</v>
       </c>
-      <c r="K322" s="104">
+      <c r="K322">
         <f>(I322+(J322*E322))/1000</f>
         <v>13.44</v>
       </c>
@@ -61111,7 +61115,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="323" spans="8:8" ht="18.0">
+    <row r="323" spans="8:8" ht="16.9">
       <c r="A323" s="94" t="s">
         <v>1041</v>
       </c>
@@ -61141,7 +61145,7 @@
       <c r="J323" s="149">
         <v>64.6</v>
       </c>
-      <c r="K323" s="104">
+      <c r="K323">
         <f>(I323+(J323*E323))/1000</f>
         <v>16.657199999999996</v>
       </c>
@@ -61161,7 +61165,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="324" spans="8:8" ht="18.0">
+    <row r="324" spans="8:8" ht="16.9">
       <c r="A324" s="94" t="s">
         <v>1044</v>
       </c>
@@ -61191,7 +61195,7 @@
       <c r="J324" s="149">
         <v>59.8</v>
       </c>
-      <c r="K324" s="104">
+      <c r="K324">
         <f>(I324+(J324*E324))/1000</f>
         <v>12.24</v>
       </c>
@@ -61211,7 +61215,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="325" spans="8:8" ht="18.0">
+    <row r="325" spans="8:8" ht="16.9">
       <c r="A325" s="94" t="s">
         <v>1047</v>
       </c>
@@ -61241,7 +61245,7 @@
       <c r="J325" s="149">
         <v>3.6</v>
       </c>
-      <c r="K325" s="104">
+      <c r="K325">
         <f>(I325+(J325*E325))/1000</f>
         <v>3.88</v>
       </c>
@@ -61261,7 +61265,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="326" spans="8:8" ht="18.0">
+    <row r="326" spans="8:8" ht="16.9">
       <c r="A326" s="94" t="s">
         <v>1050</v>
       </c>
@@ -61289,7 +61293,7 @@
       <c r="J326" s="149">
         <v>79.8</v>
       </c>
-      <c r="K326" s="104">
+      <c r="K326">
         <f>(I326+(J326*E326))/1000</f>
         <v>6.7032</v>
       </c>
@@ -61307,7 +61311,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="327" spans="8:8" ht="18.0">
+    <row r="327" spans="8:8" ht="16.9">
       <c r="A327" s="111" t="s">
         <v>1053</v>
       </c>
@@ -61337,7 +61341,7 @@
       <c r="J327" s="149">
         <v>19.8</v>
       </c>
-      <c r="K327" s="104">
+      <c r="K327">
         <f>(I327+(J327*E327))/1000</f>
         <v>0.7926799999999999</v>
       </c>
@@ -61357,7 +61361,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="328" spans="8:8" ht="18.0">
+    <row r="328" spans="8:8" ht="16.9">
       <c r="A328" s="111" t="s">
         <v>1057</v>
       </c>
@@ -61387,7 +61391,7 @@
       <c r="J328" s="149">
         <v>37.0</v>
       </c>
-      <c r="K328" s="104">
+      <c r="K328">
         <f>(I328+(J328*E328))/1000</f>
         <v>9.53</v>
       </c>
@@ -61409,7 +61413,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="329" spans="8:8" ht="18.0">
+    <row r="329" spans="8:8" ht="16.9">
       <c r="A329" s="111" t="s">
         <v>1060</v>
       </c>
@@ -61439,7 +61443,7 @@
       <c r="J329" s="149">
         <v>28.8</v>
       </c>
-      <c r="K329" s="104">
+      <c r="K329">
         <f>(I329+(J329*E329))/1000</f>
         <v>19.684</v>
       </c>
@@ -61461,7 +61465,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="330" spans="8:8" ht="18.0">
+    <row r="330" spans="8:8" ht="16.9">
       <c r="A330" s="111" t="s">
         <v>1063</v>
       </c>
@@ -61491,7 +61495,7 @@
       <c r="J330" s="149">
         <v>59.6</v>
       </c>
-      <c r="K330" s="104">
+      <c r="K330">
         <f>(I330+(J330*E330))/1000</f>
         <v>14.584</v>
       </c>
@@ -61513,7 +61517,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="331" spans="8:8" ht="18.0">
+    <row r="331" spans="8:8" ht="16.9">
       <c r="A331" s="111" t="s">
         <v>1065</v>
       </c>
@@ -61541,7 +61545,7 @@
       <c r="J331" s="149">
         <v>462.0</v>
       </c>
-      <c r="K331" s="104">
+      <c r="K331">
         <f>(I331+(J331*E331))/1000</f>
         <v>0.58</v>
       </c>
@@ -61561,7 +61565,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="332" spans="8:8" ht="18.0">
+    <row r="332" spans="8:8" ht="16.9">
       <c r="A332" s="111" t="s">
         <v>1069</v>
       </c>
@@ -61589,7 +61593,7 @@
       <c r="J332" s="149">
         <v>802.0</v>
       </c>
-      <c r="K332" s="104">
+      <c r="K332">
         <f>(I332+(J332*E332))/1000</f>
         <v>0.58</v>
       </c>
@@ -61609,7 +61613,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="333" spans="8:8" ht="18.0">
+    <row r="333" spans="8:8" ht="16.9">
       <c r="A333" s="111" t="s">
         <v>1073</v>
       </c>
@@ -61637,7 +61641,7 @@
         <v>2112.0</v>
       </c>
       <c r="J333" s="158"/>
-      <c r="K333" s="104">
+      <c r="K333">
         <f>(I333+(J333*E333))/1000</f>
         <v>2.112</v>
       </c>
@@ -61657,7 +61661,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="334" spans="8:8" ht="18.0">
+    <row r="334" spans="8:8" ht="16.9">
       <c r="A334" s="111" t="s">
         <v>1078</v>
       </c>
@@ -61683,7 +61687,7 @@
       </c>
       <c r="I334" s="148"/>
       <c r="J334" s="158"/>
-      <c r="K334" s="104" t="e">
+      <c r="K334" t="e">
         <f>(I334+(J334*E334))/1000</f>
         <v>#VALUE!</v>
       </c>
@@ -61701,7 +61705,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="335" spans="8:8" ht="18.0">
+    <row r="335" spans="8:8" ht="16.9">
       <c r="A335" s="111" t="s">
         <v>1083</v>
       </c>
@@ -61727,7 +61731,7 @@
       </c>
       <c r="I335" s="148"/>
       <c r="J335" s="158"/>
-      <c r="K335" s="104" t="e">
+      <c r="K335" t="e">
         <f>(I335+(J335*E335))/1000</f>
         <v>#VALUE!</v>
       </c>
@@ -61745,7 +61749,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="336" spans="8:8" ht="18.0">
+    <row r="336" spans="8:8" ht="16.9">
       <c r="A336" s="111" t="s">
         <v>1086</v>
       </c>
@@ -61771,7 +61775,7 @@
       </c>
       <c r="I336" s="148"/>
       <c r="J336" s="158"/>
-      <c r="K336" s="104">
+      <c r="K336">
         <f>(I336+(J336*E336))/1000</f>
         <v>0.0</v>
       </c>
@@ -61789,7 +61793,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="337" spans="8:8" ht="18.0">
+    <row r="337" spans="8:8" ht="16.9">
       <c r="A337" s="111" t="s">
         <v>1090</v>
       </c>
@@ -61819,7 +61823,7 @@
       <c r="J337" s="149">
         <v>262.0</v>
       </c>
-      <c r="K337" s="104">
+      <c r="K337">
         <f>(I337+(J337*E337))/1000</f>
         <v>8.29</v>
       </c>
@@ -61843,7 +61847,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="338" spans="8:8" ht="18.0">
+    <row r="338" spans="8:8" ht="16.9">
       <c r="A338" s="111" t="s">
         <v>1094</v>
       </c>
@@ -61873,7 +61877,7 @@
       <c r="J338" s="149">
         <v>2863.0</v>
       </c>
-      <c r="K338" s="104">
+      <c r="K338">
         <f>(I338+(J338*E338))/1000</f>
         <v>3.02</v>
       </c>
@@ -61895,7 +61899,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="339" spans="8:8" ht="18.0">
+    <row r="339" spans="8:8" ht="16.9">
       <c r="A339" s="111" t="s">
         <v>1099</v>
       </c>
@@ -61921,7 +61925,7 @@
         <v>13.4</v>
       </c>
       <c r="J339" s="158"/>
-      <c r="K339" s="104">
+      <c r="K339">
         <f>(I339+(J339*E339))/1000</f>
         <v>0.0134</v>
       </c>
@@ -61943,7 +61947,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="340" spans="8:8" ht="18.0">
+    <row r="340" spans="8:8" ht="16.9">
       <c r="A340" s="111" t="s">
         <v>1102</v>
       </c>
@@ -61973,7 +61977,7 @@
       <c r="J340" s="149">
         <v>16.3</v>
       </c>
-      <c r="K340" s="104" t="e">
+      <c r="K340" t="e">
         <f>(I340+(J340*E340))/1000</f>
         <v>#VALUE!</v>
       </c>
@@ -61993,7 +61997,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="341" spans="8:8" ht="18.0">
+    <row r="341" spans="8:8" ht="16.9">
       <c r="A341" s="111" t="s">
         <v>1104</v>
       </c>
@@ -62023,7 +62027,7 @@
       <c r="J341" s="149">
         <v>20.0</v>
       </c>
-      <c r="K341" s="104">
+      <c r="K341">
         <f>(I341+(J341*E341))/1000</f>
         <v>9.844</v>
       </c>
@@ -62045,7 +62049,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="342" spans="8:8" ht="18.0">
+    <row r="342" spans="8:8" ht="16.9">
       <c r="A342" s="111" t="s">
         <v>1108</v>
       </c>
@@ -62075,7 +62079,7 @@
       <c r="J342" s="149">
         <v>262.0</v>
       </c>
-      <c r="K342" s="104">
+      <c r="K342">
         <f>(I342+(J342*E342))/1000</f>
         <v>8.29</v>
       </c>
@@ -62097,7 +62101,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="343" spans="8:8" ht="18.0">
+    <row r="343" spans="8:8" ht="16.9">
       <c r="A343" s="111" t="s">
         <v>1110</v>
       </c>
@@ -62125,7 +62129,7 @@
       <c r="J343" s="149">
         <v>76.0</v>
       </c>
-      <c r="K343" s="104">
+      <c r="K343">
         <f>(I343+(J343*E343))/1000</f>
         <v>0.244</v>
       </c>
@@ -62147,7 +62151,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="344" spans="8:8" ht="18.0">
+    <row r="344" spans="8:8" ht="16.9">
       <c r="A344" s="111" t="s">
         <v>1114</v>
       </c>
@@ -62175,7 +62179,7 @@
       <c r="J344" s="149">
         <v>72.0</v>
       </c>
-      <c r="K344" s="104">
+      <c r="K344">
         <f>(I344+(J344*E344))/1000</f>
         <v>0.244</v>
       </c>
@@ -62197,7 +62201,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="345" spans="8:8" ht="18.0">
+    <row r="345" spans="8:8" ht="16.9">
       <c r="A345" s="111" t="s">
         <v>1118</v>
       </c>
@@ -62227,7 +62231,7 @@
       <c r="J345" s="149">
         <v>28.5</v>
       </c>
-      <c r="K345" s="104">
+      <c r="K345">
         <f>(I345+(J345*E345))/1000</f>
         <v>23.08</v>
       </c>
@@ -62249,7 +62253,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="346" spans="8:8" ht="18.0">
+    <row r="346" spans="8:8" ht="16.9">
       <c r="A346" s="111" t="s">
         <v>1122</v>
       </c>
@@ -62279,7 +62283,7 @@
       <c r="J346" s="149">
         <v>152.6</v>
       </c>
-      <c r="K346" s="104">
+      <c r="K346">
         <v>0.28</v>
       </c>
       <c r="L346" s="113" t="s">
@@ -62300,7 +62304,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="347" spans="8:8" ht="18.0">
+    <row r="347" spans="8:8" ht="16.9">
       <c r="A347" s="111" t="s">
         <v>1124</v>
       </c>
@@ -62330,7 +62334,7 @@
       <c r="J347" s="149">
         <v>152.6</v>
       </c>
-      <c r="K347" s="104">
+      <c r="K347">
         <v>0.28</v>
       </c>
       <c r="L347" s="113" t="s">
@@ -62351,7 +62355,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="348" spans="8:8" ht="18.0">
+    <row r="348" spans="8:8" ht="16.9">
       <c r="A348" s="111" t="s">
         <v>1125</v>
       </c>
@@ -62380,7 +62384,7 @@
       <c r="J348" s="149">
         <v>459.0</v>
       </c>
-      <c r="K348" s="104">
+      <c r="K348">
         <v>0.58</v>
       </c>
       <c r="L348" s="113" t="s">
@@ -62400,7 +62404,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="349" spans="8:8" ht="18.0">
+    <row r="349" spans="8:8" ht="16.9">
       <c r="A349" s="111" t="s">
         <v>1128</v>
       </c>
@@ -62430,7 +62434,7 @@
       <c r="J349" s="149">
         <v>19.5</v>
       </c>
-      <c r="K349" s="104">
+      <c r="K349">
         <f>(I349+(J349*E349))/1000</f>
         <v>8.08</v>
       </c>
@@ -62452,7 +62456,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="350" spans="8:8" ht="18.0">
+    <row r="350" spans="8:8" ht="16.9">
       <c r="A350" s="111" t="s">
         <v>1131</v>
       </c>
@@ -62482,7 +62486,7 @@
       <c r="J350" s="149">
         <v>19.5</v>
       </c>
-      <c r="K350" s="104">
+      <c r="K350">
         <f>(I350+(J350*E350))/1000</f>
         <v>8.08</v>
       </c>
@@ -62504,7 +62508,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="351" spans="8:8" ht="18.0">
+    <row r="351" spans="8:8" ht="16.9">
       <c r="A351" s="111" t="s">
         <v>1134</v>
       </c>
@@ -62534,7 +62538,7 @@
       <c r="J351" s="149">
         <v>76.5</v>
       </c>
-      <c r="K351" s="104">
+      <c r="K351">
         <f>(I351+(J351*E351))/1000</f>
         <v>19.369</v>
       </c>
@@ -62556,7 +62560,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="352" spans="8:8" ht="18.0">
+    <row r="352" spans="8:8" ht="16.9">
       <c r="A352" s="111" t="s">
         <v>1136</v>
       </c>
@@ -62586,7 +62590,7 @@
       <c r="J352" s="149">
         <v>438.0</v>
       </c>
-      <c r="K352" s="104">
+      <c r="K352">
         <f>(I352+(J352*E352))/1000</f>
         <v>12.642</v>
       </c>
@@ -62608,7 +62612,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="353" spans="8:8" ht="18.0">
+    <row r="353" spans="8:8" ht="16.9">
       <c r="A353" s="111" t="s">
         <v>1139</v>
       </c>
@@ -62638,7 +62642,7 @@
       <c r="J353" s="149">
         <v>82.5</v>
       </c>
-      <c r="K353" s="104">
+      <c r="K353">
         <f>(I353+(J353*E353))/1000</f>
         <v>3.678</v>
       </c>
@@ -62660,7 +62664,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="354" spans="8:8" ht="18.0">
+    <row r="354" spans="8:8" ht="16.9">
       <c r="A354" s="111" t="s">
         <v>1142</v>
       </c>
@@ -62690,7 +62694,7 @@
       <c r="J354" s="149">
         <v>40.5</v>
       </c>
-      <c r="K354" s="104">
+      <c r="K354">
         <f>(I354+(J354*E354))/1000</f>
         <v>3.78</v>
       </c>
@@ -62712,7 +62716,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="355" spans="8:8" ht="18.0">
+    <row r="355" spans="8:8" ht="16.9">
       <c r="A355" s="111" t="s">
         <v>1144</v>
       </c>
@@ -62742,7 +62746,7 @@
       <c r="J355" s="149">
         <v>76.0</v>
       </c>
-      <c r="K355" s="104">
+      <c r="K355">
         <f>(I355+(J355*E355))/1000</f>
         <v>6.324</v>
       </c>
@@ -62764,7 +62768,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="356" spans="8:8" ht="18.0">
+    <row r="356" spans="8:8" ht="16.9">
       <c r="A356" s="111" t="s">
         <v>1147</v>
       </c>
@@ -62794,7 +62798,7 @@
       <c r="J356" s="149">
         <v>22.0</v>
       </c>
-      <c r="K356" s="104">
+      <c r="K356">
         <f>(I356+(J356*E356))/1000</f>
         <v>11.244</v>
       </c>
@@ -62816,7 +62820,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="357" spans="8:8" ht="18.0">
+    <row r="357" spans="8:8" ht="16.9">
       <c r="A357" s="111" t="s">
         <v>1150</v>
       </c>
@@ -62846,7 +62850,7 @@
       <c r="J357" s="149">
         <v>16.5</v>
       </c>
-      <c r="K357" s="104">
+      <c r="K357">
         <f>(I357+(J357*E357))/1000</f>
         <v>2.224</v>
       </c>
@@ -62868,7 +62872,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="358" spans="8:8" ht="18.0">
+    <row r="358" spans="8:8" ht="16.9">
       <c r="A358" s="111" t="s">
         <v>1153</v>
       </c>
@@ -62898,7 +62902,7 @@
       <c r="J358" s="149">
         <v>20.0</v>
       </c>
-      <c r="K358" s="104">
+      <c r="K358">
         <f>(I358+(J358*E358))/1000</f>
         <v>1.078</v>
       </c>
@@ -62920,7 +62924,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="359" spans="8:8" ht="18.0">
+    <row r="359" spans="8:8" ht="16.9">
       <c r="A359" s="111" t="s">
         <v>1156</v>
       </c>
@@ -62950,7 +62954,7 @@
       <c r="J359" s="149">
         <v>8.0</v>
       </c>
-      <c r="K359" s="104">
+      <c r="K359">
         <f>(I359+(J359*E359))/1000</f>
         <v>4.278</v>
       </c>
@@ -62972,7 +62976,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="360" spans="8:8" ht="18.0">
+    <row r="360" spans="8:8" ht="16.9">
       <c r="A360" s="111" t="s">
         <v>1159</v>
       </c>
@@ -63002,7 +63006,7 @@
       <c r="J360" s="149">
         <v>98.0</v>
       </c>
-      <c r="K360" s="104">
+      <c r="K360">
         <f>(I360+(J360*E360))/1000</f>
         <v>4.164</v>
       </c>
@@ -63024,7 +63028,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="361" spans="8:8" ht="18.0">
+    <row r="361" spans="8:8" ht="16.9">
       <c r="A361" s="111" t="s">
         <v>1162</v>
       </c>
@@ -63054,7 +63058,7 @@
       <c r="J361" s="149">
         <v>8.0</v>
       </c>
-      <c r="K361" s="104">
+      <c r="K361">
         <f>(I361+(J361*E361))/1000</f>
         <v>8.28</v>
       </c>
@@ -63076,7 +63080,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="362" spans="8:8" ht="18.0">
+    <row r="362" spans="8:8" ht="16.9">
       <c r="A362" s="111" t="s">
         <v>1165</v>
       </c>
@@ -63106,7 +63110,7 @@
       <c r="J362" s="149">
         <v>264.0</v>
       </c>
-      <c r="K362" s="104">
+      <c r="K362">
         <f>(I362+(J362*E362))/1000</f>
         <v>2.918</v>
       </c>
@@ -63128,7 +63132,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="363" spans="8:8" ht="18.0">
+    <row r="363" spans="8:8" ht="16.9">
       <c r="A363" s="111" t="s">
         <v>1168</v>
       </c>
@@ -63156,7 +63160,7 @@
       <c r="J363" s="149">
         <v>207.0</v>
       </c>
-      <c r="K363" s="104">
+      <c r="K363">
         <f>(I363+(J363*E363))/1000</f>
         <v>0.28</v>
       </c>
@@ -63178,7 +63182,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="364" spans="8:8" ht="18.0">
+    <row r="364" spans="8:8" ht="16.9">
       <c r="A364" s="111" t="s">
         <v>1170</v>
       </c>
@@ -63206,7 +63210,7 @@
       <c r="J364" s="149">
         <v>207.0</v>
       </c>
-      <c r="K364" s="104">
+      <c r="K364">
         <f>(I364+(J364*E364))/1000</f>
         <v>0.28</v>
       </c>
@@ -63228,7 +63232,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="365" spans="8:8" ht="18.0">
+    <row r="365" spans="8:8" ht="16.9">
       <c r="A365" s="111" t="s">
         <v>1172</v>
       </c>
@@ -63256,7 +63260,7 @@
       <c r="J365" s="149">
         <v>72.0</v>
       </c>
-      <c r="K365" s="104">
+      <c r="K365">
         <f>(I365+(J365*E365))/1000</f>
         <v>0.244</v>
       </c>
@@ -63278,7 +63282,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="366" spans="8:8" ht="18.0">
+    <row r="366" spans="8:8" ht="16.9">
       <c r="A366" s="111" t="s">
         <v>1175</v>
       </c>
@@ -63306,7 +63310,7 @@
       <c r="J366" s="149">
         <v>124.0</v>
       </c>
-      <c r="K366" s="104">
+      <c r="K366">
         <f>(I366+(J366*E366))/1000</f>
         <v>0.244</v>
       </c>
@@ -63328,7 +63332,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="367" spans="8:8" ht="18.0">
+    <row r="367" spans="8:8" ht="16.9">
       <c r="A367" s="111" t="s">
         <v>1178</v>
       </c>
@@ -63356,7 +63360,7 @@
       <c r="J367" s="149">
         <v>70.0</v>
       </c>
-      <c r="K367" s="104">
+      <c r="K367">
         <f>(I367+(J367*E367))/1000</f>
         <v>0.244</v>
       </c>
@@ -63378,7 +63382,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="368" spans="8:8" ht="18.0">
+    <row r="368" spans="8:8" ht="16.9">
       <c r="A368" s="111" t="s">
         <v>1182</v>
       </c>
@@ -63406,7 +63410,7 @@
       <c r="J368" s="149">
         <v>70.0</v>
       </c>
-      <c r="K368" s="104">
+      <c r="K368">
         <f>(I368+(J368*E368))/1000</f>
         <v>0.244</v>
       </c>
@@ -63428,7 +63432,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="369" spans="8:8" ht="18.0">
+    <row r="369" spans="8:8" ht="16.9">
       <c r="A369" s="111" t="s">
         <v>1186</v>
       </c>
@@ -63456,7 +63460,7 @@
       <c r="J369" s="149">
         <v>37.6</v>
       </c>
-      <c r="K369" s="104">
+      <c r="K369">
         <f>(I369+(J369*E369))/1000</f>
         <v>0.244</v>
       </c>
@@ -63478,7 +63482,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="370" spans="8:8" ht="18.0">
+    <row r="370" spans="8:8" ht="16.9">
       <c r="A370" s="111" t="s">
         <v>1190</v>
       </c>
@@ -63506,7 +63510,7 @@
       <c r="J370" s="149">
         <v>20.0</v>
       </c>
-      <c r="K370" s="104">
+      <c r="K370">
         <f>(I370+(J370*E370))/1000</f>
         <v>0.244</v>
       </c>
@@ -63528,7 +63532,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="371" spans="8:8" ht="18.0">
+    <row r="371" spans="8:8" ht="16.9">
       <c r="A371" s="111" t="s">
         <v>1193</v>
       </c>
@@ -63558,7 +63562,7 @@
       <c r="J371" s="149">
         <v>31.7</v>
       </c>
-      <c r="K371" s="104">
+      <c r="K371">
         <f>(I371+(J371*E371))/1000</f>
         <v>3.1675999999999997</v>
       </c>
@@ -63580,7 +63584,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="372" spans="8:8" ht="18.0">
+    <row r="372" spans="8:8" ht="16.9">
       <c r="A372" s="111" t="s">
         <v>1196</v>
       </c>
@@ -63610,7 +63614,7 @@
       <c r="J372" s="149">
         <v>87.0</v>
       </c>
-      <c r="K372" s="104">
+      <c r="K372">
         <f>(I372+(J372*E372))/1000</f>
         <v>8.944</v>
       </c>
@@ -63632,7 +63636,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="373" spans="8:8" ht="18.0">
+    <row r="373" spans="8:8" ht="16.9">
       <c r="A373" s="111" t="s">
         <v>1199</v>
       </c>
@@ -63662,7 +63666,7 @@
       <c r="J373" s="149">
         <v>49.1</v>
       </c>
-      <c r="K373" s="104">
+      <c r="K373">
         <f>(I373+(J373*E373))/1000</f>
         <v>6.136</v>
       </c>
@@ -63684,7 +63688,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="374" spans="8:8" ht="18.0">
+    <row r="374" spans="8:8" ht="16.9">
       <c r="A374" s="111" t="s">
         <v>1202</v>
       </c>
@@ -63714,7 +63718,7 @@
       <c r="J374" s="149">
         <v>1.26</v>
       </c>
-      <c r="K374" s="104">
+      <c r="K374">
         <f>(I374+(J374*E374))/1000</f>
         <v>2.764</v>
       </c>
@@ -63741,45 +63745,45 @@
     <mergeCell ref="I3:M3"/>
     <mergeCell ref="A1:N2"/>
   </mergeCells>
+  <conditionalFormatting sqref="B334:B335">
+    <cfRule type="duplicateValues" priority="9" dxfId="19"/>
+    <cfRule type="duplicateValues" priority="8" dxfId="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B338">
+    <cfRule type="duplicateValues" priority="2" dxfId="21"/>
+    <cfRule type="duplicateValues" priority="1" dxfId="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B331:B332">
+    <cfRule type="duplicateValues" priority="12" dxfId="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H331:H332">
+    <cfRule type="duplicateValues" priority="5" dxfId="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H343:H348">
+    <cfRule type="duplicateValues" priority="19" dxfId="25"/>
+    <cfRule type="duplicateValues" priority="18" dxfId="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B327">
+    <cfRule type="duplicateValues" priority="15" dxfId="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B333">
+    <cfRule type="duplicateValues" priority="11" dxfId="28"/>
+    <cfRule type="duplicateValues" priority="10" dxfId="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B328">
+    <cfRule type="duplicateValues" priority="14" dxfId="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B336">
+    <cfRule type="duplicateValues" priority="7" dxfId="31"/>
+    <cfRule type="duplicateValues" priority="6" dxfId="32"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B339:B374">
-    <cfRule type="duplicateValues" priority="34" dxfId="19"/>
-    <cfRule type="duplicateValues" priority="35" dxfId="20"/>
+    <cfRule type="duplicateValues" priority="34" dxfId="33"/>
+    <cfRule type="duplicateValues" priority="35" dxfId="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B337">
-    <cfRule type="duplicateValues" priority="3" dxfId="21"/>
-    <cfRule type="duplicateValues" priority="4" dxfId="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B336">
-    <cfRule type="duplicateValues" priority="7" dxfId="23"/>
-    <cfRule type="duplicateValues" priority="6" dxfId="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B333">
-    <cfRule type="duplicateValues" priority="11" dxfId="25"/>
-    <cfRule type="duplicateValues" priority="10" dxfId="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B328">
-    <cfRule type="duplicateValues" priority="14" dxfId="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B338">
-    <cfRule type="duplicateValues" priority="1" dxfId="28"/>
-    <cfRule type="duplicateValues" priority="2" dxfId="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B331:B332">
-    <cfRule type="duplicateValues" priority="12" dxfId="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H331:H332">
-    <cfRule type="duplicateValues" priority="5" dxfId="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B327">
-    <cfRule type="duplicateValues" priority="15" dxfId="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H343:H348">
-    <cfRule type="duplicateValues" priority="18" dxfId="33"/>
-    <cfRule type="duplicateValues" priority="19" dxfId="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B334:B335">
-    <cfRule type="duplicateValues" priority="9" dxfId="35"/>
-    <cfRule type="duplicateValues" priority="8" dxfId="36"/>
+    <cfRule type="duplicateValues" priority="3" dxfId="35"/>
+    <cfRule type="duplicateValues" priority="4" dxfId="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B329:B330">
     <cfRule type="duplicateValues" priority="13" dxfId="37"/>
@@ -63791,7 +63795,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="12.7109375" style="0"/>
